--- a/144/DQ Templates and Instructions/Topic 5 DQ 2/Topic 5 DQ 2.xlsx
+++ b/144/DQ Templates and Instructions/Topic 5 DQ 2/Topic 5 DQ 2.xlsx
@@ -5,12 +5,12 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://gcumail-my.sharepoint.com/personal/richard_ketchersid_gcu_edu/Documents/Course Materials/git/Teaching/144/DQ Templates and Instructions/Topic 5 DQ 2/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://gcumail.sharepoint.com/sites/MathematicsProgramFacultyStaff-MATOFTF/Shared Documents/MATOFTF/ALEKS/DQ Templates and Instructions/Topic 5 DQ 2/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="429" documentId="13_ncr:1_{01544684-905C-417E-A831-5CA460CC2737}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{13701FA5-648C-5089-A33E-7230B2E5BF64}"/>
+  <xr:revisionPtr revIDLastSave="437" documentId="13_ncr:1_{01544684-905C-417E-A831-5CA460CC2737}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EDFBA17D-8293-463C-ACE5-3B8D9698E8AC}"/>
   <bookViews>
-    <workbookView xWindow="1095" yWindow="0" windowWidth="27000" windowHeight="15645" tabRatio="649" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="649" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Goals and Instructions" sheetId="7" r:id="rId1"/>
@@ -6500,7 +6500,7 @@
         <v>#N/A</v>
       </c>
       <c r="K25" s="50" t="b">
-        <f ca="1">IFERROR(OR(J25:J26),FALSE)</f>
+        <f ca="1">IFERROR(OR(J25:J27),FALSE)</f>
         <v>0</v>
       </c>
       <c r="AK25" s="50">
@@ -6545,6 +6545,10 @@
       <c r="F27" s="155"/>
       <c r="G27" s="155"/>
       <c r="H27" s="156"/>
+      <c r="J27" s="50" t="e">
+        <f ca="1">SUBSTITUTE(SUBSTITUTE(_xlfn.FORMULATEXT('Water Quality'!G11), " ",""),"$","") = "=FREQUENCY(Difference_in_water_quality,E11:E20)"</f>
+        <v>#N/A</v>
+      </c>
       <c r="AK27" s="50">
         <f t="shared" si="1"/>
         <v>145</v>
@@ -7765,7 +7769,7 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="YPVebjYUhGbt44GV5/LjJQGkdbY1AOR4VHFZ4fgF19dfIxxpR6wTLej6Al6tJgi8f/Hn23uhiliWkAhDB9UpWA==" saltValue="NqTYqMZdnstkH+c1Vfq59Q==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="B2U0Nw9tFkRrTqNzu4uLjIdeRoY3notrCVZBF0XCAVaZqX1RRmcsY/1RC92isVhdqgWBs0A8o3eyxjxupwGjnQ==" saltValue="ZjDy95YJELmAOjAiI1hydw==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
   <mergeCells count="9">
     <mergeCell ref="J10:O23"/>
     <mergeCell ref="D24:H27"/>
@@ -18275,121 +18279,121 @@
     <row r="2" spans="1:1">
       <c r="A2" s="3">
         <f ca="1">ROUND(NORMINV(RAND(),68,3.75),1)</f>
-        <v>67.3</v>
+        <v>64.599999999999994</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="3">
         <f t="shared" ref="A3:A66" ca="1" si="0">ROUND(NORMINV(RAND(),68,3.75),1)</f>
-        <v>68.2</v>
+        <v>69.7</v>
       </c>
     </row>
     <row r="4" spans="1:1">
       <c r="A4" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>67.400000000000006</v>
+        <v>66.900000000000006</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>70</v>
+        <v>73.5</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>71.400000000000006</v>
+        <v>68.900000000000006</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>70.3</v>
+        <v>67.099999999999994</v>
       </c>
     </row>
     <row r="8" spans="1:1">
       <c r="A8" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>66</v>
+        <v>70.400000000000006</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>71.599999999999994</v>
+        <v>63.7</v>
       </c>
     </row>
     <row r="10" spans="1:1">
       <c r="A10" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>64.8</v>
+        <v>73.099999999999994</v>
       </c>
     </row>
     <row r="11" spans="1:1">
       <c r="A11" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>72.5</v>
+        <v>63.5</v>
       </c>
     </row>
     <row r="12" spans="1:1">
       <c r="A12" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>73.7</v>
+        <v>67.2</v>
       </c>
     </row>
     <row r="13" spans="1:1">
       <c r="A13" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>71.400000000000006</v>
+        <v>70.2</v>
       </c>
     </row>
     <row r="14" spans="1:1">
       <c r="A14" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>63.4</v>
+        <v>74.400000000000006</v>
       </c>
     </row>
     <row r="15" spans="1:1">
       <c r="A15" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>64.7</v>
+        <v>72.3</v>
       </c>
     </row>
     <row r="16" spans="1:1">
       <c r="A16" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>69.599999999999994</v>
+        <v>66.400000000000006</v>
       </c>
     </row>
     <row r="17" spans="1:1">
       <c r="A17" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>65.8</v>
+        <v>69.099999999999994</v>
       </c>
     </row>
     <row r="18" spans="1:1">
       <c r="A18" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>72.400000000000006</v>
+        <v>62.8</v>
       </c>
     </row>
     <row r="19" spans="1:1">
       <c r="A19" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>70</v>
+        <v>66.2</v>
       </c>
     </row>
     <row r="20" spans="1:1">
       <c r="A20" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>69.900000000000006</v>
+        <v>70.5</v>
       </c>
     </row>
     <row r="21" spans="1:1">
       <c r="A21" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>63.8</v>
+        <v>67.7</v>
       </c>
     </row>
     <row r="22" spans="1:1">
@@ -18401,7 +18405,7 @@
     <row r="23" spans="1:1">
       <c r="A23" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>65.3</v>
+        <v>62.7</v>
       </c>
     </row>
     <row r="24" spans="1:1">
@@ -18413,7 +18417,7 @@
     <row r="25" spans="1:1">
       <c r="A25" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>66.099999999999994</v>
+        <v>70.099999999999994</v>
       </c>
     </row>
     <row r="26" spans="1:1">
@@ -18425,331 +18429,331 @@
     <row r="27" spans="1:1">
       <c r="A27" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>66.3</v>
+        <v>68.7</v>
       </c>
     </row>
     <row r="28" spans="1:1">
       <c r="A28" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>72.8</v>
+        <v>67.7</v>
       </c>
     </row>
     <row r="29" spans="1:1">
       <c r="A29" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>70.8</v>
+        <v>75.5</v>
       </c>
     </row>
     <row r="30" spans="1:1">
       <c r="A30" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>72.2</v>
+        <v>69.900000000000006</v>
       </c>
     </row>
     <row r="31" spans="1:1">
       <c r="A31" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>69.2</v>
+        <v>67.3</v>
       </c>
     </row>
     <row r="32" spans="1:1">
       <c r="A32" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>70.099999999999994</v>
+        <v>66.599999999999994</v>
       </c>
     </row>
     <row r="33" spans="1:1">
       <c r="A33" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>70.2</v>
+        <v>72</v>
       </c>
     </row>
     <row r="34" spans="1:1">
       <c r="A34" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>62.1</v>
+        <v>73.099999999999994</v>
       </c>
     </row>
     <row r="35" spans="1:1">
       <c r="A35" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>70.900000000000006</v>
+        <v>64.599999999999994</v>
       </c>
     </row>
     <row r="36" spans="1:1">
       <c r="A36" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>73.400000000000006</v>
+        <v>64</v>
       </c>
     </row>
     <row r="37" spans="1:1">
       <c r="A37" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>71.400000000000006</v>
+        <v>79.5</v>
       </c>
     </row>
     <row r="38" spans="1:1">
       <c r="A38" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>72.5</v>
+        <v>66.099999999999994</v>
       </c>
     </row>
     <row r="39" spans="1:1">
       <c r="A39" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>65.599999999999994</v>
+        <v>60.2</v>
       </c>
     </row>
     <row r="40" spans="1:1">
       <c r="A40" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>67.400000000000006</v>
+        <v>58.9</v>
       </c>
     </row>
     <row r="41" spans="1:1">
       <c r="A41" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>81.8</v>
+        <v>64.2</v>
       </c>
     </row>
     <row r="42" spans="1:1">
       <c r="A42" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>74.400000000000006</v>
+        <v>73.900000000000006</v>
       </c>
     </row>
     <row r="43" spans="1:1">
       <c r="A43" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>62.9</v>
+        <v>64.099999999999994</v>
       </c>
     </row>
     <row r="44" spans="1:1">
       <c r="A44" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>69.3</v>
+        <v>65.599999999999994</v>
       </c>
     </row>
     <row r="45" spans="1:1">
       <c r="A45" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>71.400000000000006</v>
+        <v>63.2</v>
       </c>
     </row>
     <row r="46" spans="1:1">
       <c r="A46" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>65.7</v>
+        <v>70</v>
       </c>
     </row>
     <row r="47" spans="1:1">
       <c r="A47" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>68.400000000000006</v>
+        <v>65.7</v>
       </c>
     </row>
     <row r="48" spans="1:1">
       <c r="A48" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>63.6</v>
+        <v>70.8</v>
       </c>
     </row>
     <row r="49" spans="1:1">
       <c r="A49" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>61.7</v>
+        <v>67</v>
       </c>
     </row>
     <row r="50" spans="1:1">
       <c r="A50" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>66.900000000000006</v>
+        <v>61.5</v>
       </c>
     </row>
     <row r="51" spans="1:1">
       <c r="A51" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>67.7</v>
+        <v>69</v>
       </c>
     </row>
     <row r="52" spans="1:1">
       <c r="A52" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>64.099999999999994</v>
+        <v>70.8</v>
       </c>
     </row>
     <row r="53" spans="1:1">
       <c r="A53" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>66.400000000000006</v>
+        <v>65.7</v>
       </c>
     </row>
     <row r="54" spans="1:1">
       <c r="A54" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>65.5</v>
+        <v>62.8</v>
       </c>
     </row>
     <row r="55" spans="1:1">
       <c r="A55" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>63.4</v>
+        <v>69.7</v>
       </c>
     </row>
     <row r="56" spans="1:1">
       <c r="A56" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>69.099999999999994</v>
+        <v>66.3</v>
       </c>
     </row>
     <row r="57" spans="1:1">
       <c r="A57" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>66.2</v>
+        <v>67.900000000000006</v>
       </c>
     </row>
     <row r="58" spans="1:1">
       <c r="A58" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>65.5</v>
+        <v>69.7</v>
       </c>
     </row>
     <row r="59" spans="1:1">
       <c r="A59" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>69</v>
+        <v>73.7</v>
       </c>
     </row>
     <row r="60" spans="1:1">
       <c r="A60" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>62</v>
+        <v>71</v>
       </c>
     </row>
     <row r="61" spans="1:1">
       <c r="A61" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>64.2</v>
+        <v>67.8</v>
       </c>
     </row>
     <row r="62" spans="1:1">
       <c r="A62" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>67.400000000000006</v>
+        <v>63.9</v>
       </c>
     </row>
     <row r="63" spans="1:1">
       <c r="A63" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>71.599999999999994</v>
+        <v>65.599999999999994</v>
       </c>
     </row>
     <row r="64" spans="1:1">
       <c r="A64" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>64.900000000000006</v>
+        <v>70.599999999999994</v>
       </c>
     </row>
     <row r="65" spans="1:1">
       <c r="A65" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>62.1</v>
+        <v>72.099999999999994</v>
       </c>
     </row>
     <row r="66" spans="1:1">
       <c r="A66" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>67.900000000000006</v>
+        <v>67.099999999999994</v>
       </c>
     </row>
     <row r="67" spans="1:1">
       <c r="A67" s="3">
         <f t="shared" ref="A67:A103" ca="1" si="1">ROUND(NORMINV(RAND(),68,3.75),1)</f>
-        <v>63.8</v>
+        <v>71.2</v>
       </c>
     </row>
     <row r="68" spans="1:1">
       <c r="A68" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>73</v>
+        <v>67.7</v>
       </c>
     </row>
     <row r="69" spans="1:1">
       <c r="A69" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>69.599999999999994</v>
+        <v>71.7</v>
       </c>
     </row>
     <row r="70" spans="1:1">
       <c r="A70" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>68.5</v>
+        <v>61.6</v>
       </c>
     </row>
     <row r="71" spans="1:1">
       <c r="A71" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>76.900000000000006</v>
+        <v>72.7</v>
       </c>
     </row>
     <row r="72" spans="1:1">
       <c r="A72" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>66.400000000000006</v>
+        <v>62.9</v>
       </c>
     </row>
     <row r="73" spans="1:1">
       <c r="A73" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>71.7</v>
+        <v>68.5</v>
       </c>
     </row>
     <row r="74" spans="1:1">
       <c r="A74" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>76.400000000000006</v>
+        <v>67.900000000000006</v>
       </c>
     </row>
     <row r="75" spans="1:1">
       <c r="A75" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>71.3</v>
+        <v>70.7</v>
       </c>
     </row>
     <row r="76" spans="1:1">
       <c r="A76" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>69.099999999999994</v>
+        <v>61.6</v>
       </c>
     </row>
     <row r="77" spans="1:1">
       <c r="A77" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>62.2</v>
+        <v>66.8</v>
       </c>
     </row>
     <row r="78" spans="1:1">
       <c r="A78" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>62.3</v>
+        <v>71.5</v>
       </c>
     </row>
     <row r="79" spans="1:1">
       <c r="A79" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>70.3</v>
+        <v>68.7</v>
       </c>
     </row>
     <row r="80" spans="1:1">
       <c r="A80" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>75.8</v>
+        <v>72.2</v>
       </c>
     </row>
     <row r="81" spans="1:1">
       <c r="A81" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>63.3</v>
+        <v>74.900000000000006</v>
       </c>
     </row>
     <row r="82" spans="1:1">
@@ -18761,127 +18765,127 @@
     <row r="83" spans="1:1">
       <c r="A83" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>70.099999999999994</v>
+        <v>62.3</v>
       </c>
     </row>
     <row r="84" spans="1:1">
       <c r="A84" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>71.599999999999994</v>
+        <v>66.5</v>
       </c>
     </row>
     <row r="85" spans="1:1">
       <c r="A85" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>65.8</v>
+        <v>64.7</v>
       </c>
     </row>
     <row r="86" spans="1:1">
       <c r="A86" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>67.099999999999994</v>
+        <v>71.099999999999994</v>
       </c>
     </row>
     <row r="87" spans="1:1">
       <c r="A87" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>66.7</v>
+        <v>71.599999999999994</v>
       </c>
     </row>
     <row r="88" spans="1:1">
       <c r="A88" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>67.599999999999994</v>
+        <v>74.3</v>
       </c>
     </row>
     <row r="89" spans="1:1">
       <c r="A89" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>68.8</v>
+        <v>70.900000000000006</v>
       </c>
     </row>
     <row r="90" spans="1:1">
       <c r="A90" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>67.5</v>
+        <v>62.8</v>
       </c>
     </row>
     <row r="91" spans="1:1">
       <c r="A91" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>67.900000000000006</v>
+        <v>65.3</v>
       </c>
     </row>
     <row r="92" spans="1:1">
       <c r="A92" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>66</v>
+        <v>71.599999999999994</v>
       </c>
     </row>
     <row r="93" spans="1:1">
       <c r="A93" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>66.8</v>
+        <v>67.099999999999994</v>
       </c>
     </row>
     <row r="94" spans="1:1">
       <c r="A94" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>63.5</v>
+        <v>66.2</v>
       </c>
     </row>
     <row r="95" spans="1:1">
       <c r="A95" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>67.3</v>
+        <v>67</v>
       </c>
     </row>
     <row r="96" spans="1:1">
       <c r="A96" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>70.5</v>
+        <v>67.900000000000006</v>
       </c>
     </row>
     <row r="97" spans="1:1">
       <c r="A97" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>70.2</v>
+        <v>65.400000000000006</v>
       </c>
     </row>
     <row r="98" spans="1:1">
       <c r="A98" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>74.3</v>
+        <v>65.2</v>
       </c>
     </row>
     <row r="99" spans="1:1">
       <c r="A99" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>61</v>
+        <v>63.1</v>
       </c>
     </row>
     <row r="100" spans="1:1">
       <c r="A100" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>61.7</v>
+        <v>66.599999999999994</v>
       </c>
     </row>
     <row r="101" spans="1:1">
       <c r="A101" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>66.400000000000006</v>
+        <v>65</v>
       </c>
     </row>
     <row r="102" spans="1:1">
       <c r="A102" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>68.2</v>
+        <v>64.5</v>
       </c>
     </row>
     <row r="103" spans="1:1">
       <c r="A103" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>72.8</v>
+        <v>68.900000000000006</v>
       </c>
     </row>
   </sheetData>
@@ -18993,6 +18997,16 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="cca9fd2d-ef84-45c9-8063-8f4bd4c29606">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101002C289946819CFF499E91D197BC975371" ma:contentTypeVersion="13" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="674b7a4e239a9748c7aaa97e309327a4">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="cca9fd2d-ef84-45c9-8063-8f4bd4c29606" xmlns:ns3="18557d39-01b8-4d71-9479-3fad465290ae" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="600253478e594d1349e02792803dc53a" ns2:_="" ns3:_="">
     <xsd:import namespace="cca9fd2d-ef84-45c9-8063-8f4bd4c29606"/>
@@ -19209,16 +19223,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="cca9fd2d-ef84-45c9-8063-8f4bd4c29606">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{17F1EF20-95AB-4016-A693-6625F3A67214}">
   <ds:schemaRefs>
@@ -19228,6 +19232,16 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{924A8F3D-57F5-4941-A32A-55B7F7F7AF07}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="cca9fd2d-ef84-45c9-8063-8f4bd4c29606"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8F527DFD-99D6-4A6C-AC9B-EC23CCFE992B}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -19244,14 +19258,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{924A8F3D-57F5-4941-A32A-55B7F7F7AF07}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="cca9fd2d-ef84-45c9-8063-8f4bd4c29606"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/144/DQ Templates and Instructions/Topic 5 DQ 2/Topic 5 DQ 2.xlsx
+++ b/144/DQ Templates and Instructions/Topic 5 DQ 2/Topic 5 DQ 2.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://gcumail.sharepoint.com/sites/MathematicsProgramFacultyStaff-MATOFTF/Shared Documents/MATOFTF/ALEKS/DQ Templates and Instructions/Topic 5 DQ 2/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="437" documentId="13_ncr:1_{01544684-905C-417E-A831-5CA460CC2737}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EDFBA17D-8293-463C-ACE5-3B8D9698E8AC}"/>
+  <xr:revisionPtr revIDLastSave="440" documentId="13_ncr:1_{01544684-905C-417E-A831-5CA460CC2737}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E2C0B8A9-1FEA-4679-903E-3F7064AE11E2}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="649" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="12684" windowWidth="21600" windowHeight="12516" tabRatio="649" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Goals and Instructions" sheetId="7" r:id="rId1"/>
@@ -21,8 +21,6 @@
     <sheet name="Sheet1" sheetId="8" state="hidden" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="Difference_in_water_quality">'Water Quality'!$B$2:$B$103</definedName>
-    <definedName name="height">'Water Quality'!$B$2:$B$103</definedName>
     <definedName name="Z_8A50E3A6_4261_4BD1_A94F_918D0E3EEAC3_.wvu.Cols" localSheetId="1" hidden="1">'Water Quality'!$AK:$AK</definedName>
   </definedNames>
   <calcPr calcId="191028"/>
@@ -5595,7 +5593,7 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="Pq7RIan/mNZCLPQcvx5p6eX4ElFx78FdxcQeCdKs0gUFg9Diu5AiOyVXN2o7+xYS69a/hE0JJg/bG6DtG6HaHw==" saltValue="rGSJJDonhgn5KWAFFm175Q==" spinCount="100000" sheet="1" formatCells="0" formatColumns="0" insertColumns="0" insertHyperlinks="0"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="KtmsjmAtDQLDyqMZss2JToUwi0WfhTAUOtFvRU4AbgQM8hr0gj0bR7jvKLPHeZrfRCGTm90GzbbxeaBsyO2i2Q==" saltValue="PD74Wt5QUXpE0KrXj4s4Hw==" spinCount="100000" sheet="1" formatCells="0" formatColumns="0" insertColumns="0" insertHyperlinks="0"/>
   <dataConsolidate/>
   <customSheetViews>
     <customSheetView guid="{8A50E3A6-4261-4BD1-A94F-918D0E3EEAC3}" hiddenColumns="1">
@@ -18285,607 +18283,607 @@
     <row r="3" spans="1:1">
       <c r="A3" s="3">
         <f t="shared" ref="A3:A66" ca="1" si="0">ROUND(NORMINV(RAND(),68,3.75),1)</f>
-        <v>69.7</v>
+        <v>65.599999999999994</v>
       </c>
     </row>
     <row r="4" spans="1:1">
       <c r="A4" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>66.900000000000006</v>
+        <v>69.8</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>73.5</v>
+        <v>65.400000000000006</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>68.900000000000006</v>
+        <v>65.7</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>67.099999999999994</v>
+        <v>66.8</v>
       </c>
     </row>
     <row r="8" spans="1:1">
       <c r="A8" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>70.400000000000006</v>
+        <v>64.900000000000006</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>63.7</v>
+        <v>61</v>
       </c>
     </row>
     <row r="10" spans="1:1">
       <c r="A10" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>73.099999999999994</v>
+        <v>66.2</v>
       </c>
     </row>
     <row r="11" spans="1:1">
       <c r="A11" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>63.5</v>
+        <v>68.2</v>
       </c>
     </row>
     <row r="12" spans="1:1">
       <c r="A12" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>67.2</v>
+        <v>67.900000000000006</v>
       </c>
     </row>
     <row r="13" spans="1:1">
       <c r="A13" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>70.2</v>
+        <v>59.3</v>
       </c>
     </row>
     <row r="14" spans="1:1">
       <c r="A14" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>74.400000000000006</v>
+        <v>75.099999999999994</v>
       </c>
     </row>
     <row r="15" spans="1:1">
       <c r="A15" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>72.3</v>
+        <v>67.099999999999994</v>
       </c>
     </row>
     <row r="16" spans="1:1">
       <c r="A16" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>66.400000000000006</v>
+        <v>64.400000000000006</v>
       </c>
     </row>
     <row r="17" spans="1:1">
       <c r="A17" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>69.099999999999994</v>
+        <v>68.599999999999994</v>
       </c>
     </row>
     <row r="18" spans="1:1">
       <c r="A18" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>62.8</v>
+        <v>64.400000000000006</v>
       </c>
     </row>
     <row r="19" spans="1:1">
       <c r="A19" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>66.2</v>
+        <v>73.900000000000006</v>
       </c>
     </row>
     <row r="20" spans="1:1">
       <c r="A20" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>70.5</v>
+        <v>63.8</v>
       </c>
     </row>
     <row r="21" spans="1:1">
       <c r="A21" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>67.7</v>
+        <v>65.7</v>
       </c>
     </row>
     <row r="22" spans="1:1">
       <c r="A22" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>67.599999999999994</v>
+        <v>69.599999999999994</v>
       </c>
     </row>
     <row r="23" spans="1:1">
       <c r="A23" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>62.7</v>
+        <v>64</v>
       </c>
     </row>
     <row r="24" spans="1:1">
       <c r="A24" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>72.099999999999994</v>
+        <v>69.8</v>
       </c>
     </row>
     <row r="25" spans="1:1">
       <c r="A25" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>70.099999999999994</v>
+        <v>68.099999999999994</v>
       </c>
     </row>
     <row r="26" spans="1:1">
       <c r="A26" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>70.599999999999994</v>
+        <v>66</v>
       </c>
     </row>
     <row r="27" spans="1:1">
       <c r="A27" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>68.7</v>
+        <v>75.400000000000006</v>
       </c>
     </row>
     <row r="28" spans="1:1">
       <c r="A28" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>67.7</v>
+        <v>66.400000000000006</v>
       </c>
     </row>
     <row r="29" spans="1:1">
       <c r="A29" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>75.5</v>
+        <v>72.5</v>
       </c>
     </row>
     <row r="30" spans="1:1">
       <c r="A30" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>69.900000000000006</v>
+        <v>66.5</v>
       </c>
     </row>
     <row r="31" spans="1:1">
       <c r="A31" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>67.3</v>
+        <v>69.3</v>
       </c>
     </row>
     <row r="32" spans="1:1">
       <c r="A32" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>66.599999999999994</v>
+        <v>64.3</v>
       </c>
     </row>
     <row r="33" spans="1:1">
       <c r="A33" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>72</v>
+        <v>68</v>
       </c>
     </row>
     <row r="34" spans="1:1">
       <c r="A34" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>73.099999999999994</v>
+        <v>69</v>
       </c>
     </row>
     <row r="35" spans="1:1">
       <c r="A35" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>64.599999999999994</v>
+        <v>67.3</v>
       </c>
     </row>
     <row r="36" spans="1:1">
       <c r="A36" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>64</v>
+        <v>64.8</v>
       </c>
     </row>
     <row r="37" spans="1:1">
       <c r="A37" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>79.5</v>
+        <v>66.3</v>
       </c>
     </row>
     <row r="38" spans="1:1">
       <c r="A38" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>66.099999999999994</v>
+        <v>62.1</v>
       </c>
     </row>
     <row r="39" spans="1:1">
       <c r="A39" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>60.2</v>
+        <v>62.2</v>
       </c>
     </row>
     <row r="40" spans="1:1">
       <c r="A40" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>58.9</v>
+        <v>70.599999999999994</v>
       </c>
     </row>
     <row r="41" spans="1:1">
       <c r="A41" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>64.2</v>
+        <v>74.8</v>
       </c>
     </row>
     <row r="42" spans="1:1">
       <c r="A42" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>73.900000000000006</v>
+        <v>70</v>
       </c>
     </row>
     <row r="43" spans="1:1">
       <c r="A43" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>64.099999999999994</v>
+        <v>71</v>
       </c>
     </row>
     <row r="44" spans="1:1">
       <c r="A44" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>65.599999999999994</v>
+        <v>61.5</v>
       </c>
     </row>
     <row r="45" spans="1:1">
       <c r="A45" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>63.2</v>
+        <v>75.5</v>
       </c>
     </row>
     <row r="46" spans="1:1">
       <c r="A46" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>70</v>
+        <v>70.599999999999994</v>
       </c>
     </row>
     <row r="47" spans="1:1">
       <c r="A47" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>65.7</v>
+        <v>69.5</v>
       </c>
     </row>
     <row r="48" spans="1:1">
       <c r="A48" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>70.8</v>
+        <v>61.6</v>
       </c>
     </row>
     <row r="49" spans="1:1">
       <c r="A49" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>67</v>
+        <v>71.8</v>
       </c>
     </row>
     <row r="50" spans="1:1">
       <c r="A50" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>61.5</v>
+        <v>65.900000000000006</v>
       </c>
     </row>
     <row r="51" spans="1:1">
       <c r="A51" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>69</v>
+        <v>71.900000000000006</v>
       </c>
     </row>
     <row r="52" spans="1:1">
       <c r="A52" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>70.8</v>
+        <v>67.5</v>
       </c>
     </row>
     <row r="53" spans="1:1">
       <c r="A53" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>65.7</v>
+        <v>74.099999999999994</v>
       </c>
     </row>
     <row r="54" spans="1:1">
       <c r="A54" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>62.8</v>
+        <v>71.8</v>
       </c>
     </row>
     <row r="55" spans="1:1">
       <c r="A55" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>69.7</v>
+        <v>66.099999999999994</v>
       </c>
     </row>
     <row r="56" spans="1:1">
       <c r="A56" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>66.3</v>
+        <v>67.7</v>
       </c>
     </row>
     <row r="57" spans="1:1">
       <c r="A57" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>67.900000000000006</v>
+        <v>65.7</v>
       </c>
     </row>
     <row r="58" spans="1:1">
       <c r="A58" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>69.7</v>
+        <v>68.2</v>
       </c>
     </row>
     <row r="59" spans="1:1">
       <c r="A59" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>73.7</v>
+        <v>70.599999999999994</v>
       </c>
     </row>
     <row r="60" spans="1:1">
       <c r="A60" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>71</v>
+        <v>67.2</v>
       </c>
     </row>
     <row r="61" spans="1:1">
       <c r="A61" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>67.8</v>
+        <v>66.3</v>
       </c>
     </row>
     <row r="62" spans="1:1">
       <c r="A62" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>63.9</v>
+        <v>63.3</v>
       </c>
     </row>
     <row r="63" spans="1:1">
       <c r="A63" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>65.599999999999994</v>
+        <v>67.599999999999994</v>
       </c>
     </row>
     <row r="64" spans="1:1">
       <c r="A64" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>70.599999999999994</v>
+        <v>70.900000000000006</v>
       </c>
     </row>
     <row r="65" spans="1:1">
       <c r="A65" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>72.099999999999994</v>
+        <v>70.3</v>
       </c>
     </row>
     <row r="66" spans="1:1">
       <c r="A66" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>67.099999999999994</v>
+        <v>67.3</v>
       </c>
     </row>
     <row r="67" spans="1:1">
       <c r="A67" s="3">
         <f t="shared" ref="A67:A103" ca="1" si="1">ROUND(NORMINV(RAND(),68,3.75),1)</f>
-        <v>71.2</v>
+        <v>60.9</v>
       </c>
     </row>
     <row r="68" spans="1:1">
       <c r="A68" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>67.7</v>
+        <v>68.7</v>
       </c>
     </row>
     <row r="69" spans="1:1">
       <c r="A69" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>71.7</v>
+        <v>63.9</v>
       </c>
     </row>
     <row r="70" spans="1:1">
       <c r="A70" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>61.6</v>
+        <v>61.1</v>
       </c>
     </row>
     <row r="71" spans="1:1">
       <c r="A71" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>72.7</v>
+        <v>65.599999999999994</v>
       </c>
     </row>
     <row r="72" spans="1:1">
       <c r="A72" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>62.9</v>
+        <v>68.599999999999994</v>
       </c>
     </row>
     <row r="73" spans="1:1">
       <c r="A73" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>68.5</v>
+        <v>65.900000000000006</v>
       </c>
     </row>
     <row r="74" spans="1:1">
       <c r="A74" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>67.900000000000006</v>
+        <v>65.099999999999994</v>
       </c>
     </row>
     <row r="75" spans="1:1">
       <c r="A75" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>70.7</v>
+        <v>72.099999999999994</v>
       </c>
     </row>
     <row r="76" spans="1:1">
       <c r="A76" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>61.6</v>
+        <v>67.099999999999994</v>
       </c>
     </row>
     <row r="77" spans="1:1">
       <c r="A77" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>66.8</v>
+        <v>70</v>
       </c>
     </row>
     <row r="78" spans="1:1">
       <c r="A78" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>71.5</v>
+        <v>64.900000000000006</v>
       </c>
     </row>
     <row r="79" spans="1:1">
       <c r="A79" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>68.7</v>
+        <v>70.599999999999994</v>
       </c>
     </row>
     <row r="80" spans="1:1">
       <c r="A80" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>72.2</v>
+        <v>68.3</v>
       </c>
     </row>
     <row r="81" spans="1:1">
       <c r="A81" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>74.900000000000006</v>
+        <v>66.5</v>
       </c>
     </row>
     <row r="82" spans="1:1">
       <c r="A82" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>71.400000000000006</v>
+        <v>69</v>
       </c>
     </row>
     <row r="83" spans="1:1">
       <c r="A83" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>62.3</v>
+        <v>64</v>
       </c>
     </row>
     <row r="84" spans="1:1">
       <c r="A84" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>66.5</v>
+        <v>70.400000000000006</v>
       </c>
     </row>
     <row r="85" spans="1:1">
       <c r="A85" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>64.7</v>
+        <v>64.599999999999994</v>
       </c>
     </row>
     <row r="86" spans="1:1">
       <c r="A86" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>71.099999999999994</v>
+        <v>69</v>
       </c>
     </row>
     <row r="87" spans="1:1">
       <c r="A87" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>71.599999999999994</v>
+        <v>64.2</v>
       </c>
     </row>
     <row r="88" spans="1:1">
       <c r="A88" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>74.3</v>
+        <v>68.599999999999994</v>
       </c>
     </row>
     <row r="89" spans="1:1">
       <c r="A89" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>70.900000000000006</v>
+        <v>66.7</v>
       </c>
     </row>
     <row r="90" spans="1:1">
       <c r="A90" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>62.8</v>
+        <v>68.8</v>
       </c>
     </row>
     <row r="91" spans="1:1">
       <c r="A91" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>65.3</v>
+        <v>65.5</v>
       </c>
     </row>
     <row r="92" spans="1:1">
       <c r="A92" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>71.599999999999994</v>
+        <v>66.400000000000006</v>
       </c>
     </row>
     <row r="93" spans="1:1">
       <c r="A93" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>67.099999999999994</v>
+        <v>76.900000000000006</v>
       </c>
     </row>
     <row r="94" spans="1:1">
       <c r="A94" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>66.2</v>
+        <v>73.900000000000006</v>
       </c>
     </row>
     <row r="95" spans="1:1">
       <c r="A95" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>67</v>
+        <v>63.8</v>
       </c>
     </row>
     <row r="96" spans="1:1">
       <c r="A96" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>67.900000000000006</v>
+        <v>70.5</v>
       </c>
     </row>
     <row r="97" spans="1:1">
       <c r="A97" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>65.400000000000006</v>
+        <v>63</v>
       </c>
     </row>
     <row r="98" spans="1:1">
       <c r="A98" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>65.2</v>
+        <v>68.7</v>
       </c>
     </row>
     <row r="99" spans="1:1">
       <c r="A99" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>63.1</v>
+        <v>73.900000000000006</v>
       </c>
     </row>
     <row r="100" spans="1:1">
       <c r="A100" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>66.599999999999994</v>
+        <v>67.099999999999994</v>
       </c>
     </row>
     <row r="101" spans="1:1">
       <c r="A101" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>65</v>
+        <v>75.8</v>
       </c>
     </row>
     <row r="102" spans="1:1">
       <c r="A102" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>64.5</v>
+        <v>63.8</v>
       </c>
     </row>
     <row r="103" spans="1:1">
       <c r="A103" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>68.900000000000006</v>
+        <v>68.5</v>
       </c>
     </row>
   </sheetData>
@@ -18997,16 +18995,6 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="cca9fd2d-ef84-45c9-8063-8f4bd4c29606">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101002C289946819CFF499E91D197BC975371" ma:contentTypeVersion="13" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="674b7a4e239a9748c7aaa97e309327a4">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="cca9fd2d-ef84-45c9-8063-8f4bd4c29606" xmlns:ns3="18557d39-01b8-4d71-9479-3fad465290ae" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="600253478e594d1349e02792803dc53a" ns2:_="" ns3:_="">
     <xsd:import namespace="cca9fd2d-ef84-45c9-8063-8f4bd4c29606"/>
@@ -19223,6 +19211,16 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="cca9fd2d-ef84-45c9-8063-8f4bd4c29606">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{17F1EF20-95AB-4016-A693-6625F3A67214}">
   <ds:schemaRefs>
@@ -19232,16 +19230,6 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{924A8F3D-57F5-4941-A32A-55B7F7F7AF07}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="cca9fd2d-ef84-45c9-8063-8f4bd4c29606"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8F527DFD-99D6-4A6C-AC9B-EC23CCFE992B}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -19258,4 +19246,14 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{924A8F3D-57F5-4941-A32A-55B7F7F7AF07}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="cca9fd2d-ef84-45c9-8063-8f4bd4c29606"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/144/DQ Templates and Instructions/Topic 5 DQ 2/Topic 5 DQ 2.xlsx
+++ b/144/DQ Templates and Instructions/Topic 5 DQ 2/Topic 5 DQ 2.xlsx
@@ -5,10 +5,10 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://gcumail.sharepoint.com/sites/MathematicsProgramFacultyStaff-MATOFTF/Shared Documents/MATOFTF/ALEKS/DQ Templates and Instructions/Topic 5 DQ 2/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://gcumail-my.sharepoint.com/personal/richard_ketchersid_gcu_edu/Documents/Course Materials/git/Teaching/144/DQ Templates and Instructions/Topic 5 DQ 2/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{BC8DD8CE-B614-41DD-B719-CB0318BCD400}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{12AA510E-2862-4432-B2CF-9EB1FA17CB08}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="649" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3186,7 +3186,35 @@
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="8">
+  <dxfs count="15">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color rgb="FF00B050"/>
+      </font>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color rgb="FF00B050"/>
+      </font>
+    </dxf>
     <dxf>
       <fill>
         <patternFill>
@@ -3223,11 +3251,18 @@
       </font>
     </dxf>
     <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <color rgb="FF00B050"/>
-      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
     </dxf>
     <dxf>
       <font>
@@ -3242,6 +3277,20 @@
           <bgColor rgb="FFFFFF00"/>
         </patternFill>
       </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color rgb="FF00B050"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color rgb="FF00B050"/>
+      </font>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -4182,7 +4231,7 @@
       <xdr:row>0</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="14497050" cy="8534400"/>
+    <xdr:ext cx="16497300" cy="22479000"/>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
         <xdr:cNvPr id="2" name="TextBox 1">
@@ -4197,7 +4246,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="0" y="0"/>
-          <a:ext cx="14497050" cy="8534400"/>
+          <a:ext cx="16497300" cy="22479000"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -4222,7 +4271,7 @@
       </xdr:style>
       <xdr:txBody>
         <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t">
-          <a:spAutoFit/>
+          <a:noAutofit/>
         </a:bodyPr>
         <a:lstStyle/>
         <a:p>
@@ -6541,7 +6590,7 @@
     <mergeCell ref="N5:S5"/>
   </mergeCells>
   <conditionalFormatting sqref="E5:E7 D11:F21">
-    <cfRule type="expression" dxfId="7" priority="10">
+    <cfRule type="expression" dxfId="6" priority="12">
       <formula>AND(NOT(ISBLANK(D5)),NOT(_xlfn.ISFORMULA(D5)))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -6559,7 +6608,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="expression" priority="1" id="{95EE6F23-0B2C-4FB6-A0DA-4CA5E8A7CDEA}">
+          <x14:cfRule type="expression" priority="11" id="{95EE6F23-0B2C-4FB6-A0DA-4CA5E8A7CDEA}">
             <xm:f>Solution!$D11</xm:f>
             <x14:dxf>
               <font>
@@ -6569,10 +6618,10 @@
               </font>
             </x14:dxf>
           </x14:cfRule>
-          <xm:sqref>D11:F21 G22:H22</xm:sqref>
+          <xm:sqref>D11:F21</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="expression" priority="9" id="{DE6384A9-777C-486F-98B0-332395F82AE2}">
+          <x14:cfRule type="expression" priority="10" id="{DE6384A9-777C-486F-98B0-332395F82AE2}">
             <xm:f>ABS(E5-Solution!E5)&lt;=1</xm:f>
             <x14:dxf>
               <font>
@@ -6585,7 +6634,7 @@
           <xm:sqref>E5:E6</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="expression" priority="8" id="{174487E6-EF19-4EDA-A8E0-E0649208B2BD}">
+          <x14:cfRule type="expression" priority="3" id="{174487E6-EF19-4EDA-A8E0-E0649208B2BD}">
             <xm:f>ABS(E7-Solution!E7)&lt;0.001</xm:f>
             <x14:dxf>
               <font>
@@ -6598,8 +6647,18 @@
           <xm:sqref>E7</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="expression" priority="2" id="{5730DA97-8C32-439D-8C77-E6CF78939293}">
-            <xm:f>Solution!$K28</xm:f>
+          <x14:cfRule type="expression" priority="29" id="{03827A15-B0AA-4B09-A0D4-7D276C8E808E}">
+            <xm:f>AND(NOT(Solution!L$32),NOT(_xlfn.ISFORMULA(G11)),NOT(ISBLANK(G11)))</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill>
+                  <bgColor rgb="FFFFFF00"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <x14:cfRule type="expression" priority="2" id="{246D2ADF-3B33-44BD-B369-436EC59685E8}">
+            <xm:f>Solution!$K36</xm:f>
             <x14:dxf>
               <font>
                 <b/>
@@ -6608,8 +6667,11 @@
               </font>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="expression" priority="13" id="{03827A15-B0AA-4B09-A0D4-7D276C8E808E}">
-            <xm:f>AND(NOT(Solution!K$24),NOT(_xlfn.ISFORMULA(G11)),NOT(ISBLANK(G11)))</xm:f>
+          <xm:sqref>G11:G21</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="expression" priority="23" id="{4E9ED7D7-7D3C-43AB-856B-D39E9D2A4C8F}">
+            <xm:f>AND(NOT(_xlfn.ISFORMULA(H11)),NOT(Solution!Q$31),NOT(ISBLANK(H11)))</xm:f>
             <x14:dxf>
               <fill>
                 <patternFill>
@@ -6618,27 +6680,14 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <xm:sqref>G11:G21</xm:sqref>
-        </x14:conditionalFormatting>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="expression" priority="6" id="{53EF07A5-2F3A-48B4-8702-4D6E46520C43}">
-            <xm:f>Solution!$M29</xm:f>
+          <x14:cfRule type="expression" priority="1" id="{2454C867-EE89-4EA6-B198-26951C41E144}">
+            <xm:f>Solution!$P36</xm:f>
             <x14:dxf>
               <font>
                 <b/>
                 <i val="0"/>
                 <color rgb="FF00B050"/>
               </font>
-            </x14:dxf>
-          </x14:cfRule>
-          <x14:cfRule type="expression" priority="12" id="{4E9ED7D7-7D3C-43AB-856B-D39E9D2A4C8F}">
-            <xm:f>AND(NOT(_xlfn.ISFORMULA(H11)),NOT(Solution!M$24),NOT(ISBLANK(H11)))</xm:f>
-            <x14:dxf>
-              <fill>
-                <patternFill>
-                  <bgColor rgb="FFFFFF00"/>
-                </patternFill>
-              </fill>
             </x14:dxf>
           </x14:cfRule>
           <xm:sqref>H11:H21</xm:sqref>
@@ -7426,14 +7475,6 @@
       <c r="F24" s="144"/>
       <c r="G24" s="144"/>
       <c r="H24" s="145"/>
-      <c r="K24" s="43" t="b">
-        <f ca="1">IFERROR(OR(J25:J27),FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="M24" s="43" t="b">
-        <f ca="1">IFERROR(OR(L25:L28),FALSE)</f>
-        <v>0</v>
-      </c>
       <c r="AK24" s="43">
         <f t="shared" si="1"/>
         <v>1978</v>
@@ -7453,22 +7494,6 @@
       <c r="F25" s="144"/>
       <c r="G25" s="144"/>
       <c r="H25" s="145"/>
-      <c r="J25" s="43" t="e">
-        <f ca="1">SUBSTITUTE(SUBSTITUTE(_xlfn.FORMULATEXT('Water Quality'!G11), " ",""),"$","") = "=FREQUENCY(B:B,E11:E20)"</f>
-        <v>#N/A</v>
-      </c>
-      <c r="K25" s="43" t="b">
-        <f ca="1">IFERROR(OR(J25:J27),FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="L25" s="43" t="e">
-        <f ca="1">SUBSTITUTE(SUBSTITUTE(_xlfn.FORMULATEXT('Water Quality'!H11), " ",""),"$","") = "=G11#/SUM(G11#)"</f>
-        <v>#N/A</v>
-      </c>
-      <c r="M25" s="43" t="b">
-        <f ca="1">IFERROR(OR(L25:L39),FALSE)</f>
-        <v>0</v>
-      </c>
       <c r="AK25" s="43">
         <f t="shared" si="1"/>
         <v>1603</v>
@@ -7488,14 +7513,6 @@
       <c r="F26" s="144"/>
       <c r="G26" s="144"/>
       <c r="H26" s="145"/>
-      <c r="J26" s="43" t="e">
-        <f ca="1">SUBSTITUTE(SUBSTITUTE(_xlfn.FORMULATEXT('Water Quality'!G11), " ",""),"$","") = "=FREQUENCY(B2:B103,E11:E20)"</f>
-        <v>#N/A</v>
-      </c>
-      <c r="L26" s="43" t="e">
-        <f ca="1">SUBSTITUTE(SUBSTITUTE(_xlfn.FORMULATEXT('Water Quality'!H11), " ",""),"$","") = "=G11:G28/SUM(G11:G28)"</f>
-        <v>#N/A</v>
-      </c>
       <c r="AK26" s="43">
         <f t="shared" si="1"/>
         <v>8360</v>
@@ -7515,14 +7532,6 @@
       <c r="F27" s="148"/>
       <c r="G27" s="148"/>
       <c r="H27" s="149"/>
-      <c r="J27" s="43" t="e">
-        <f ca="1">SUBSTITUTE(SUBSTITUTE(_xlfn.FORMULATEXT('Water Quality'!G11), " ",""),"$","") = "=FREQUENCY(Difference_in_water_quality,E11:E20)"</f>
-        <v>#N/A</v>
-      </c>
-      <c r="L27" s="43" t="e">
-        <f ca="1">SUBSTITUTE(SUBSTITUTE(_xlfn.FORMULATEXT('Water Quality'!H11), " ",""),"$","") = "=G11#/102"</f>
-        <v>#N/A</v>
-      </c>
       <c r="AK27" s="43">
         <f t="shared" si="1"/>
         <v>145</v>
@@ -7537,18 +7546,6 @@
         <f>IF(D$2="Your Name Here","Enter Name",ROUND(_xlfn.NORM.INV(Random!D38,20,15),1))</f>
         <v>Enter Name</v>
       </c>
-      <c r="J28" s="43" t="b">
-        <f>'Water Quality'!G11=Solution!G11</f>
-        <v>1</v>
-      </c>
-      <c r="K28" s="43" t="b">
-        <f ca="1">OR(K$25,J28)</f>
-        <v>1</v>
-      </c>
-      <c r="L28" s="43" t="e">
-        <f ca="1">SUBSTITUTE(SUBSTITUTE(_xlfn.FORMULATEXT('Water Quality'!H11), " ",""),"$","") = "=G11:G21/102"</f>
-        <v>#N/A</v>
-      </c>
       <c r="AK28" s="43">
         <f t="shared" si="1"/>
         <v>438</v>
@@ -7570,26 +7567,6 @@
       <c r="F29" s="151"/>
       <c r="G29" s="151"/>
       <c r="H29" s="152"/>
-      <c r="J29" s="43" t="b">
-        <f>'Water Quality'!G12=Solution!G12</f>
-        <v>1</v>
-      </c>
-      <c r="K29" s="43" t="b">
-        <f t="shared" ref="K29:K38" ca="1" si="5">OR(K$25,J29)</f>
-        <v>1</v>
-      </c>
-      <c r="L29" s="43" t="e">
-        <f>'Water Quality'!H11=Solution!H11</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="M29" s="43" t="e">
-        <f>OR(L29,M$25)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="N29" s="43" t="e">
-        <f ca="1">OR(M24,L29)</f>
-        <v>#DIV/0!</v>
-      </c>
       <c r="AK29" s="43">
         <f t="shared" si="1"/>
         <v>8195</v>
@@ -7609,26 +7586,6 @@
       <c r="F30" s="154"/>
       <c r="G30" s="154"/>
       <c r="H30" s="155"/>
-      <c r="J30" s="43" t="b">
-        <f>'Water Quality'!G13=Solution!G13</f>
-        <v>1</v>
-      </c>
-      <c r="K30" s="43" t="b">
-        <f t="shared" ca="1" si="5"/>
-        <v>1</v>
-      </c>
-      <c r="L30" s="43" t="e">
-        <f>'Water Quality'!H12=Solution!H12</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="M30" s="43" t="e">
-        <f t="shared" ref="M30:M39" si="6">OR(L30,M$25)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="N30" s="43" t="e">
-        <f t="shared" ref="N30:N39" ca="1" si="7">OR(M25,L30)</f>
-        <v>#DIV/0!</v>
-      </c>
       <c r="AK30" s="43">
         <f t="shared" si="1"/>
         <v>6420</v>
@@ -7648,25 +7605,9 @@
       <c r="F31" s="154"/>
       <c r="G31" s="154"/>
       <c r="H31" s="155"/>
-      <c r="J31" s="43" t="b">
-        <f>'Water Quality'!G14=Solution!G14</f>
-        <v>1</v>
-      </c>
-      <c r="K31" s="43" t="b">
-        <f t="shared" ca="1" si="5"/>
-        <v>1</v>
-      </c>
-      <c r="L31" s="43" t="e">
-        <f>'Water Quality'!H13=Solution!H13</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="M31" s="43" t="e">
-        <f t="shared" si="6"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="N31" s="43" t="e">
-        <f t="shared" si="7"/>
-        <v>#DIV/0!</v>
+      <c r="Q31" s="43" t="b">
+        <f ca="1">IFERROR(OR(P32:P35),FALSE)</f>
+        <v>0</v>
       </c>
       <c r="AK31" s="43">
         <f t="shared" si="1"/>
@@ -7687,25 +7628,17 @@
       <c r="F32" s="154"/>
       <c r="G32" s="154"/>
       <c r="H32" s="155"/>
-      <c r="J32" s="43" t="b">
-        <f>'Water Quality'!G15=Solution!G15</f>
-        <v>1</v>
-      </c>
-      <c r="K32" s="43" t="b">
-        <f t="shared" ca="1" si="5"/>
-        <v>1</v>
-      </c>
-      <c r="L32" s="43" t="e">
-        <f>'Water Quality'!H14=Solution!H14</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="M32" s="43" t="e">
-        <f t="shared" si="6"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="N32" s="43" t="e">
-        <f t="shared" si="7"/>
-        <v>#DIV/0!</v>
+      <c r="L32" s="43" t="b">
+        <f ca="1">IFERROR(OR(K33:K35),FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="P32" s="43" t="e">
+        <f ca="1">SUBSTITUTE(SUBSTITUTE(_xlfn.FORMULATEXT('Water Quality'!H11), " ",""),"$","") = "=G11#/SUM(G11#)"</f>
+        <v>#N/A</v>
+      </c>
+      <c r="Q32" s="43" t="b">
+        <f ca="1">IFERROR(OR(P32:P46),FALSE)</f>
+        <v>0</v>
       </c>
       <c r="AK32" s="43">
         <f t="shared" si="1"/>
@@ -7726,25 +7659,17 @@
       <c r="F33" s="154"/>
       <c r="G33" s="154"/>
       <c r="H33" s="155"/>
-      <c r="J33" s="43" t="b">
-        <f>'Water Quality'!G16=Solution!G16</f>
-        <v>1</v>
-      </c>
-      <c r="K33" s="43" t="b">
-        <f t="shared" ca="1" si="5"/>
-        <v>1</v>
-      </c>
-      <c r="L33" s="43" t="e">
-        <f>'Water Quality'!H15=Solution!H15</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="M33" s="43" t="e">
-        <f t="shared" si="6"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="N33" s="43" t="e">
-        <f t="shared" si="7"/>
-        <v>#DIV/0!</v>
+      <c r="K33" s="43" t="e">
+        <f ca="1">SUBSTITUTE(SUBSTITUTE(_xlfn.FORMULATEXT('Water Quality'!G11), " ",""),"$","") = "=FREQUENCY(B:B,E11:E20)"</f>
+        <v>#N/A</v>
+      </c>
+      <c r="L33" s="43" t="b">
+        <f ca="1">IFERROR(OR(K33:K35),FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="P33" s="43" t="e">
+        <f ca="1">SUBSTITUTE(SUBSTITUTE(_xlfn.FORMULATEXT('Water Quality'!H11), " ",""),"$","") = "=G11:G28/SUM(G11:G28)"</f>
+        <v>#N/A</v>
       </c>
       <c r="AK33" s="43">
         <f t="shared" si="1"/>
@@ -7765,25 +7690,13 @@
       <c r="F34" s="154"/>
       <c r="G34" s="154"/>
       <c r="H34" s="155"/>
-      <c r="J34" s="43" t="b">
-        <f>'Water Quality'!G17=Solution!G17</f>
-        <v>1</v>
-      </c>
-      <c r="K34" s="43" t="b">
-        <f t="shared" ca="1" si="5"/>
-        <v>1</v>
-      </c>
-      <c r="L34" s="43" t="e">
-        <f>'Water Quality'!H16=Solution!H16</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="M34" s="43" t="e">
-        <f t="shared" si="6"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="N34" s="43" t="e">
-        <f t="shared" si="7"/>
-        <v>#DIV/0!</v>
+      <c r="K34" s="43" t="e">
+        <f ca="1">SUBSTITUTE(SUBSTITUTE(_xlfn.FORMULATEXT('Water Quality'!G11), " ",""),"$","") = "=FREQUENCY(B2:B103,E11:E20)"</f>
+        <v>#N/A</v>
+      </c>
+      <c r="P34" s="43" t="e">
+        <f ca="1">SUBSTITUTE(SUBSTITUTE(_xlfn.FORMULATEXT('Water Quality'!H11), " ",""),"$","") = "=G11#/102"</f>
+        <v>#N/A</v>
       </c>
       <c r="AK34" s="43">
         <f t="shared" si="1"/>
@@ -7804,25 +7717,13 @@
       <c r="F35" s="154"/>
       <c r="G35" s="154"/>
       <c r="H35" s="155"/>
-      <c r="J35" s="43" t="b">
-        <f>'Water Quality'!G18=Solution!G18</f>
-        <v>1</v>
-      </c>
-      <c r="K35" s="43" t="b">
-        <f t="shared" ca="1" si="5"/>
-        <v>1</v>
-      </c>
-      <c r="L35" s="43" t="e">
-        <f>'Water Quality'!H17=Solution!H17</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="M35" s="43" t="e">
-        <f t="shared" si="6"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="N35" s="43" t="e">
-        <f t="shared" si="7"/>
-        <v>#DIV/0!</v>
+      <c r="K35" s="43" t="e">
+        <f ca="1">SUBSTITUTE(SUBSTITUTE(_xlfn.FORMULATEXT('Water Quality'!G11), " ",""),"$","") = "=FREQUENCY(Difference_in_water_quality,E11:E20)"</f>
+        <v>#N/A</v>
+      </c>
+      <c r="P35" s="43" t="e">
+        <f ca="1">SUBSTITUTE(SUBSTITUTE(_xlfn.FORMULATEXT('Water Quality'!H11), " ",""),"$","") = "=G11:G21/102"</f>
+        <v>#N/A</v>
       </c>
       <c r="AK35" s="43">
         <f t="shared" si="1"/>
@@ -7843,24 +7744,28 @@
       <c r="F36" s="154"/>
       <c r="G36" s="154"/>
       <c r="H36" s="155"/>
-      <c r="J36" s="43" t="b">
-        <f>'Water Quality'!G19=Solution!G19</f>
-        <v>1</v>
-      </c>
       <c r="K36" s="43" t="b">
-        <f t="shared" ca="1" si="5"/>
-        <v>1</v>
-      </c>
-      <c r="L36" s="43" t="e">
-        <f>'Water Quality'!H18=Solution!H18</f>
+        <f>'Water Quality'!G11=Solution!G11</f>
+        <v>1</v>
+      </c>
+      <c r="L36" s="43" t="b">
+        <f t="shared" ref="L36:L46" ca="1" si="5">OR(L$33,K36)</f>
+        <v>1</v>
+      </c>
+      <c r="M36" s="43" t="b">
+        <f ca="1">AND(L$32,K36)</f>
+        <v>0</v>
+      </c>
+      <c r="P36" s="43" t="e">
+        <f>'Water Quality'!H11=Solution!H11</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="M36" s="43" t="e">
-        <f t="shared" si="6"/>
+      <c r="Q36" s="43" t="e">
+        <f t="shared" ref="Q36:Q46" si="6">OR(P36,Q$32)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="N36" s="43" t="e">
-        <f t="shared" si="7"/>
+      <c r="R36" s="43" t="e">
+        <f ca="1">AND(Q$31,P36)</f>
         <v>#DIV/0!</v>
       </c>
       <c r="AK36" s="43">
@@ -7882,24 +7787,28 @@
       <c r="F37" s="154"/>
       <c r="G37" s="154"/>
       <c r="H37" s="155"/>
-      <c r="J37" s="43" t="b">
-        <f>'Water Quality'!G20=Solution!G20</f>
-        <v>1</v>
-      </c>
       <c r="K37" s="43" t="b">
+        <f>'Water Quality'!G12=Solution!G12</f>
+        <v>1</v>
+      </c>
+      <c r="L37" s="43" t="b">
         <f t="shared" ca="1" si="5"/>
         <v>1</v>
       </c>
-      <c r="L37" s="43" t="e">
-        <f>'Water Quality'!H19=Solution!H19</f>
+      <c r="M37" s="43" t="b">
+        <f t="shared" ref="M37:M46" ca="1" si="7">AND(L$32,K37)</f>
+        <v>0</v>
+      </c>
+      <c r="P37" s="43" t="e">
+        <f>'Water Quality'!H12=Solution!H12</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="M37" s="43" t="e">
+      <c r="Q37" s="43" t="e">
         <f t="shared" si="6"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="N37" s="43" t="e">
-        <f t="shared" si="7"/>
+      <c r="R37" s="43" t="e">
+        <f t="shared" ref="R37:R46" ca="1" si="8">AND(Q$31,P37)</f>
         <v>#DIV/0!</v>
       </c>
       <c r="AK37" s="43">
@@ -7921,24 +7830,28 @@
       <c r="F38" s="154"/>
       <c r="G38" s="154"/>
       <c r="H38" s="155"/>
-      <c r="J38" s="43" t="b">
-        <f>'Water Quality'!G21=Solution!G21</f>
-        <v>1</v>
-      </c>
       <c r="K38" s="43" t="b">
+        <f>'Water Quality'!G13=Solution!G13</f>
+        <v>1</v>
+      </c>
+      <c r="L38" s="43" t="b">
         <f t="shared" ca="1" si="5"/>
         <v>1</v>
       </c>
-      <c r="L38" s="43" t="e">
-        <f>'Water Quality'!H20=Solution!H20</f>
+      <c r="M38" s="43" t="b">
+        <f t="shared" ca="1" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="P38" s="43" t="e">
+        <f>'Water Quality'!H13=Solution!H13</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="M38" s="43" t="e">
+      <c r="Q38" s="43" t="e">
         <f t="shared" si="6"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="N38" s="43" t="e">
-        <f t="shared" si="7"/>
+      <c r="R38" s="43" t="e">
+        <f t="shared" ca="1" si="8"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AK38" s="43">
@@ -7960,16 +7873,28 @@
       <c r="F39" s="154"/>
       <c r="G39" s="154"/>
       <c r="H39" s="155"/>
-      <c r="L39" s="43" t="e">
-        <f>'Water Quality'!H21=Solution!H21</f>
+      <c r="K39" s="43" t="b">
+        <f>'Water Quality'!G14=Solution!G14</f>
+        <v>1</v>
+      </c>
+      <c r="L39" s="43" t="b">
+        <f t="shared" ca="1" si="5"/>
+        <v>1</v>
+      </c>
+      <c r="M39" s="43" t="b">
+        <f t="shared" ca="1" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="P39" s="43" t="e">
+        <f>'Water Quality'!H14=Solution!H14</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="M39" s="43" t="e">
+      <c r="Q39" s="43" t="e">
         <f t="shared" si="6"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="N39" s="43" t="e">
-        <f t="shared" si="7"/>
+      <c r="R39" s="43" t="e">
+        <f t="shared" ca="1" si="8"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AK39" s="43">
@@ -7991,6 +7916,30 @@
       <c r="F40" s="157"/>
       <c r="G40" s="157"/>
       <c r="H40" s="158"/>
+      <c r="K40" s="43" t="b">
+        <f>'Water Quality'!G15=Solution!G15</f>
+        <v>1</v>
+      </c>
+      <c r="L40" s="43" t="b">
+        <f t="shared" ca="1" si="5"/>
+        <v>1</v>
+      </c>
+      <c r="M40" s="43" t="b">
+        <f t="shared" ca="1" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="P40" s="43" t="e">
+        <f>'Water Quality'!H15=Solution!H15</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="Q40" s="43" t="e">
+        <f t="shared" si="6"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="R40" s="43" t="e">
+        <f t="shared" ca="1" si="8"/>
+        <v>#DIV/0!</v>
+      </c>
       <c r="AK40" s="43">
         <f t="shared" si="1"/>
         <v>4006</v>
@@ -8005,6 +7954,30 @@
         <f>IF(D$2="Your Name Here","Enter Name",ROUND(_xlfn.NORM.INV(Random!D51,20,15),1))</f>
         <v>Enter Name</v>
       </c>
+      <c r="K41" s="43" t="b">
+        <f>'Water Quality'!G16=Solution!G16</f>
+        <v>1</v>
+      </c>
+      <c r="L41" s="43" t="b">
+        <f t="shared" ca="1" si="5"/>
+        <v>1</v>
+      </c>
+      <c r="M41" s="43" t="b">
+        <f t="shared" ca="1" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="P41" s="43" t="e">
+        <f>'Water Quality'!H16=Solution!H16</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="Q41" s="43" t="e">
+        <f t="shared" si="6"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="R41" s="43" t="e">
+        <f t="shared" ca="1" si="8"/>
+        <v>#DIV/0!</v>
+      </c>
       <c r="AK41" s="43">
         <f t="shared" si="1"/>
         <v>355</v>
@@ -8019,6 +7992,30 @@
         <f>IF(D$2="Your Name Here","Enter Name",ROUND(_xlfn.NORM.INV(Random!D52,20,15),1))</f>
         <v>Enter Name</v>
       </c>
+      <c r="K42" s="43" t="b">
+        <f>'Water Quality'!G17=Solution!G17</f>
+        <v>1</v>
+      </c>
+      <c r="L42" s="43" t="b">
+        <f t="shared" ca="1" si="5"/>
+        <v>1</v>
+      </c>
+      <c r="M42" s="43" t="b">
+        <f t="shared" ca="1" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="P42" s="43" t="e">
+        <f>'Water Quality'!H17=Solution!H17</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="Q42" s="43" t="e">
+        <f t="shared" si="6"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="R42" s="43" t="e">
+        <f t="shared" ca="1" si="8"/>
+        <v>#DIV/0!</v>
+      </c>
       <c r="AK42" s="43">
         <f t="shared" si="1"/>
         <v>9128</v>
@@ -8033,6 +8030,30 @@
         <f>IF(D$2="Your Name Here","Enter Name",ROUND(_xlfn.NORM.INV(Random!D53,20,15),1))</f>
         <v>Enter Name</v>
       </c>
+      <c r="K43" s="43" t="b">
+        <f>'Water Quality'!G18=Solution!G18</f>
+        <v>1</v>
+      </c>
+      <c r="L43" s="43" t="b">
+        <f t="shared" ca="1" si="5"/>
+        <v>1</v>
+      </c>
+      <c r="M43" s="43" t="b">
+        <f t="shared" ca="1" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="P43" s="43" t="e">
+        <f>'Water Quality'!H18=Solution!H18</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="Q43" s="43" t="e">
+        <f t="shared" si="6"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="R43" s="43" t="e">
+        <f t="shared" ca="1" si="8"/>
+        <v>#DIV/0!</v>
+      </c>
       <c r="AK43" s="43">
         <f t="shared" si="1"/>
         <v>1789</v>
@@ -8047,6 +8068,30 @@
         <f>IF(D$2="Your Name Here","Enter Name",ROUND(_xlfn.NORM.INV(Random!D54,20,15),1))</f>
         <v>Enter Name</v>
       </c>
+      <c r="K44" s="43" t="b">
+        <f>'Water Quality'!G19=Solution!G19</f>
+        <v>1</v>
+      </c>
+      <c r="L44" s="43" t="b">
+        <f t="shared" ca="1" si="5"/>
+        <v>1</v>
+      </c>
+      <c r="M44" s="43" t="b">
+        <f t="shared" ca="1" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="P44" s="43" t="e">
+        <f>'Water Quality'!H19=Solution!H19</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="Q44" s="43" t="e">
+        <f t="shared" si="6"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="R44" s="43" t="e">
+        <f t="shared" ca="1" si="8"/>
+        <v>#DIV/0!</v>
+      </c>
       <c r="AK44" s="43">
         <f t="shared" si="1"/>
         <v>2954</v>
@@ -8061,6 +8106,30 @@
         <f>IF(D$2="Your Name Here","Enter Name",ROUND(_xlfn.NORM.INV(Random!D55,20,15),1))</f>
         <v>Enter Name</v>
       </c>
+      <c r="K45" s="43" t="b">
+        <f>'Water Quality'!G20=Solution!G20</f>
+        <v>1</v>
+      </c>
+      <c r="L45" s="43" t="b">
+        <f t="shared" ca="1" si="5"/>
+        <v>1</v>
+      </c>
+      <c r="M45" s="43" t="b">
+        <f t="shared" ca="1" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="P45" s="43" t="e">
+        <f>'Water Quality'!H20=Solution!H20</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="Q45" s="43" t="e">
+        <f t="shared" si="6"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="R45" s="43" t="e">
+        <f t="shared" ca="1" si="8"/>
+        <v>#DIV/0!</v>
+      </c>
       <c r="AK45" s="43">
         <f t="shared" si="1"/>
         <v>3119</v>
@@ -8075,6 +8144,30 @@
         <f>IF(D$2="Your Name Here","Enter Name",ROUND(_xlfn.NORM.INV(Random!D56,20,15),1))</f>
         <v>Enter Name</v>
       </c>
+      <c r="K46" s="43" t="b">
+        <f>'Water Quality'!G21=Solution!G21</f>
+        <v>1</v>
+      </c>
+      <c r="L46" s="43" t="b">
+        <f t="shared" ca="1" si="5"/>
+        <v>1</v>
+      </c>
+      <c r="M46" s="43" t="b">
+        <f t="shared" ca="1" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="P46" s="43" t="e">
+        <f>'Water Quality'!H21=Solution!H21</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="Q46" s="43" t="e">
+        <f t="shared" si="6"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="R46" s="43" t="e">
+        <f t="shared" ca="1" si="8"/>
+        <v>#DIV/0!</v>
+      </c>
       <c r="AK46" s="43">
         <f t="shared" si="1"/>
         <v>6016</v>
@@ -8376,7 +8469,7 @@
     </row>
     <row r="68" spans="1:37">
       <c r="A68" s="46">
-        <f t="shared" ref="A68:A103" si="8">A67+1</f>
+        <f t="shared" ref="A68:A103" si="9">A67+1</f>
         <v>67</v>
       </c>
       <c r="B68" s="46" t="str">
@@ -8384,13 +8477,13 @@
         <v>Enter Name</v>
       </c>
       <c r="AK68" s="43">
-        <f t="shared" ref="AK68:AK103" si="9">MOD(AK67*1103515245 + 12345,9172)</f>
+        <f t="shared" ref="AK68:AK103" si="10">MOD(AK67*1103515245 + 12345,9172)</f>
         <v>8390</v>
       </c>
     </row>
     <row r="69" spans="1:37">
       <c r="A69" s="46">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>68</v>
       </c>
       <c r="B69" s="46" t="str">
@@ -8398,13 +8491,13 @@
         <v>Enter Name</v>
       </c>
       <c r="AK69" s="43">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>4007</v>
       </c>
     </row>
     <row r="70" spans="1:37">
       <c r="A70" s="46">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>69</v>
       </c>
       <c r="B70" s="46" t="str">
@@ -8412,13 +8505,13 @@
         <v>Enter Name</v>
       </c>
       <c r="AK70" s="43">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>4764</v>
       </c>
     </row>
     <row r="71" spans="1:37">
       <c r="A71" s="46">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>70</v>
       </c>
       <c r="B71" s="46" t="str">
@@ -8426,13 +8519,13 @@
         <v>Enter Name</v>
       </c>
       <c r="AK71" s="43">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>3769</v>
       </c>
     </row>
     <row r="72" spans="1:37">
       <c r="A72" s="46">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>71</v>
       </c>
       <c r="B72" s="46" t="str">
@@ -8440,13 +8533,13 @@
         <v>Enter Name</v>
       </c>
       <c r="AK72" s="43">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>1030</v>
       </c>
     </row>
     <row r="73" spans="1:37">
       <c r="A73" s="46">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>72</v>
       </c>
       <c r="B73" s="46" t="str">
@@ -8454,13 +8547,13 @@
         <v>Enter Name</v>
       </c>
       <c r="AK73" s="43">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>4303</v>
       </c>
     </row>
     <row r="74" spans="1:37">
       <c r="A74" s="46">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>73</v>
       </c>
       <c r="B74" s="46" t="str">
@@ -8468,13 +8561,13 @@
         <v>Enter Name</v>
       </c>
       <c r="AK74" s="43">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>7404</v>
       </c>
     </row>
     <row r="75" spans="1:37">
       <c r="A75" s="46">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>74</v>
       </c>
       <c r="B75" s="46" t="str">
@@ -8482,13 +8575,13 @@
         <v>Enter Name</v>
       </c>
       <c r="AK75" s="43">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>4261</v>
       </c>
     </row>
     <row r="76" spans="1:37">
       <c r="A76" s="46">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>75</v>
       </c>
       <c r="B76" s="46" t="str">
@@ -8496,13 +8589,13 @@
         <v>Enter Name</v>
       </c>
       <c r="AK76" s="43">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>5666</v>
       </c>
     </row>
     <row r="77" spans="1:37">
       <c r="A77" s="46">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>76</v>
       </c>
       <c r="B77" s="46" t="str">
@@ -8510,13 +8603,13 @@
         <v>Enter Name</v>
       </c>
       <c r="AK77" s="43">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>39</v>
       </c>
     </row>
     <row r="78" spans="1:37">
       <c r="A78" s="46">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>77</v>
       </c>
       <c r="B78" s="46" t="str">
@@ -8524,13 +8617,13 @@
         <v>Enter Name</v>
       </c>
       <c r="AK78" s="43">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>856</v>
       </c>
     </row>
     <row r="79" spans="1:37">
       <c r="A79" s="46">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>78</v>
       </c>
       <c r="B79" s="46" t="str">
@@ -8538,13 +8631,13 @@
         <v>Enter Name</v>
       </c>
       <c r="AK79" s="43">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>7585</v>
       </c>
     </row>
     <row r="80" spans="1:37">
       <c r="A80" s="46">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>79</v>
       </c>
       <c r="B80" s="46" t="str">
@@ -8552,13 +8645,13 @@
         <v>Enter Name</v>
       </c>
       <c r="AK80" s="43">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>4326</v>
       </c>
     </row>
     <row r="81" spans="1:37">
       <c r="A81" s="46">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>80</v>
       </c>
       <c r="B81" s="46" t="str">
@@ -8566,13 +8659,13 @@
         <v>Enter Name</v>
       </c>
       <c r="AK81" s="43">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>7919</v>
       </c>
     </row>
     <row r="82" spans="1:37">
       <c r="A82" s="46">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>81</v>
       </c>
       <c r="B82" s="46" t="str">
@@ -8580,13 +8673,13 @@
         <v>Enter Name</v>
       </c>
       <c r="AK82" s="43">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>240</v>
       </c>
     </row>
     <row r="83" spans="1:37">
       <c r="A83" s="46">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>82</v>
       </c>
       <c r="B83" s="46" t="str">
@@ -8594,13 +8687,13 @@
         <v>Enter Name</v>
       </c>
       <c r="AK83" s="43">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>6553</v>
       </c>
     </row>
     <row r="84" spans="1:37">
       <c r="A84" s="46">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>83</v>
       </c>
       <c r="B84" s="46" t="str">
@@ -8608,13 +8701,13 @@
         <v>Enter Name</v>
       </c>
       <c r="AK84" s="43">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>3550</v>
       </c>
     </row>
     <row r="85" spans="1:37">
       <c r="A85" s="46">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>84</v>
       </c>
       <c r="B85" s="46" t="str">
@@ -8622,13 +8715,13 @@
         <v>Enter Name</v>
       </c>
       <c r="AK85" s="43">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>7691</v>
       </c>
     </row>
     <row r="86" spans="1:37">
       <c r="A86" s="46">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>85</v>
       </c>
       <c r="B86" s="46" t="str">
@@ -8636,13 +8729,13 @@
         <v>Enter Name</v>
       </c>
       <c r="AK86" s="43">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>3908</v>
       </c>
     </row>
     <row r="87" spans="1:37">
       <c r="A87" s="46">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>86</v>
       </c>
       <c r="B87" s="46" t="str">
@@ -8650,13 +8743,13 @@
         <v>Enter Name</v>
       </c>
       <c r="AK87" s="43">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>8529</v>
       </c>
     </row>
     <row r="88" spans="1:37">
       <c r="A88" s="46">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>87</v>
       </c>
       <c r="B88" s="46" t="str">
@@ -8664,13 +8757,13 @@
         <v>Enter Name</v>
       </c>
       <c r="AK88" s="43">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>2334</v>
       </c>
     </row>
     <row r="89" spans="1:37">
       <c r="A89" s="46">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>88</v>
       </c>
       <c r="B89" s="46" t="str">
@@ -8678,13 +8771,13 @@
         <v>Enter Name</v>
       </c>
       <c r="AK89" s="43">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>2795</v>
       </c>
     </row>
     <row r="90" spans="1:37">
       <c r="A90" s="46">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>89</v>
       </c>
       <c r="B90" s="46" t="str">
@@ -8692,13 +8785,13 @@
         <v>Enter Name</v>
       </c>
       <c r="AK90" s="43">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>8332</v>
       </c>
     </row>
     <row r="91" spans="1:37">
       <c r="A91" s="46">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>90</v>
       </c>
       <c r="B91" s="46" t="str">
@@ -8706,13 +8799,13 @@
         <v>Enter Name</v>
       </c>
       <c r="AK91" s="43">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>5101</v>
       </c>
     </row>
     <row r="92" spans="1:37">
       <c r="A92" s="46">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>91</v>
       </c>
       <c r="B92" s="46" t="str">
@@ -8720,13 +8813,13 @@
         <v>Enter Name</v>
       </c>
       <c r="AK92" s="43">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>3738</v>
       </c>
     </row>
     <row r="93" spans="1:37">
       <c r="A93" s="46">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>92</v>
       </c>
       <c r="B93" s="46" t="str">
@@ -8734,13 +8827,13 @@
         <v>Enter Name</v>
       </c>
       <c r="AK93" s="43">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>1931</v>
       </c>
     </row>
     <row r="94" spans="1:37">
       <c r="A94" s="46">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>93</v>
       </c>
       <c r="B94" s="46" t="str">
@@ -8748,13 +8841,13 @@
         <v>Enter Name</v>
       </c>
       <c r="AK94" s="43">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>5336</v>
       </c>
     </row>
     <row r="95" spans="1:37">
       <c r="A95" s="46">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>94</v>
       </c>
       <c r="B95" s="46" t="str">
@@ -8762,13 +8855,13 @@
         <v>Enter Name</v>
       </c>
       <c r="AK95" s="43">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>3417</v>
       </c>
     </row>
     <row r="96" spans="1:37">
       <c r="A96" s="46">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>95</v>
       </c>
       <c r="B96" s="46" t="str">
@@ -8776,13 +8869,13 @@
         <v>Enter Name</v>
       </c>
       <c r="AK96" s="43">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>8302</v>
       </c>
     </row>
     <row r="97" spans="1:37">
       <c r="A97" s="46">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>96</v>
       </c>
       <c r="B97" s="46" t="str">
@@ -8790,13 +8883,13 @@
         <v>Enter Name</v>
       </c>
       <c r="AK97" s="43">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>1239</v>
       </c>
     </row>
     <row r="98" spans="1:37">
       <c r="A98" s="46">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>97</v>
       </c>
       <c r="B98" s="46" t="str">
@@ -8804,13 +8897,13 @@
         <v>Enter Name</v>
       </c>
       <c r="AK98" s="43">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>8584</v>
       </c>
     </row>
     <row r="99" spans="1:37">
       <c r="A99" s="46">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>98</v>
       </c>
       <c r="B99" s="46" t="str">
@@ -8818,13 +8911,13 @@
         <v>Enter Name</v>
       </c>
       <c r="AK99" s="43">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>6357</v>
       </c>
     </row>
     <row r="100" spans="1:37">
       <c r="A100" s="46">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>99</v>
       </c>
       <c r="B100" s="46" t="str">
@@ -8832,13 +8925,13 @@
         <v>Enter Name</v>
       </c>
       <c r="AK100" s="43">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>1554</v>
       </c>
     </row>
     <row r="101" spans="1:37">
       <c r="A101" s="46">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>100</v>
       </c>
       <c r="B101" s="46" t="str">
@@ -8846,13 +8939,13 @@
         <v>Enter Name</v>
       </c>
       <c r="AK101" s="43">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>3275</v>
       </c>
     </row>
     <row r="102" spans="1:37">
       <c r="A102" s="46">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>101</v>
       </c>
       <c r="B102" s="46" t="str">
@@ -8860,13 +8953,13 @@
         <v>Enter Name</v>
       </c>
       <c r="AK102" s="43">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>5920</v>
       </c>
     </row>
     <row r="103" spans="1:37">
       <c r="A103" s="46">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>102</v>
       </c>
       <c r="B103" s="46" t="str">
@@ -8874,12 +8967,12 @@
         <v>Enter Name</v>
       </c>
       <c r="AK103" s="43">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>941</v>
       </c>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="xOM/K2RcEa/ZsVodp6AguBuaIOQLaQZWOPEUpcZZZMsBEr9nO/f+NhduI/zL+S8KAiYEG7A6P1lBa3WRuWnO4Q==" saltValue="k1wOCDh8L5NZ9dnEv0+uWQ==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="2lm+KzlfhBBr/oqMv6QFd1DRMVKg4lvdlQU9TfWvAf8oMfVAmia3Xj8EmGsuo2yD4WGbP1hPcIkVVhxKrjyOqA==" saltValue="1HQzKTEeJ8xP3itMRDb9IQ==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
   <mergeCells count="9">
     <mergeCell ref="J10:O23"/>
     <mergeCell ref="D24:H27"/>
@@ -19389,199 +19482,199 @@
     <row r="2" spans="1:1">
       <c r="A2" s="3">
         <f ca="1">ROUND(NORMINV(RAND(),68,3.75),1)</f>
-        <v>69.3</v>
+        <v>61.5</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="3">
         <f t="shared" ref="A3:A66" ca="1" si="0">ROUND(NORMINV(RAND(),68,3.75),1)</f>
-        <v>64.599999999999994</v>
+        <v>71.099999999999994</v>
       </c>
     </row>
     <row r="4" spans="1:1">
       <c r="A4" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>67.400000000000006</v>
+        <v>68.400000000000006</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>65.2</v>
+        <v>69.099999999999994</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>67.3</v>
+        <v>73.400000000000006</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>61.7</v>
+        <v>67</v>
       </c>
     </row>
     <row r="8" spans="1:1">
       <c r="A8" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>62.2</v>
+        <v>70.7</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>65.7</v>
+        <v>69.8</v>
       </c>
     </row>
     <row r="10" spans="1:1">
       <c r="A10" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>65.5</v>
+        <v>71.099999999999994</v>
       </c>
     </row>
     <row r="11" spans="1:1">
       <c r="A11" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>68.400000000000006</v>
+        <v>73.7</v>
       </c>
     </row>
     <row r="12" spans="1:1">
       <c r="A12" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>65.7</v>
+        <v>65.5</v>
       </c>
     </row>
     <row r="13" spans="1:1">
       <c r="A13" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>68.7</v>
+        <v>62.7</v>
       </c>
     </row>
     <row r="14" spans="1:1">
       <c r="A14" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>61.6</v>
+        <v>65.7</v>
       </c>
     </row>
     <row r="15" spans="1:1">
       <c r="A15" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>64.099999999999994</v>
+        <v>67.900000000000006</v>
       </c>
     </row>
     <row r="16" spans="1:1">
       <c r="A16" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>67.400000000000006</v>
+        <v>69.3</v>
       </c>
     </row>
     <row r="17" spans="1:1">
       <c r="A17" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>69.400000000000006</v>
+        <v>67.599999999999994</v>
       </c>
     </row>
     <row r="18" spans="1:1">
       <c r="A18" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>68.599999999999994</v>
+        <v>64.099999999999994</v>
       </c>
     </row>
     <row r="19" spans="1:1">
       <c r="A19" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>66.400000000000006</v>
+        <v>69.7</v>
       </c>
     </row>
     <row r="20" spans="1:1">
       <c r="A20" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>67.2</v>
+        <v>69.5</v>
       </c>
     </row>
     <row r="21" spans="1:1">
       <c r="A21" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>66.099999999999994</v>
+        <v>71.400000000000006</v>
       </c>
     </row>
     <row r="22" spans="1:1">
       <c r="A22" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>64.7</v>
+        <v>68.099999999999994</v>
       </c>
     </row>
     <row r="23" spans="1:1">
       <c r="A23" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>72.5</v>
+        <v>64.599999999999994</v>
       </c>
     </row>
     <row r="24" spans="1:1">
       <c r="A24" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>61.9</v>
+        <v>72.599999999999994</v>
       </c>
     </row>
     <row r="25" spans="1:1">
       <c r="A25" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>74.7</v>
+        <v>67.400000000000006</v>
       </c>
     </row>
     <row r="26" spans="1:1">
       <c r="A26" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>68</v>
+        <v>64.900000000000006</v>
       </c>
     </row>
     <row r="27" spans="1:1">
       <c r="A27" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>67.900000000000006</v>
+        <v>66.8</v>
       </c>
     </row>
     <row r="28" spans="1:1">
       <c r="A28" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>69.3</v>
+        <v>64.5</v>
       </c>
     </row>
     <row r="29" spans="1:1">
       <c r="A29" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>68.3</v>
+        <v>70.2</v>
       </c>
     </row>
     <row r="30" spans="1:1">
       <c r="A30" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>59.3</v>
+        <v>69.2</v>
       </c>
     </row>
     <row r="31" spans="1:1">
       <c r="A31" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>60.9</v>
+        <v>67.099999999999994</v>
       </c>
     </row>
     <row r="32" spans="1:1">
       <c r="A32" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>69.599999999999994</v>
+        <v>68.8</v>
       </c>
     </row>
     <row r="33" spans="1:1">
       <c r="A33" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>70.8</v>
+        <v>65.2</v>
       </c>
     </row>
     <row r="34" spans="1:1">
       <c r="A34" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>59.8</v>
+        <v>58.9</v>
       </c>
     </row>
     <row r="35" spans="1:1">
@@ -19593,409 +19686,409 @@
     <row r="36" spans="1:1">
       <c r="A36" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>70</v>
+        <v>63.2</v>
       </c>
     </row>
     <row r="37" spans="1:1">
       <c r="A37" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>65.8</v>
+        <v>69.5</v>
       </c>
     </row>
     <row r="38" spans="1:1">
       <c r="A38" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>69.3</v>
+        <v>73.8</v>
       </c>
     </row>
     <row r="39" spans="1:1">
       <c r="A39" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>69.7</v>
+        <v>69.400000000000006</v>
       </c>
     </row>
     <row r="40" spans="1:1">
       <c r="A40" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>70.400000000000006</v>
+        <v>72.3</v>
       </c>
     </row>
     <row r="41" spans="1:1">
       <c r="A41" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>66.5</v>
+        <v>72.8</v>
       </c>
     </row>
     <row r="42" spans="1:1">
       <c r="A42" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>72.8</v>
+        <v>66.900000000000006</v>
       </c>
     </row>
     <row r="43" spans="1:1">
       <c r="A43" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>66.3</v>
+        <v>65.900000000000006</v>
       </c>
     </row>
     <row r="44" spans="1:1">
       <c r="A44" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>75</v>
+        <v>64.7</v>
       </c>
     </row>
     <row r="45" spans="1:1">
       <c r="A45" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>72.2</v>
+        <v>61.4</v>
       </c>
     </row>
     <row r="46" spans="1:1">
       <c r="A46" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>75.3</v>
+        <v>67.5</v>
       </c>
     </row>
     <row r="47" spans="1:1">
       <c r="A47" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>62.2</v>
+        <v>68.099999999999994</v>
       </c>
     </row>
     <row r="48" spans="1:1">
       <c r="A48" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>68</v>
+        <v>68.8</v>
       </c>
     </row>
     <row r="49" spans="1:1">
       <c r="A49" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>63.8</v>
+        <v>73.2</v>
       </c>
     </row>
     <row r="50" spans="1:1">
       <c r="A50" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>67.5</v>
+        <v>66</v>
       </c>
     </row>
     <row r="51" spans="1:1">
       <c r="A51" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>68.900000000000006</v>
+        <v>66.3</v>
       </c>
     </row>
     <row r="52" spans="1:1">
       <c r="A52" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>69.8</v>
+        <v>65</v>
       </c>
     </row>
     <row r="53" spans="1:1">
       <c r="A53" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>67.8</v>
+        <v>66.900000000000006</v>
       </c>
     </row>
     <row r="54" spans="1:1">
       <c r="A54" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>64.3</v>
+        <v>65.599999999999994</v>
       </c>
     </row>
     <row r="55" spans="1:1">
       <c r="A55" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>70.400000000000006</v>
+        <v>67.5</v>
       </c>
     </row>
     <row r="56" spans="1:1">
       <c r="A56" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>76.400000000000006</v>
+        <v>70.900000000000006</v>
       </c>
     </row>
     <row r="57" spans="1:1">
       <c r="A57" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>70.8</v>
+        <v>68.400000000000006</v>
       </c>
     </row>
     <row r="58" spans="1:1">
       <c r="A58" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>70.3</v>
+        <v>69.900000000000006</v>
       </c>
     </row>
     <row r="59" spans="1:1">
       <c r="A59" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>63.2</v>
+        <v>63.9</v>
       </c>
     </row>
     <row r="60" spans="1:1">
       <c r="A60" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>69.400000000000006</v>
+        <v>60.2</v>
       </c>
     </row>
     <row r="61" spans="1:1">
       <c r="A61" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>69.7</v>
+        <v>65.7</v>
       </c>
     </row>
     <row r="62" spans="1:1">
       <c r="A62" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>72.2</v>
+        <v>63.3</v>
       </c>
     </row>
     <row r="63" spans="1:1">
       <c r="A63" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>69.3</v>
+        <v>75.8</v>
       </c>
     </row>
     <row r="64" spans="1:1">
       <c r="A64" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>69.5</v>
+        <v>68.400000000000006</v>
       </c>
     </row>
     <row r="65" spans="1:1">
       <c r="A65" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>69.5</v>
+        <v>60.3</v>
       </c>
     </row>
     <row r="66" spans="1:1">
       <c r="A66" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>63.6</v>
+        <v>70.5</v>
       </c>
     </row>
     <row r="67" spans="1:1">
       <c r="A67" s="3">
         <f t="shared" ref="A67:A103" ca="1" si="1">ROUND(NORMINV(RAND(),68,3.75),1)</f>
-        <v>71.3</v>
+        <v>68.3</v>
       </c>
     </row>
     <row r="68" spans="1:1">
       <c r="A68" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>69</v>
+        <v>62.8</v>
       </c>
     </row>
     <row r="69" spans="1:1">
       <c r="A69" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>72.599999999999994</v>
+        <v>67</v>
       </c>
     </row>
     <row r="70" spans="1:1">
       <c r="A70" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>73.900000000000006</v>
+        <v>68</v>
       </c>
     </row>
     <row r="71" spans="1:1">
       <c r="A71" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>64.5</v>
+        <v>67.8</v>
       </c>
     </row>
     <row r="72" spans="1:1">
       <c r="A72" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>69.8</v>
+        <v>71.400000000000006</v>
       </c>
     </row>
     <row r="73" spans="1:1">
       <c r="A73" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>65.8</v>
+        <v>62.9</v>
       </c>
     </row>
     <row r="74" spans="1:1">
       <c r="A74" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>65.3</v>
+        <v>73</v>
       </c>
     </row>
     <row r="75" spans="1:1">
       <c r="A75" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>69.2</v>
+        <v>69.3</v>
       </c>
     </row>
     <row r="76" spans="1:1">
       <c r="A76" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>66.7</v>
+        <v>65.5</v>
       </c>
     </row>
     <row r="77" spans="1:1">
       <c r="A77" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>71.900000000000006</v>
+        <v>62.8</v>
       </c>
     </row>
     <row r="78" spans="1:1">
       <c r="A78" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>73.7</v>
+        <v>62.1</v>
       </c>
     </row>
     <row r="79" spans="1:1">
       <c r="A79" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>67.3</v>
+        <v>66.3</v>
       </c>
     </row>
     <row r="80" spans="1:1">
       <c r="A80" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>71</v>
+        <v>73.599999999999994</v>
       </c>
     </row>
     <row r="81" spans="1:1">
       <c r="A81" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>63.2</v>
+        <v>65.3</v>
       </c>
     </row>
     <row r="82" spans="1:1">
       <c r="A82" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>66.400000000000006</v>
+        <v>77.3</v>
       </c>
     </row>
     <row r="83" spans="1:1">
       <c r="A83" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>71.3</v>
+        <v>66.3</v>
       </c>
     </row>
     <row r="84" spans="1:1">
       <c r="A84" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>71.099999999999994</v>
+        <v>72.5</v>
       </c>
     </row>
     <row r="85" spans="1:1">
       <c r="A85" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>60.2</v>
+        <v>73.599999999999994</v>
       </c>
     </row>
     <row r="86" spans="1:1">
       <c r="A86" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>66.900000000000006</v>
+        <v>67.7</v>
       </c>
     </row>
     <row r="87" spans="1:1">
       <c r="A87" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>66.400000000000006</v>
+        <v>69.2</v>
       </c>
     </row>
     <row r="88" spans="1:1">
       <c r="A88" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>66.7</v>
+        <v>64.599999999999994</v>
       </c>
     </row>
     <row r="89" spans="1:1">
       <c r="A89" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>72.3</v>
+        <v>66.8</v>
       </c>
     </row>
     <row r="90" spans="1:1">
       <c r="A90" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>65.099999999999994</v>
+        <v>69.5</v>
       </c>
     </row>
     <row r="91" spans="1:1">
       <c r="A91" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>66.900000000000006</v>
+        <v>63.6</v>
       </c>
     </row>
     <row r="92" spans="1:1">
       <c r="A92" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>68.400000000000006</v>
+        <v>69</v>
       </c>
     </row>
     <row r="93" spans="1:1">
       <c r="A93" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>65.599999999999994</v>
+        <v>66.8</v>
       </c>
     </row>
     <row r="94" spans="1:1">
       <c r="A94" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>67.2</v>
+        <v>62.6</v>
       </c>
     </row>
     <row r="95" spans="1:1">
       <c r="A95" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>68.900000000000006</v>
+        <v>61</v>
       </c>
     </row>
     <row r="96" spans="1:1">
       <c r="A96" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>71.900000000000006</v>
+        <v>65.900000000000006</v>
       </c>
     </row>
     <row r="97" spans="1:1">
       <c r="A97" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>58.5</v>
+        <v>68.599999999999994</v>
       </c>
     </row>
     <row r="98" spans="1:1">
       <c r="A98" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>67.5</v>
+        <v>66.099999999999994</v>
       </c>
     </row>
     <row r="99" spans="1:1">
       <c r="A99" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>58.2</v>
+        <v>65.400000000000006</v>
       </c>
     </row>
     <row r="100" spans="1:1">
       <c r="A100" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>65.2</v>
+        <v>69.5</v>
       </c>
     </row>
     <row r="101" spans="1:1">
       <c r="A101" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>74.2</v>
+        <v>71.8</v>
       </c>
     </row>
     <row r="102" spans="1:1">
       <c r="A102" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>64.900000000000006</v>
+        <v>69</v>
       </c>
     </row>
     <row r="103" spans="1:1">
       <c r="A103" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>64.8</v>
+        <v>67.900000000000006</v>
       </c>
     </row>
   </sheetData>
@@ -20098,6 +20191,15 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <lcf76f155ced4ddcb4097134ff3c332f xmlns="cca9fd2d-ef84-45c9-8063-8f4bd4c29606">
@@ -20107,7 +20209,7 @@
 </p:properties>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101002C289946819CFF499E91D197BC975371" ma:contentTypeVersion="13" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="674b7a4e239a9748c7aaa97e309327a4">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="cca9fd2d-ef84-45c9-8063-8f4bd4c29606" xmlns:ns3="18557d39-01b8-4d71-9479-3fad465290ae" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="600253478e594d1349e02792803dc53a" ns2:_="" ns3:_="">
     <xsd:import namespace="cca9fd2d-ef84-45c9-8063-8f4bd4c29606"/>
@@ -20324,16 +20426,15 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{17F1EF20-95AB-4016-A693-6625F3A67214}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{924A8F3D-57F5-4941-A32A-55B7F7F7AF07}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
@@ -20343,7 +20444,7 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8F527DFD-99D6-4A6C-AC9B-EC23CCFE992B}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -20360,12 +20461,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{17F1EF20-95AB-4016-A693-6625F3A67214}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/144/DQ Templates and Instructions/Topic 5 DQ 2/Topic 5 DQ 2.xlsx
+++ b/144/DQ Templates and Instructions/Topic 5 DQ 2/Topic 5 DQ 2.xlsx
@@ -5,10 +5,10 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://gcumail-my.sharepoint.com/personal/richard_ketchersid_gcu_edu/Documents/Course Materials/git/Teaching/144/DQ Templates and Instructions/Topic 5 DQ 2/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://gcumail.sharepoint.com/sites/MathematicsProgramFacultyStaff-MATOFTF/Shared Documents/MATOFTF/ALEKS/DQ Templates and Instructions/Topic 5 DQ 2/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{12AA510E-2862-4432-B2CF-9EB1FA17CB08}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="10" documentId="8_{46C128A8-172E-4984-BBC3-77234BE2C9F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D338C630-11E0-41E6-A46A-5F84BCDDE0F7}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="649" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -119,7 +119,7 @@
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
   <metadataTypes count="1">
     <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
   </metadataTypes>
@@ -2811,6 +2811,61 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="43" xfId="0" applyBorder="1" applyProtection="1">
       <protection hidden="1"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
       <protection hidden="1"/>
@@ -2971,33 +3026,6 @@
       <alignment horizontal="center" vertical="center"/>
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
       <protection hidden="1"/>
@@ -3153,40 +3181,12 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="15">
+  <dxfs count="8">
     <dxf>
       <fill>
         <patternFill>
@@ -3214,55 +3214,6 @@
         <i val="0"/>
         <color rgb="FF00B050"/>
       </font>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <color rgb="FF00B050"/>
-      </font>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <color rgb="FF00B050"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <color rgb="FF00B050"/>
-      </font>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
     </dxf>
     <dxf>
       <font>
@@ -4628,56 +4579,56 @@
       <c r="B3" s="15" t="s">
         <v>0</v>
       </c>
-      <c r="D3" s="124" t="s">
-        <v>1</v>
-      </c>
-      <c r="E3" s="125"/>
-      <c r="F3" s="125"/>
-      <c r="G3" s="125"/>
-      <c r="H3" s="125"/>
-      <c r="I3" s="126"/>
+      <c r="D3" s="91" t="s">
+        <v>1</v>
+      </c>
+      <c r="E3" s="92"/>
+      <c r="F3" s="92"/>
+      <c r="G3" s="92"/>
+      <c r="H3" s="92"/>
+      <c r="I3" s="93"/>
     </row>
     <row r="4" spans="2:9">
       <c r="B4" t="s">
         <v>2</v>
       </c>
-      <c r="D4" s="127"/>
-      <c r="E4" s="128"/>
-      <c r="F4" s="128"/>
-      <c r="G4" s="128"/>
-      <c r="H4" s="128"/>
-      <c r="I4" s="129"/>
+      <c r="D4" s="94"/>
+      <c r="E4" s="95"/>
+      <c r="F4" s="95"/>
+      <c r="G4" s="95"/>
+      <c r="H4" s="95"/>
+      <c r="I4" s="96"/>
     </row>
     <row r="5" spans="2:9" ht="30">
       <c r="B5" s="17" t="s">
         <v>3</v>
       </c>
-      <c r="D5" s="127"/>
-      <c r="E5" s="128"/>
-      <c r="F5" s="128"/>
-      <c r="G5" s="128"/>
-      <c r="H5" s="128"/>
-      <c r="I5" s="129"/>
+      <c r="D5" s="94"/>
+      <c r="E5" s="95"/>
+      <c r="F5" s="95"/>
+      <c r="G5" s="95"/>
+      <c r="H5" s="95"/>
+      <c r="I5" s="96"/>
     </row>
     <row r="6" spans="2:9" ht="30">
       <c r="B6" s="17" t="s">
         <v>4</v>
       </c>
-      <c r="D6" s="127"/>
-      <c r="E6" s="128"/>
-      <c r="F6" s="128"/>
-      <c r="G6" s="128"/>
-      <c r="H6" s="128"/>
-      <c r="I6" s="129"/>
+      <c r="D6" s="94"/>
+      <c r="E6" s="95"/>
+      <c r="F6" s="95"/>
+      <c r="G6" s="95"/>
+      <c r="H6" s="95"/>
+      <c r="I6" s="96"/>
     </row>
     <row r="7" spans="2:9" ht="15.75" thickBot="1">
       <c r="B7" s="17"/>
-      <c r="D7" s="130"/>
-      <c r="E7" s="131"/>
-      <c r="F7" s="131"/>
-      <c r="G7" s="131"/>
-      <c r="H7" s="131"/>
-      <c r="I7" s="132"/>
+      <c r="D7" s="97"/>
+      <c r="E7" s="98"/>
+      <c r="F7" s="98"/>
+      <c r="G7" s="98"/>
+      <c r="H7" s="98"/>
+      <c r="I7" s="99"/>
     </row>
     <row r="8" spans="2:9">
       <c r="B8" s="16"/>
@@ -4762,26 +4713,26 @@
         <v>501</v>
       </c>
       <c r="E2" s="23"/>
-      <c r="F2" s="115" t="s">
+      <c r="F2" s="131" t="s">
         <v>12</v>
       </c>
-      <c r="G2" s="116"/>
-      <c r="H2" s="117"/>
-      <c r="J2" s="93" t="s">
+      <c r="G2" s="132"/>
+      <c r="H2" s="133"/>
+      <c r="J2" s="109" t="s">
         <v>13</v>
       </c>
-      <c r="K2" s="94"/>
+      <c r="K2" s="110"/>
       <c r="M2" s="78">
         <v>15</v>
       </c>
-      <c r="N2" s="120" t="s">
+      <c r="N2" s="136" t="s">
         <v>14</v>
       </c>
-      <c r="O2" s="120"/>
-      <c r="P2" s="120"/>
-      <c r="Q2" s="120"/>
-      <c r="R2" s="120"/>
-      <c r="S2" s="121"/>
+      <c r="O2" s="136"/>
+      <c r="P2" s="136"/>
+      <c r="Q2" s="136"/>
+      <c r="R2" s="136"/>
+      <c r="S2" s="137"/>
       <c r="AK2" s="4">
         <f>MOD(CODE(MID(D2,1,1))*CODE(MID(D2,2,1))*CODE(MID(D2,3,1))*1103515245 + 12345,9172)</f>
         <v>5008</v>
@@ -4797,11 +4748,11 @@
         <v>Enter Name</v>
       </c>
       <c r="E3" s="23"/>
-      <c r="F3" s="115" t="s">
+      <c r="F3" s="131" t="s">
         <v>15</v>
       </c>
-      <c r="G3" s="116"/>
-      <c r="H3" s="117"/>
+      <c r="G3" s="132"/>
+      <c r="H3" s="133"/>
       <c r="J3" s="7" t="s">
         <v>16</v>
       </c>
@@ -4811,14 +4762,14 @@
       <c r="M3" s="79">
         <v>15</v>
       </c>
-      <c r="N3" s="118" t="s">
+      <c r="N3" s="134" t="s">
         <v>18</v>
       </c>
-      <c r="O3" s="118"/>
-      <c r="P3" s="118"/>
-      <c r="Q3" s="118"/>
-      <c r="R3" s="118"/>
-      <c r="S3" s="119"/>
+      <c r="O3" s="134"/>
+      <c r="P3" s="134"/>
+      <c r="Q3" s="134"/>
+      <c r="R3" s="134"/>
+      <c r="S3" s="135"/>
       <c r="AK3" s="4">
         <f>MOD(AK2*1103515245 + 12345,9172)</f>
         <v>6441</v>
@@ -4837,11 +4788,11 @@
         <v>19</v>
       </c>
       <c r="E4" s="25"/>
-      <c r="F4" s="115" t="s">
+      <c r="F4" s="131" t="s">
         <v>20</v>
       </c>
-      <c r="G4" s="116"/>
-      <c r="H4" s="117"/>
+      <c r="G4" s="132"/>
+      <c r="H4" s="133"/>
       <c r="J4" s="9" t="s">
         <v>21</v>
       </c>
@@ -4876,7 +4827,7 @@
       <c r="D5" s="26" t="s">
         <v>24</v>
       </c>
-      <c r="E5" s="176"/>
+      <c r="E5" s="88"/>
       <c r="G5" s="27"/>
       <c r="H5" s="28"/>
       <c r="J5" s="11" t="s">
@@ -4888,14 +4839,14 @@
       <c r="M5" s="81">
         <v>16</v>
       </c>
-      <c r="N5" s="122" t="s">
+      <c r="N5" s="138" t="s">
         <v>27</v>
       </c>
-      <c r="O5" s="122"/>
-      <c r="P5" s="122"/>
-      <c r="Q5" s="122"/>
-      <c r="R5" s="122"/>
-      <c r="S5" s="123"/>
+      <c r="O5" s="138"/>
+      <c r="P5" s="138"/>
+      <c r="Q5" s="138"/>
+      <c r="R5" s="138"/>
+      <c r="S5" s="139"/>
       <c r="AK5" s="4">
         <f t="shared" si="1"/>
         <v>2547</v>
@@ -4913,7 +4864,7 @@
       <c r="D6" s="29" t="s">
         <v>28</v>
       </c>
-      <c r="E6" s="177"/>
+      <c r="E6" s="89"/>
       <c r="G6" s="77"/>
       <c r="H6" s="77"/>
       <c r="J6" s="12" t="s">
@@ -4939,7 +4890,7 @@
       <c r="D7" s="30" t="s">
         <v>31</v>
       </c>
-      <c r="E7" s="178"/>
+      <c r="E7" s="90"/>
       <c r="G7" s="77"/>
       <c r="H7" s="77"/>
       <c r="J7" s="13" t="s">
@@ -4976,13 +4927,13 @@
         <f>IF(D$2="Your Name Here","Enter Name",ROUND(_xlfn.NORM.INV(Random!D19,20,15),1))</f>
         <v>Enter Name</v>
       </c>
-      <c r="D9" s="103" t="s">
+      <c r="D9" s="119" t="s">
         <v>34</v>
       </c>
-      <c r="E9" s="104"/>
-      <c r="F9" s="104"/>
-      <c r="G9" s="104"/>
-      <c r="H9" s="105"/>
+      <c r="E9" s="120"/>
+      <c r="F9" s="120"/>
+      <c r="G9" s="120"/>
+      <c r="H9" s="121"/>
       <c r="AK9" s="4">
         <f t="shared" si="1"/>
         <v>6743</v>
@@ -5012,14 +4963,14 @@
       <c r="H10" s="33" t="s">
         <v>39</v>
       </c>
-      <c r="J10" s="106" t="s">
+      <c r="J10" s="122" t="s">
         <v>40</v>
       </c>
-      <c r="K10" s="107"/>
-      <c r="L10" s="107"/>
-      <c r="M10" s="107"/>
-      <c r="N10" s="107"/>
-      <c r="O10" s="108"/>
+      <c r="K10" s="123"/>
+      <c r="L10" s="123"/>
+      <c r="M10" s="123"/>
+      <c r="N10" s="123"/>
+      <c r="O10" s="124"/>
       <c r="AK10" s="4">
         <f t="shared" si="1"/>
         <v>6608</v>
@@ -5034,17 +4985,17 @@
         <f>IF(D$2="Your Name Here","Enter Name",ROUND(_xlfn.NORM.INV(Random!D21,20,15),1))</f>
         <v>Enter Name</v>
       </c>
-      <c r="D11" s="172"/>
-      <c r="E11" s="173"/>
-      <c r="F11" s="173"/>
-      <c r="G11" s="173"/>
-      <c r="H11" s="174"/>
-      <c r="J11" s="109"/>
-      <c r="K11" s="110"/>
-      <c r="L11" s="110"/>
-      <c r="M11" s="110"/>
-      <c r="N11" s="110"/>
-      <c r="O11" s="111"/>
+      <c r="D11" s="84"/>
+      <c r="E11" s="85"/>
+      <c r="F11" s="85"/>
+      <c r="G11" s="85"/>
+      <c r="H11" s="86"/>
+      <c r="J11" s="125"/>
+      <c r="K11" s="126"/>
+      <c r="L11" s="126"/>
+      <c r="M11" s="126"/>
+      <c r="N11" s="126"/>
+      <c r="O11" s="127"/>
       <c r="AK11" s="4">
         <f t="shared" si="1"/>
         <v>7573</v>
@@ -5059,17 +5010,17 @@
         <f>IF(D$2="Your Name Here","Enter Name",ROUND(_xlfn.NORM.INV(Random!D22,20,15),1))</f>
         <v>Enter Name</v>
       </c>
-      <c r="D12" s="175"/>
-      <c r="E12" s="173"/>
-      <c r="F12" s="173"/>
-      <c r="G12" s="173"/>
-      <c r="H12" s="174"/>
-      <c r="J12" s="109"/>
-      <c r="K12" s="110"/>
-      <c r="L12" s="110"/>
-      <c r="M12" s="110"/>
-      <c r="N12" s="110"/>
-      <c r="O12" s="111"/>
+      <c r="D12" s="87"/>
+      <c r="E12" s="85"/>
+      <c r="F12" s="85"/>
+      <c r="G12" s="85"/>
+      <c r="H12" s="86"/>
+      <c r="J12" s="125"/>
+      <c r="K12" s="126"/>
+      <c r="L12" s="126"/>
+      <c r="M12" s="126"/>
+      <c r="N12" s="126"/>
+      <c r="O12" s="127"/>
       <c r="AK12" s="4">
         <f t="shared" si="1"/>
         <v>6450</v>
@@ -5084,17 +5035,17 @@
         <f>IF(D$2="Your Name Here","Enter Name",ROUND(_xlfn.NORM.INV(Random!D23,20,15),1))</f>
         <v>Enter Name</v>
       </c>
-      <c r="D13" s="175"/>
-      <c r="E13" s="173"/>
-      <c r="F13" s="173"/>
-      <c r="G13" s="173"/>
-      <c r="H13" s="174"/>
-      <c r="J13" s="109"/>
-      <c r="K13" s="110"/>
-      <c r="L13" s="110"/>
-      <c r="M13" s="110"/>
-      <c r="N13" s="110"/>
-      <c r="O13" s="111"/>
+      <c r="D13" s="87"/>
+      <c r="E13" s="85"/>
+      <c r="F13" s="85"/>
+      <c r="G13" s="85"/>
+      <c r="H13" s="86"/>
+      <c r="J13" s="125"/>
+      <c r="K13" s="126"/>
+      <c r="L13" s="126"/>
+      <c r="M13" s="126"/>
+      <c r="N13" s="126"/>
+      <c r="O13" s="127"/>
       <c r="AK13" s="4">
         <f t="shared" si="1"/>
         <v>8023</v>
@@ -5109,17 +5060,17 @@
         <f>IF(D$2="Your Name Here","Enter Name",ROUND(_xlfn.NORM.INV(Random!D24,20,15),1))</f>
         <v>Enter Name</v>
       </c>
-      <c r="D14" s="175"/>
-      <c r="E14" s="173"/>
-      <c r="F14" s="173"/>
-      <c r="G14" s="173"/>
-      <c r="H14" s="174"/>
-      <c r="J14" s="109"/>
-      <c r="K14" s="110"/>
-      <c r="L14" s="110"/>
-      <c r="M14" s="110"/>
-      <c r="N14" s="110"/>
-      <c r="O14" s="111"/>
+      <c r="D14" s="87"/>
+      <c r="E14" s="85"/>
+      <c r="F14" s="85"/>
+      <c r="G14" s="85"/>
+      <c r="H14" s="86"/>
+      <c r="J14" s="125"/>
+      <c r="K14" s="126"/>
+      <c r="L14" s="126"/>
+      <c r="M14" s="126"/>
+      <c r="N14" s="126"/>
+      <c r="O14" s="127"/>
       <c r="AK14" s="4">
         <f>MOD(AK13*1103515245 + 12345,9172)</f>
         <v>176</v>
@@ -5134,17 +5085,17 @@
         <f>IF(D$2="Your Name Here","Enter Name",ROUND(_xlfn.NORM.INV(Random!D25,20,15),1))</f>
         <v>Enter Name</v>
       </c>
-      <c r="D15" s="175"/>
-      <c r="E15" s="173"/>
-      <c r="F15" s="173"/>
-      <c r="G15" s="173"/>
-      <c r="H15" s="174"/>
-      <c r="J15" s="109"/>
-      <c r="K15" s="110"/>
-      <c r="L15" s="110"/>
-      <c r="M15" s="110"/>
-      <c r="N15" s="110"/>
-      <c r="O15" s="111"/>
+      <c r="D15" s="87"/>
+      <c r="E15" s="85"/>
+      <c r="F15" s="85"/>
+      <c r="G15" s="85"/>
+      <c r="H15" s="86"/>
+      <c r="J15" s="125"/>
+      <c r="K15" s="126"/>
+      <c r="L15" s="126"/>
+      <c r="M15" s="126"/>
+      <c r="N15" s="126"/>
+      <c r="O15" s="127"/>
       <c r="AK15" s="4">
         <f t="shared" si="1"/>
         <v>8709</v>
@@ -5159,17 +5110,17 @@
         <f>IF(D$2="Your Name Here","Enter Name",ROUND(_xlfn.NORM.INV(Random!D26,20,15),1))</f>
         <v>Enter Name</v>
       </c>
-      <c r="D16" s="175"/>
-      <c r="E16" s="173"/>
-      <c r="F16" s="173"/>
-      <c r="G16" s="173"/>
-      <c r="H16" s="174"/>
-      <c r="J16" s="109"/>
-      <c r="K16" s="110"/>
-      <c r="L16" s="110"/>
-      <c r="M16" s="110"/>
-      <c r="N16" s="110"/>
-      <c r="O16" s="111"/>
+      <c r="D16" s="87"/>
+      <c r="E16" s="85"/>
+      <c r="F16" s="85"/>
+      <c r="G16" s="85"/>
+      <c r="H16" s="86"/>
+      <c r="J16" s="125"/>
+      <c r="K16" s="126"/>
+      <c r="L16" s="126"/>
+      <c r="M16" s="126"/>
+      <c r="N16" s="126"/>
+      <c r="O16" s="127"/>
       <c r="AK16" s="4">
         <f t="shared" si="1"/>
         <v>7162</v>
@@ -5184,17 +5135,17 @@
         <f>IF(D$2="Your Name Here","Enter Name",ROUND(_xlfn.NORM.INV(Random!D27,20,15),1))</f>
         <v>Enter Name</v>
       </c>
-      <c r="D17" s="175"/>
-      <c r="E17" s="173"/>
-      <c r="F17" s="173"/>
-      <c r="G17" s="173"/>
-      <c r="H17" s="174"/>
-      <c r="J17" s="109"/>
-      <c r="K17" s="110"/>
-      <c r="L17" s="110"/>
-      <c r="M17" s="110"/>
-      <c r="N17" s="110"/>
-      <c r="O17" s="111"/>
+      <c r="D17" s="87"/>
+      <c r="E17" s="85"/>
+      <c r="F17" s="85"/>
+      <c r="G17" s="85"/>
+      <c r="H17" s="86"/>
+      <c r="J17" s="125"/>
+      <c r="K17" s="126"/>
+      <c r="L17" s="126"/>
+      <c r="M17" s="126"/>
+      <c r="N17" s="126"/>
+      <c r="O17" s="127"/>
       <c r="AK17" s="4">
         <f t="shared" si="1"/>
         <v>1235</v>
@@ -5209,17 +5160,17 @@
         <f>IF(D$2="Your Name Here","Enter Name",ROUND(_xlfn.NORM.INV(Random!D28,20,15),1))</f>
         <v>Enter Name</v>
       </c>
-      <c r="D18" s="175"/>
-      <c r="E18" s="173"/>
-      <c r="F18" s="173"/>
-      <c r="G18" s="173"/>
-      <c r="H18" s="174"/>
-      <c r="J18" s="109"/>
-      <c r="K18" s="110"/>
-      <c r="L18" s="110"/>
-      <c r="M18" s="110"/>
-      <c r="N18" s="110"/>
-      <c r="O18" s="111"/>
+      <c r="D18" s="87"/>
+      <c r="E18" s="85"/>
+      <c r="F18" s="85"/>
+      <c r="G18" s="85"/>
+      <c r="H18" s="86"/>
+      <c r="J18" s="125"/>
+      <c r="K18" s="126"/>
+      <c r="L18" s="126"/>
+      <c r="M18" s="126"/>
+      <c r="N18" s="126"/>
+      <c r="O18" s="127"/>
       <c r="AK18" s="4">
         <f t="shared" si="1"/>
         <v>120</v>
@@ -5234,17 +5185,17 @@
         <f>IF(D$2="Your Name Here","Enter Name",ROUND(_xlfn.NORM.INV(Random!D29,20,15),1))</f>
         <v>Enter Name</v>
       </c>
-      <c r="D19" s="175"/>
-      <c r="E19" s="173"/>
-      <c r="F19" s="173"/>
-      <c r="G19" s="173"/>
-      <c r="H19" s="174"/>
-      <c r="J19" s="109"/>
-      <c r="K19" s="110"/>
-      <c r="L19" s="110"/>
-      <c r="M19" s="110"/>
-      <c r="N19" s="110"/>
-      <c r="O19" s="111"/>
+      <c r="D19" s="87"/>
+      <c r="E19" s="85"/>
+      <c r="F19" s="85"/>
+      <c r="G19" s="85"/>
+      <c r="H19" s="86"/>
+      <c r="J19" s="125"/>
+      <c r="K19" s="126"/>
+      <c r="L19" s="126"/>
+      <c r="M19" s="126"/>
+      <c r="N19" s="126"/>
+      <c r="O19" s="127"/>
       <c r="Q19" s="34"/>
       <c r="AK19" s="4">
         <f t="shared" si="1"/>
@@ -5260,17 +5211,17 @@
         <f>IF(D$2="Your Name Here","Enter Name",ROUND(_xlfn.NORM.INV(Random!D30,20,15),1))</f>
         <v>Enter Name</v>
       </c>
-      <c r="D20" s="175"/>
-      <c r="E20" s="173"/>
-      <c r="F20" s="173"/>
-      <c r="G20" s="173"/>
-      <c r="H20" s="174"/>
-      <c r="J20" s="109"/>
-      <c r="K20" s="110"/>
-      <c r="L20" s="110"/>
-      <c r="M20" s="110"/>
-      <c r="N20" s="110"/>
-      <c r="O20" s="111"/>
+      <c r="D20" s="87"/>
+      <c r="E20" s="85"/>
+      <c r="F20" s="85"/>
+      <c r="G20" s="85"/>
+      <c r="H20" s="86"/>
+      <c r="J20" s="125"/>
+      <c r="K20" s="126"/>
+      <c r="L20" s="126"/>
+      <c r="M20" s="126"/>
+      <c r="N20" s="126"/>
+      <c r="O20" s="127"/>
       <c r="Q20" s="34"/>
       <c r="AK20" s="4">
         <f t="shared" si="1"/>
@@ -5286,17 +5237,17 @@
         <f>IF(D$2="Your Name Here","Enter Name",ROUND(_xlfn.NORM.INV(Random!D31,20,15),1))</f>
         <v>Enter Name</v>
       </c>
-      <c r="D21" s="175"/>
-      <c r="E21" s="173"/>
-      <c r="F21" s="173"/>
-      <c r="G21" s="173"/>
-      <c r="H21" s="174"/>
-      <c r="J21" s="109"/>
-      <c r="K21" s="110"/>
-      <c r="L21" s="110"/>
-      <c r="M21" s="110"/>
-      <c r="N21" s="110"/>
-      <c r="O21" s="111"/>
+      <c r="D21" s="87"/>
+      <c r="E21" s="85"/>
+      <c r="F21" s="85"/>
+      <c r="G21" s="85"/>
+      <c r="H21" s="86"/>
+      <c r="J21" s="125"/>
+      <c r="K21" s="126"/>
+      <c r="L21" s="126"/>
+      <c r="M21" s="126"/>
+      <c r="N21" s="126"/>
+      <c r="O21" s="127"/>
       <c r="AK21" s="4">
         <f t="shared" si="1"/>
         <v>7051</v>
@@ -5322,12 +5273,12 @@
         <f>SUM(H11:H21)</f>
         <v>0</v>
       </c>
-      <c r="J22" s="109"/>
-      <c r="K22" s="110"/>
-      <c r="L22" s="110"/>
-      <c r="M22" s="110"/>
-      <c r="N22" s="110"/>
-      <c r="O22" s="111"/>
+      <c r="J22" s="125"/>
+      <c r="K22" s="126"/>
+      <c r="L22" s="126"/>
+      <c r="M22" s="126"/>
+      <c r="N22" s="126"/>
+      <c r="O22" s="127"/>
       <c r="AK22" s="4">
         <f t="shared" si="1"/>
         <v>7124</v>
@@ -5351,12 +5302,12 @@
       <c r="H23" s="38">
         <v>1</v>
       </c>
-      <c r="J23" s="112"/>
-      <c r="K23" s="113"/>
-      <c r="L23" s="113"/>
-      <c r="M23" s="113"/>
-      <c r="N23" s="113"/>
-      <c r="O23" s="114"/>
+      <c r="J23" s="128"/>
+      <c r="K23" s="129"/>
+      <c r="L23" s="129"/>
+      <c r="M23" s="129"/>
+      <c r="N23" s="129"/>
+      <c r="O23" s="130"/>
       <c r="AK23" s="4">
         <f t="shared" si="1"/>
         <v>7961</v>
@@ -5371,13 +5322,13 @@
         <f>IF(D$2="Your Name Here","Enter Name",ROUND(_xlfn.NORM.INV(Random!D34,20,15),1))</f>
         <v>Enter Name</v>
       </c>
-      <c r="D24" s="95" t="s">
+      <c r="D24" s="111" t="s">
         <v>43</v>
       </c>
-      <c r="E24" s="96"/>
-      <c r="F24" s="97"/>
-      <c r="G24" s="97"/>
-      <c r="H24" s="98"/>
+      <c r="E24" s="112"/>
+      <c r="F24" s="113"/>
+      <c r="G24" s="113"/>
+      <c r="H24" s="114"/>
       <c r="AK24" s="4">
         <f t="shared" si="1"/>
         <v>1978</v>
@@ -5392,11 +5343,11 @@
         <f>IF(D$2="Your Name Here","Enter Name",ROUND(_xlfn.NORM.INV(Random!D35,20,15),1))</f>
         <v>Enter Name</v>
       </c>
-      <c r="D25" s="99"/>
-      <c r="E25" s="97"/>
-      <c r="F25" s="97"/>
-      <c r="G25" s="97"/>
-      <c r="H25" s="98"/>
+      <c r="D25" s="115"/>
+      <c r="E25" s="113"/>
+      <c r="F25" s="113"/>
+      <c r="G25" s="113"/>
+      <c r="H25" s="114"/>
       <c r="AK25" s="4">
         <f t="shared" si="1"/>
         <v>1603</v>
@@ -5411,11 +5362,11 @@
         <f>IF(D$2="Your Name Here","Enter Name",ROUND(_xlfn.NORM.INV(Random!D36,20,15),1))</f>
         <v>Enter Name</v>
       </c>
-      <c r="D26" s="99"/>
-      <c r="E26" s="97"/>
-      <c r="F26" s="97"/>
-      <c r="G26" s="97"/>
-      <c r="H26" s="98"/>
+      <c r="D26" s="115"/>
+      <c r="E26" s="113"/>
+      <c r="F26" s="113"/>
+      <c r="G26" s="113"/>
+      <c r="H26" s="114"/>
       <c r="AK26" s="4">
         <f t="shared" si="1"/>
         <v>8360</v>
@@ -5430,11 +5381,11 @@
         <f>IF(D$2="Your Name Here","Enter Name",ROUND(_xlfn.NORM.INV(Random!D37,20,15),1))</f>
         <v>Enter Name</v>
       </c>
-      <c r="D27" s="100"/>
-      <c r="E27" s="101"/>
-      <c r="F27" s="101"/>
-      <c r="G27" s="101"/>
-      <c r="H27" s="102"/>
+      <c r="D27" s="116"/>
+      <c r="E27" s="117"/>
+      <c r="F27" s="117"/>
+      <c r="G27" s="117"/>
+      <c r="H27" s="118"/>
       <c r="AK27" s="4">
         <f t="shared" si="1"/>
         <v>145</v>
@@ -5463,13 +5414,13 @@
         <f>IF(D$2="Your Name Here","Enter Name",ROUND(_xlfn.NORM.INV(Random!D39,20,15),1))</f>
         <v>Enter Name</v>
       </c>
-      <c r="D29" s="84" t="s">
+      <c r="D29" s="100" t="s">
         <v>44</v>
       </c>
-      <c r="E29" s="85"/>
-      <c r="F29" s="85"/>
-      <c r="G29" s="85"/>
-      <c r="H29" s="86"/>
+      <c r="E29" s="101"/>
+      <c r="F29" s="101"/>
+      <c r="G29" s="101"/>
+      <c r="H29" s="102"/>
       <c r="AK29" s="4">
         <f t="shared" si="1"/>
         <v>8195</v>
@@ -5484,11 +5435,11 @@
         <f>IF(D$2="Your Name Here","Enter Name",ROUND(_xlfn.NORM.INV(Random!D40,20,15),1))</f>
         <v>Enter Name</v>
       </c>
-      <c r="D30" s="87"/>
-      <c r="E30" s="88"/>
-      <c r="F30" s="88"/>
-      <c r="G30" s="88"/>
-      <c r="H30" s="89"/>
+      <c r="D30" s="103"/>
+      <c r="E30" s="104"/>
+      <c r="F30" s="104"/>
+      <c r="G30" s="104"/>
+      <c r="H30" s="105"/>
       <c r="AK30" s="4">
         <f t="shared" si="1"/>
         <v>6420</v>
@@ -5503,11 +5454,11 @@
         <f>IF(D$2="Your Name Here","Enter Name",ROUND(_xlfn.NORM.INV(Random!D41,20,15),1))</f>
         <v>Enter Name</v>
       </c>
-      <c r="D31" s="87"/>
-      <c r="E31" s="88"/>
-      <c r="F31" s="88"/>
-      <c r="G31" s="88"/>
-      <c r="H31" s="89"/>
+      <c r="D31" s="103"/>
+      <c r="E31" s="104"/>
+      <c r="F31" s="104"/>
+      <c r="G31" s="104"/>
+      <c r="H31" s="105"/>
       <c r="AK31" s="4">
         <f t="shared" si="1"/>
         <v>4161</v>
@@ -5522,11 +5473,11 @@
         <f>IF(D$2="Your Name Here","Enter Name",ROUND(_xlfn.NORM.INV(Random!D42,20,15),1))</f>
         <v>Enter Name</v>
       </c>
-      <c r="D32" s="87"/>
-      <c r="E32" s="88"/>
-      <c r="F32" s="88"/>
-      <c r="G32" s="88"/>
-      <c r="H32" s="89"/>
+      <c r="D32" s="103"/>
+      <c r="E32" s="104"/>
+      <c r="F32" s="104"/>
+      <c r="G32" s="104"/>
+      <c r="H32" s="105"/>
       <c r="AK32" s="4">
         <f t="shared" si="1"/>
         <v>5022</v>
@@ -5541,11 +5492,11 @@
         <f>IF(D$2="Your Name Here","Enter Name",ROUND(_xlfn.NORM.INV(Random!D43,20,15),1))</f>
         <v>Enter Name</v>
       </c>
-      <c r="D33" s="87"/>
-      <c r="E33" s="88"/>
-      <c r="F33" s="88"/>
-      <c r="G33" s="88"/>
-      <c r="H33" s="89"/>
+      <c r="D33" s="103"/>
+      <c r="E33" s="104"/>
+      <c r="F33" s="104"/>
+      <c r="G33" s="104"/>
+      <c r="H33" s="105"/>
       <c r="AK33" s="4">
         <f t="shared" si="1"/>
         <v>3963</v>
@@ -5560,11 +5511,11 @@
         <f>IF(D$2="Your Name Here","Enter Name",ROUND(_xlfn.NORM.INV(Random!D44,20,15),1))</f>
         <v>Enter Name</v>
       </c>
-      <c r="D34" s="87"/>
-      <c r="E34" s="88"/>
-      <c r="F34" s="88"/>
-      <c r="G34" s="88"/>
-      <c r="H34" s="89"/>
+      <c r="D34" s="103"/>
+      <c r="E34" s="104"/>
+      <c r="F34" s="104"/>
+      <c r="G34" s="104"/>
+      <c r="H34" s="105"/>
       <c r="AK34" s="4">
         <f t="shared" si="1"/>
         <v>3380</v>
@@ -5579,11 +5530,11 @@
         <f>IF(D$2="Your Name Here","Enter Name",ROUND(_xlfn.NORM.INV(Random!D45,20,15),1))</f>
         <v>Enter Name</v>
       </c>
-      <c r="D35" s="87"/>
-      <c r="E35" s="88"/>
-      <c r="F35" s="88"/>
-      <c r="G35" s="88"/>
-      <c r="H35" s="89"/>
+      <c r="D35" s="103"/>
+      <c r="E35" s="104"/>
+      <c r="F35" s="104"/>
+      <c r="G35" s="104"/>
+      <c r="H35" s="105"/>
       <c r="AK35" s="4">
         <f t="shared" si="1"/>
         <v>1093</v>
@@ -5598,11 +5549,11 @@
         <f>IF(D$2="Your Name Here","Enter Name",ROUND(_xlfn.NORM.INV(Random!D46,20,15),1))</f>
         <v>Enter Name</v>
       </c>
-      <c r="D36" s="87"/>
-      <c r="E36" s="88"/>
-      <c r="F36" s="88"/>
-      <c r="G36" s="88"/>
-      <c r="H36" s="89"/>
+      <c r="D36" s="103"/>
+      <c r="E36" s="104"/>
+      <c r="F36" s="104"/>
+      <c r="G36" s="104"/>
+      <c r="H36" s="105"/>
       <c r="AK36" s="4">
         <f t="shared" si="1"/>
         <v>6910</v>
@@ -5617,11 +5568,11 @@
         <f>IF(D$2="Your Name Here","Enter Name",ROUND(_xlfn.NORM.INV(Random!D47,20,15),1))</f>
         <v>Enter Name</v>
       </c>
-      <c r="D37" s="87"/>
-      <c r="E37" s="88"/>
-      <c r="F37" s="88"/>
-      <c r="G37" s="88"/>
-      <c r="H37" s="89"/>
+      <c r="D37" s="103"/>
+      <c r="E37" s="104"/>
+      <c r="F37" s="104"/>
+      <c r="G37" s="104"/>
+      <c r="H37" s="105"/>
       <c r="AK37" s="4">
         <f t="shared" si="1"/>
         <v>9151</v>
@@ -5636,11 +5587,11 @@
         <f>IF(D$2="Your Name Here","Enter Name",ROUND(_xlfn.NORM.INV(Random!D48,20,15),1))</f>
         <v>Enter Name</v>
       </c>
-      <c r="D38" s="87"/>
-      <c r="E38" s="88"/>
-      <c r="F38" s="88"/>
-      <c r="G38" s="88"/>
-      <c r="H38" s="89"/>
+      <c r="D38" s="103"/>
+      <c r="E38" s="104"/>
+      <c r="F38" s="104"/>
+      <c r="G38" s="104"/>
+      <c r="H38" s="105"/>
       <c r="AK38" s="4">
         <f t="shared" si="1"/>
         <v>2304</v>
@@ -5655,11 +5606,11 @@
         <f>IF(D$2="Your Name Here","Enter Name",ROUND(_xlfn.NORM.INV(Random!D49,20,15),1))</f>
         <v>Enter Name</v>
       </c>
-      <c r="D39" s="87"/>
-      <c r="E39" s="88"/>
-      <c r="F39" s="88"/>
-      <c r="G39" s="88"/>
-      <c r="H39" s="89"/>
+      <c r="D39" s="103"/>
+      <c r="E39" s="104"/>
+      <c r="F39" s="104"/>
+      <c r="G39" s="104"/>
+      <c r="H39" s="105"/>
       <c r="AK39" s="4">
         <f t="shared" si="1"/>
         <v>8105</v>
@@ -5674,11 +5625,11 @@
         <f>IF(D$2="Your Name Here","Enter Name",ROUND(_xlfn.NORM.INV(Random!D50,20,15),1))</f>
         <v>Enter Name</v>
       </c>
-      <c r="D40" s="90"/>
-      <c r="E40" s="91"/>
-      <c r="F40" s="91"/>
-      <c r="G40" s="91"/>
-      <c r="H40" s="92"/>
+      <c r="D40" s="106"/>
+      <c r="E40" s="107"/>
+      <c r="F40" s="107"/>
+      <c r="G40" s="107"/>
+      <c r="H40" s="108"/>
       <c r="AK40" s="4">
         <f t="shared" si="1"/>
         <v>4006</v>
@@ -6590,7 +6541,7 @@
     <mergeCell ref="N5:S5"/>
   </mergeCells>
   <conditionalFormatting sqref="E5:E7 D11:F21">
-    <cfRule type="expression" dxfId="6" priority="12">
+    <cfRule type="expression" dxfId="5" priority="12">
       <formula>AND(NOT(ISBLANK(D5)),NOT(_xlfn.ISFORMULA(D5)))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -6647,6 +6598,16 @@
           <xm:sqref>E7</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="expression" priority="2" id="{246D2ADF-3B33-44BD-B369-436EC59685E8}">
+            <xm:f>Solution!$K36</xm:f>
+            <x14:dxf>
+              <font>
+                <b/>
+                <i val="0"/>
+                <color rgb="FF00B050"/>
+              </font>
+            </x14:dxf>
+          </x14:cfRule>
           <x14:cfRule type="expression" priority="29" id="{03827A15-B0AA-4B09-A0D4-7D276C8E808E}">
             <xm:f>AND(NOT(Solution!L$32),NOT(_xlfn.ISFORMULA(G11)),NOT(ISBLANK(G11)))</xm:f>
             <x14:dxf>
@@ -6657,8 +6618,11 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="expression" priority="2" id="{246D2ADF-3B33-44BD-B369-436EC59685E8}">
-            <xm:f>Solution!$K36</xm:f>
+          <xm:sqref>G11:G21</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="expression" priority="1" id="{2454C867-EE89-4EA6-B198-26951C41E144}">
+            <xm:f>Solution!$P36</xm:f>
             <x14:dxf>
               <font>
                 <b/>
@@ -6667,9 +6631,6 @@
               </font>
             </x14:dxf>
           </x14:cfRule>
-          <xm:sqref>G11:G21</xm:sqref>
-        </x14:conditionalFormatting>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
           <x14:cfRule type="expression" priority="23" id="{4E9ED7D7-7D3C-43AB-856B-D39E9D2A4C8F}">
             <xm:f>AND(NOT(_xlfn.ISFORMULA(H11)),NOT(Solution!Q$31),NOT(ISBLANK(H11)))</xm:f>
             <x14:dxf>
@@ -6678,16 +6639,6 @@
                   <bgColor rgb="FFFFFF00"/>
                 </patternFill>
               </fill>
-            </x14:dxf>
-          </x14:cfRule>
-          <x14:cfRule type="expression" priority="1" id="{2454C867-EE89-4EA6-B198-26951C41E144}">
-            <xm:f>Solution!$P36</xm:f>
-            <x14:dxf>
-              <font>
-                <b/>
-                <i val="0"/>
-                <color rgb="FF00B050"/>
-              </font>
             </x14:dxf>
           </x14:cfRule>
           <xm:sqref>H11:H21</xm:sqref>
@@ -6747,15 +6698,15 @@
         <v>Your Name Here</v>
       </c>
       <c r="E2" s="48"/>
-      <c r="F2" s="159" t="s">
+      <c r="F2" s="166" t="s">
         <v>12</v>
       </c>
-      <c r="G2" s="160"/>
-      <c r="H2" s="161"/>
-      <c r="J2" s="162" t="s">
+      <c r="G2" s="167"/>
+      <c r="H2" s="168"/>
+      <c r="J2" s="169" t="s">
         <v>13</v>
       </c>
-      <c r="K2" s="163"/>
+      <c r="K2" s="170"/>
       <c r="AK2" s="43">
         <f>MOD(CODE(MID(D2,1,1))*CODE(MID(D2,2,1))*CODE(MID(D2,3,1))*1103515245 + 12345,9172)</f>
         <v>5008</v>
@@ -6771,11 +6722,11 @@
         <v>Enter Name</v>
       </c>
       <c r="E3" s="48"/>
-      <c r="F3" s="159" t="s">
+      <c r="F3" s="166" t="s">
         <v>15</v>
       </c>
-      <c r="G3" s="160"/>
-      <c r="H3" s="161"/>
+      <c r="G3" s="167"/>
+      <c r="H3" s="168"/>
       <c r="J3" s="49" t="s">
         <v>16</v>
       </c>
@@ -6800,11 +6751,11 @@
         <v>19</v>
       </c>
       <c r="E4" s="52"/>
-      <c r="F4" s="159" t="s">
+      <c r="F4" s="166" t="s">
         <v>20</v>
       </c>
-      <c r="G4" s="160"/>
-      <c r="H4" s="161"/>
+      <c r="G4" s="167"/>
+      <c r="H4" s="168"/>
       <c r="J4" s="49" t="s">
         <v>21</v>
       </c>
@@ -6861,10 +6812,10 @@
         <f>MAX(B:B)</f>
         <v>0</v>
       </c>
-      <c r="G6" s="164" t="s">
+      <c r="G6" s="171" t="s">
         <v>45</v>
       </c>
-      <c r="H6" s="165"/>
+      <c r="H6" s="172"/>
       <c r="J6" s="49" t="s">
         <v>29</v>
       </c>
@@ -6892,8 +6843,8 @@
         <f>('Water Quality'!E6-'Water Quality'!E5)/11</f>
         <v>0</v>
       </c>
-      <c r="G7" s="166"/>
-      <c r="H7" s="167"/>
+      <c r="G7" s="173"/>
+      <c r="H7" s="174"/>
       <c r="J7" s="58" t="s">
         <v>32</v>
       </c>
@@ -6928,13 +6879,13 @@
         <f>IF(D$2="Your Name Here","Enter Name",ROUND(_xlfn.NORM.INV(Random!D19,20,15),1))</f>
         <v>Enter Name</v>
       </c>
-      <c r="D9" s="168" t="s">
+      <c r="D9" s="175" t="s">
         <v>34</v>
       </c>
-      <c r="E9" s="169"/>
-      <c r="F9" s="169"/>
-      <c r="G9" s="169"/>
-      <c r="H9" s="170"/>
+      <c r="E9" s="176"/>
+      <c r="F9" s="176"/>
+      <c r="G9" s="176"/>
+      <c r="H9" s="177"/>
       <c r="AK9" s="43">
         <f t="shared" si="1"/>
         <v>6743</v>
@@ -6964,14 +6915,14 @@
       <c r="H10" s="62" t="s">
         <v>39</v>
       </c>
-      <c r="J10" s="133" t="s">
+      <c r="J10" s="140" t="s">
         <v>47</v>
       </c>
-      <c r="K10" s="134"/>
-      <c r="L10" s="134"/>
-      <c r="M10" s="134"/>
-      <c r="N10" s="134"/>
-      <c r="O10" s="135"/>
+      <c r="K10" s="141"/>
+      <c r="L10" s="141"/>
+      <c r="M10" s="141"/>
+      <c r="N10" s="141"/>
+      <c r="O10" s="142"/>
       <c r="AK10" s="43">
         <f t="shared" si="1"/>
         <v>6608</v>
@@ -6987,11 +6938,11 @@
         <v>Enter Name</v>
       </c>
       <c r="D11" s="63">
-        <f>E5</f>
+        <f>'Water Quality'!E5</f>
         <v>0</v>
       </c>
       <c r="E11" s="64">
-        <f>D11+E$7</f>
+        <f>D11+'Water Quality'!E$7</f>
         <v>0</v>
       </c>
       <c r="F11" s="64">
@@ -7006,12 +6957,12 @@
         <f t="array" ref="H11:H21">_xlfn.ANCHORARRAY(G11)/SUM(_xlfn.ANCHORARRAY(G11))</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="J11" s="136"/>
-      <c r="K11" s="137"/>
-      <c r="L11" s="137"/>
-      <c r="M11" s="137"/>
-      <c r="N11" s="137"/>
-      <c r="O11" s="138"/>
+      <c r="J11" s="143"/>
+      <c r="K11" s="144"/>
+      <c r="L11" s="144"/>
+      <c r="M11" s="144"/>
+      <c r="N11" s="144"/>
+      <c r="O11" s="145"/>
       <c r="AK11" s="43">
         <f t="shared" si="1"/>
         <v>7573</v>
@@ -7031,11 +6982,11 @@
         <v>0</v>
       </c>
       <c r="E12" s="64">
-        <f t="shared" ref="E12:E21" si="2">D12+E$7</f>
+        <f>D12+'Water Quality'!E$7</f>
         <v>0</v>
       </c>
       <c r="F12" s="64">
-        <f t="shared" ref="F12:F21" si="3">(D12+E12)/2</f>
+        <f t="shared" ref="F12:F21" si="2">(D12+E12)/2</f>
         <v>0</v>
       </c>
       <c r="G12" s="65">
@@ -7044,12 +6995,12 @@
       <c r="H12" s="66" t="e">
         <v>#DIV/0!</v>
       </c>
-      <c r="J12" s="136"/>
-      <c r="K12" s="137"/>
-      <c r="L12" s="137"/>
-      <c r="M12" s="137"/>
-      <c r="N12" s="137"/>
-      <c r="O12" s="138"/>
+      <c r="J12" s="143"/>
+      <c r="K12" s="144"/>
+      <c r="L12" s="144"/>
+      <c r="M12" s="144"/>
+      <c r="N12" s="144"/>
+      <c r="O12" s="145"/>
       <c r="AK12" s="43">
         <f t="shared" si="1"/>
         <v>6450</v>
@@ -7065,15 +7016,15 @@
         <v>Enter Name</v>
       </c>
       <c r="D13" s="67">
-        <f t="shared" ref="D13:D21" si="4">E12</f>
+        <f t="shared" ref="D13:D21" si="3">E12</f>
         <v>0</v>
       </c>
       <c r="E13" s="64">
+        <f>D13+'Water Quality'!E$7</f>
+        <v>0</v>
+      </c>
+      <c r="F13" s="64">
         <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="F13" s="64">
-        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="G13" s="65">
@@ -7082,12 +7033,12 @@
       <c r="H13" s="66" t="e">
         <v>#DIV/0!</v>
       </c>
-      <c r="J13" s="136"/>
-      <c r="K13" s="137"/>
-      <c r="L13" s="137"/>
-      <c r="M13" s="137"/>
-      <c r="N13" s="137"/>
-      <c r="O13" s="138"/>
+      <c r="J13" s="143"/>
+      <c r="K13" s="144"/>
+      <c r="L13" s="144"/>
+      <c r="M13" s="144"/>
+      <c r="N13" s="144"/>
+      <c r="O13" s="145"/>
       <c r="AK13" s="43">
         <f t="shared" si="1"/>
         <v>8023</v>
@@ -7103,15 +7054,15 @@
         <v>Enter Name</v>
       </c>
       <c r="D14" s="67">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="E14" s="64">
+        <f>D14+'Water Quality'!E$7</f>
+        <v>0</v>
+      </c>
+      <c r="F14" s="64">
         <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="F14" s="64">
-        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="G14" s="65">
@@ -7120,12 +7071,12 @@
       <c r="H14" s="66" t="e">
         <v>#DIV/0!</v>
       </c>
-      <c r="J14" s="136"/>
-      <c r="K14" s="137"/>
-      <c r="L14" s="137"/>
-      <c r="M14" s="137"/>
-      <c r="N14" s="137"/>
-      <c r="O14" s="138"/>
+      <c r="J14" s="143"/>
+      <c r="K14" s="144"/>
+      <c r="L14" s="144"/>
+      <c r="M14" s="144"/>
+      <c r="N14" s="144"/>
+      <c r="O14" s="145"/>
       <c r="AK14" s="43">
         <f>MOD(AK13*1103515245 + 12345,9172)</f>
         <v>176</v>
@@ -7141,15 +7092,15 @@
         <v>Enter Name</v>
       </c>
       <c r="D15" s="67">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="E15" s="64">
+        <f>D15+'Water Quality'!E$7</f>
+        <v>0</v>
+      </c>
+      <c r="F15" s="64">
         <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="F15" s="64">
-        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="G15" s="65">
@@ -7158,12 +7109,12 @@
       <c r="H15" s="66" t="e">
         <v>#DIV/0!</v>
       </c>
-      <c r="J15" s="136"/>
-      <c r="K15" s="137"/>
-      <c r="L15" s="137"/>
-      <c r="M15" s="137"/>
-      <c r="N15" s="137"/>
-      <c r="O15" s="138"/>
+      <c r="J15" s="143"/>
+      <c r="K15" s="144"/>
+      <c r="L15" s="144"/>
+      <c r="M15" s="144"/>
+      <c r="N15" s="144"/>
+      <c r="O15" s="145"/>
       <c r="AK15" s="43">
         <f t="shared" si="1"/>
         <v>8709</v>
@@ -7179,15 +7130,15 @@
         <v>Enter Name</v>
       </c>
       <c r="D16" s="67">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="E16" s="64">
+        <f>D16+'Water Quality'!E$7</f>
+        <v>0</v>
+      </c>
+      <c r="F16" s="64">
         <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="F16" s="64">
-        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="G16" s="65">
@@ -7196,12 +7147,12 @@
       <c r="H16" s="66" t="e">
         <v>#DIV/0!</v>
       </c>
-      <c r="J16" s="136"/>
-      <c r="K16" s="137"/>
-      <c r="L16" s="137"/>
-      <c r="M16" s="137"/>
-      <c r="N16" s="137"/>
-      <c r="O16" s="138"/>
+      <c r="J16" s="143"/>
+      <c r="K16" s="144"/>
+      <c r="L16" s="144"/>
+      <c r="M16" s="144"/>
+      <c r="N16" s="144"/>
+      <c r="O16" s="145"/>
       <c r="AK16" s="43">
         <f t="shared" si="1"/>
         <v>7162</v>
@@ -7217,15 +7168,15 @@
         <v>Enter Name</v>
       </c>
       <c r="D17" s="67">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="E17" s="64">
+        <f>D17+'Water Quality'!E$7</f>
+        <v>0</v>
+      </c>
+      <c r="F17" s="64">
         <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="F17" s="64">
-        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="G17" s="65">
@@ -7234,12 +7185,12 @@
       <c r="H17" s="66" t="e">
         <v>#DIV/0!</v>
       </c>
-      <c r="J17" s="136"/>
-      <c r="K17" s="137"/>
-      <c r="L17" s="137"/>
-      <c r="M17" s="137"/>
-      <c r="N17" s="137"/>
-      <c r="O17" s="138"/>
+      <c r="J17" s="143"/>
+      <c r="K17" s="144"/>
+      <c r="L17" s="144"/>
+      <c r="M17" s="144"/>
+      <c r="N17" s="144"/>
+      <c r="O17" s="145"/>
       <c r="AK17" s="43">
         <f t="shared" si="1"/>
         <v>1235</v>
@@ -7255,15 +7206,15 @@
         <v>Enter Name</v>
       </c>
       <c r="D18" s="67">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="E18" s="64">
+        <f>D18+'Water Quality'!E$7</f>
+        <v>0</v>
+      </c>
+      <c r="F18" s="64">
         <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="F18" s="64">
-        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="G18" s="65">
@@ -7272,12 +7223,12 @@
       <c r="H18" s="66" t="e">
         <v>#DIV/0!</v>
       </c>
-      <c r="J18" s="136"/>
-      <c r="K18" s="137"/>
-      <c r="L18" s="137"/>
-      <c r="M18" s="137"/>
-      <c r="N18" s="137"/>
-      <c r="O18" s="138"/>
+      <c r="J18" s="143"/>
+      <c r="K18" s="144"/>
+      <c r="L18" s="144"/>
+      <c r="M18" s="144"/>
+      <c r="N18" s="144"/>
+      <c r="O18" s="145"/>
       <c r="AK18" s="43">
         <f t="shared" si="1"/>
         <v>120</v>
@@ -7293,15 +7244,15 @@
         <v>Enter Name</v>
       </c>
       <c r="D19" s="67">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="E19" s="64">
+        <f>D19+'Water Quality'!E$7</f>
+        <v>0</v>
+      </c>
+      <c r="F19" s="64">
         <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="F19" s="64">
-        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="G19" s="65">
@@ -7310,12 +7261,12 @@
       <c r="H19" s="66" t="e">
         <v>#DIV/0!</v>
       </c>
-      <c r="J19" s="136"/>
-      <c r="K19" s="137"/>
-      <c r="L19" s="137"/>
-      <c r="M19" s="137"/>
-      <c r="N19" s="137"/>
-      <c r="O19" s="138"/>
+      <c r="J19" s="143"/>
+      <c r="K19" s="144"/>
+      <c r="L19" s="144"/>
+      <c r="M19" s="144"/>
+      <c r="N19" s="144"/>
+      <c r="O19" s="145"/>
       <c r="Q19" s="68"/>
       <c r="AK19" s="43">
         <f t="shared" si="1"/>
@@ -7332,15 +7283,15 @@
         <v>Enter Name</v>
       </c>
       <c r="D20" s="67">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="E20" s="64">
+        <f>D20+'Water Quality'!E$7</f>
+        <v>0</v>
+      </c>
+      <c r="F20" s="64">
         <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="F20" s="64">
-        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="G20" s="65">
@@ -7349,12 +7300,12 @@
       <c r="H20" s="66" t="e">
         <v>#DIV/0!</v>
       </c>
-      <c r="J20" s="136"/>
-      <c r="K20" s="137"/>
-      <c r="L20" s="137"/>
-      <c r="M20" s="137"/>
-      <c r="N20" s="137"/>
-      <c r="O20" s="138"/>
+      <c r="J20" s="143"/>
+      <c r="K20" s="144"/>
+      <c r="L20" s="144"/>
+      <c r="M20" s="144"/>
+      <c r="N20" s="144"/>
+      <c r="O20" s="145"/>
       <c r="Q20" s="68"/>
       <c r="AK20" s="43">
         <f t="shared" si="1"/>
@@ -7371,15 +7322,15 @@
         <v>Enter Name</v>
       </c>
       <c r="D21" s="67">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="E21" s="64">
+        <f>D21+'Water Quality'!E$7</f>
+        <v>0</v>
+      </c>
+      <c r="F21" s="64">
         <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="F21" s="64">
-        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="G21" s="69">
@@ -7388,12 +7339,12 @@
       <c r="H21" s="70" t="e">
         <v>#DIV/0!</v>
       </c>
-      <c r="J21" s="136"/>
-      <c r="K21" s="137"/>
-      <c r="L21" s="137"/>
-      <c r="M21" s="137"/>
-      <c r="N21" s="137"/>
-      <c r="O21" s="138"/>
+      <c r="J21" s="143"/>
+      <c r="K21" s="144"/>
+      <c r="L21" s="144"/>
+      <c r="M21" s="144"/>
+      <c r="N21" s="144"/>
+      <c r="O21" s="145"/>
       <c r="AK21" s="43">
         <f t="shared" si="1"/>
         <v>7051</v>
@@ -7419,12 +7370,12 @@
         <f>SUM(H11:H21)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="J22" s="136"/>
-      <c r="K22" s="137"/>
-      <c r="L22" s="137"/>
-      <c r="M22" s="137"/>
-      <c r="N22" s="137"/>
-      <c r="O22" s="138"/>
+      <c r="J22" s="143"/>
+      <c r="K22" s="144"/>
+      <c r="L22" s="144"/>
+      <c r="M22" s="144"/>
+      <c r="N22" s="144"/>
+      <c r="O22" s="145"/>
       <c r="AK22" s="43">
         <f t="shared" si="1"/>
         <v>7124</v>
@@ -7448,12 +7399,12 @@
       <c r="H23" s="76">
         <v>1</v>
       </c>
-      <c r="J23" s="139"/>
-      <c r="K23" s="140"/>
-      <c r="L23" s="140"/>
-      <c r="M23" s="140"/>
-      <c r="N23" s="140"/>
-      <c r="O23" s="141"/>
+      <c r="J23" s="146"/>
+      <c r="K23" s="147"/>
+      <c r="L23" s="147"/>
+      <c r="M23" s="147"/>
+      <c r="N23" s="147"/>
+      <c r="O23" s="148"/>
       <c r="AK23" s="43">
         <f t="shared" si="1"/>
         <v>7961</v>
@@ -7468,13 +7419,13 @@
         <f>IF(D$2="Your Name Here","Enter Name",ROUND(_xlfn.NORM.INV(Random!D34,20,15),1))</f>
         <v>Enter Name</v>
       </c>
-      <c r="D24" s="142" t="s">
+      <c r="D24" s="149" t="s">
         <v>43</v>
       </c>
-      <c r="E24" s="143"/>
-      <c r="F24" s="144"/>
-      <c r="G24" s="144"/>
-      <c r="H24" s="145"/>
+      <c r="E24" s="150"/>
+      <c r="F24" s="151"/>
+      <c r="G24" s="151"/>
+      <c r="H24" s="152"/>
       <c r="AK24" s="43">
         <f t="shared" si="1"/>
         <v>1978</v>
@@ -7489,11 +7440,11 @@
         <f>IF(D$2="Your Name Here","Enter Name",ROUND(_xlfn.NORM.INV(Random!D35,20,15),1))</f>
         <v>Enter Name</v>
       </c>
-      <c r="D25" s="146"/>
-      <c r="E25" s="144"/>
-      <c r="F25" s="144"/>
-      <c r="G25" s="144"/>
-      <c r="H25" s="145"/>
+      <c r="D25" s="153"/>
+      <c r="E25" s="151"/>
+      <c r="F25" s="151"/>
+      <c r="G25" s="151"/>
+      <c r="H25" s="152"/>
       <c r="AK25" s="43">
         <f t="shared" si="1"/>
         <v>1603</v>
@@ -7508,11 +7459,11 @@
         <f>IF(D$2="Your Name Here","Enter Name",ROUND(_xlfn.NORM.INV(Random!D36,20,15),1))</f>
         <v>Enter Name</v>
       </c>
-      <c r="D26" s="146"/>
-      <c r="E26" s="144"/>
-      <c r="F26" s="144"/>
-      <c r="G26" s="144"/>
-      <c r="H26" s="145"/>
+      <c r="D26" s="153"/>
+      <c r="E26" s="151"/>
+      <c r="F26" s="151"/>
+      <c r="G26" s="151"/>
+      <c r="H26" s="152"/>
       <c r="AK26" s="43">
         <f t="shared" si="1"/>
         <v>8360</v>
@@ -7527,11 +7478,11 @@
         <f>IF(D$2="Your Name Here","Enter Name",ROUND(_xlfn.NORM.INV(Random!D37,20,15),1))</f>
         <v>Enter Name</v>
       </c>
-      <c r="D27" s="147"/>
-      <c r="E27" s="148"/>
-      <c r="F27" s="148"/>
-      <c r="G27" s="148"/>
-      <c r="H27" s="149"/>
+      <c r="D27" s="154"/>
+      <c r="E27" s="155"/>
+      <c r="F27" s="155"/>
+      <c r="G27" s="155"/>
+      <c r="H27" s="156"/>
       <c r="AK27" s="43">
         <f t="shared" si="1"/>
         <v>145</v>
@@ -7560,13 +7511,13 @@
         <f>IF(D$2="Your Name Here","Enter Name",ROUND(_xlfn.NORM.INV(Random!D39,20,15),1))</f>
         <v>Enter Name</v>
       </c>
-      <c r="D29" s="150" t="s">
+      <c r="D29" s="157" t="s">
         <v>44</v>
       </c>
-      <c r="E29" s="151"/>
-      <c r="F29" s="151"/>
-      <c r="G29" s="151"/>
-      <c r="H29" s="152"/>
+      <c r="E29" s="158"/>
+      <c r="F29" s="158"/>
+      <c r="G29" s="158"/>
+      <c r="H29" s="159"/>
       <c r="AK29" s="43">
         <f t="shared" si="1"/>
         <v>8195</v>
@@ -7581,11 +7532,11 @@
         <f>IF(D$2="Your Name Here","Enter Name",ROUND(_xlfn.NORM.INV(Random!D40,20,15),1))</f>
         <v>Enter Name</v>
       </c>
-      <c r="D30" s="153"/>
-      <c r="E30" s="154"/>
-      <c r="F30" s="154"/>
-      <c r="G30" s="154"/>
-      <c r="H30" s="155"/>
+      <c r="D30" s="160"/>
+      <c r="E30" s="161"/>
+      <c r="F30" s="161"/>
+      <c r="G30" s="161"/>
+      <c r="H30" s="162"/>
       <c r="AK30" s="43">
         <f t="shared" si="1"/>
         <v>6420</v>
@@ -7600,11 +7551,11 @@
         <f>IF(D$2="Your Name Here","Enter Name",ROUND(_xlfn.NORM.INV(Random!D41,20,15),1))</f>
         <v>Enter Name</v>
       </c>
-      <c r="D31" s="153"/>
-      <c r="E31" s="154"/>
-      <c r="F31" s="154"/>
-      <c r="G31" s="154"/>
-      <c r="H31" s="155"/>
+      <c r="D31" s="160"/>
+      <c r="E31" s="161"/>
+      <c r="F31" s="161"/>
+      <c r="G31" s="161"/>
+      <c r="H31" s="162"/>
       <c r="Q31" s="43" t="b">
         <f ca="1">IFERROR(OR(P32:P35),FALSE)</f>
         <v>0</v>
@@ -7623,11 +7574,11 @@
         <f>IF(D$2="Your Name Here","Enter Name",ROUND(_xlfn.NORM.INV(Random!D42,20,15),1))</f>
         <v>Enter Name</v>
       </c>
-      <c r="D32" s="153"/>
-      <c r="E32" s="154"/>
-      <c r="F32" s="154"/>
-      <c r="G32" s="154"/>
-      <c r="H32" s="155"/>
+      <c r="D32" s="160"/>
+      <c r="E32" s="161"/>
+      <c r="F32" s="161"/>
+      <c r="G32" s="161"/>
+      <c r="H32" s="162"/>
       <c r="L32" s="43" t="b">
         <f ca="1">IFERROR(OR(K33:K35),FALSE)</f>
         <v>0</v>
@@ -7654,11 +7605,11 @@
         <f>IF(D$2="Your Name Here","Enter Name",ROUND(_xlfn.NORM.INV(Random!D43,20,15),1))</f>
         <v>Enter Name</v>
       </c>
-      <c r="D33" s="153"/>
-      <c r="E33" s="154"/>
-      <c r="F33" s="154"/>
-      <c r="G33" s="154"/>
-      <c r="H33" s="155"/>
+      <c r="D33" s="160"/>
+      <c r="E33" s="161"/>
+      <c r="F33" s="161"/>
+      <c r="G33" s="161"/>
+      <c r="H33" s="162"/>
       <c r="K33" s="43" t="e">
         <f ca="1">SUBSTITUTE(SUBSTITUTE(_xlfn.FORMULATEXT('Water Quality'!G11), " ",""),"$","") = "=FREQUENCY(B:B,E11:E20)"</f>
         <v>#N/A</v>
@@ -7685,11 +7636,11 @@
         <f>IF(D$2="Your Name Here","Enter Name",ROUND(_xlfn.NORM.INV(Random!D44,20,15),1))</f>
         <v>Enter Name</v>
       </c>
-      <c r="D34" s="153"/>
-      <c r="E34" s="154"/>
-      <c r="F34" s="154"/>
-      <c r="G34" s="154"/>
-      <c r="H34" s="155"/>
+      <c r="D34" s="160"/>
+      <c r="E34" s="161"/>
+      <c r="F34" s="161"/>
+      <c r="G34" s="161"/>
+      <c r="H34" s="162"/>
       <c r="K34" s="43" t="e">
         <f ca="1">SUBSTITUTE(SUBSTITUTE(_xlfn.FORMULATEXT('Water Quality'!G11), " ",""),"$","") = "=FREQUENCY(B2:B103,E11:E20)"</f>
         <v>#N/A</v>
@@ -7712,11 +7663,11 @@
         <f>IF(D$2="Your Name Here","Enter Name",ROUND(_xlfn.NORM.INV(Random!D45,20,15),1))</f>
         <v>Enter Name</v>
       </c>
-      <c r="D35" s="153"/>
-      <c r="E35" s="154"/>
-      <c r="F35" s="154"/>
-      <c r="G35" s="154"/>
-      <c r="H35" s="155"/>
+      <c r="D35" s="160"/>
+      <c r="E35" s="161"/>
+      <c r="F35" s="161"/>
+      <c r="G35" s="161"/>
+      <c r="H35" s="162"/>
       <c r="K35" s="43" t="e">
         <f ca="1">SUBSTITUTE(SUBSTITUTE(_xlfn.FORMULATEXT('Water Quality'!G11), " ",""),"$","") = "=FREQUENCY(Difference_in_water_quality,E11:E20)"</f>
         <v>#N/A</v>
@@ -7739,17 +7690,17 @@
         <f>IF(D$2="Your Name Here","Enter Name",ROUND(_xlfn.NORM.INV(Random!D46,20,15),1))</f>
         <v>Enter Name</v>
       </c>
-      <c r="D36" s="153"/>
-      <c r="E36" s="154"/>
-      <c r="F36" s="154"/>
-      <c r="G36" s="154"/>
-      <c r="H36" s="155"/>
+      <c r="D36" s="160"/>
+      <c r="E36" s="161"/>
+      <c r="F36" s="161"/>
+      <c r="G36" s="161"/>
+      <c r="H36" s="162"/>
       <c r="K36" s="43" t="b">
         <f>'Water Quality'!G11=Solution!G11</f>
         <v>1</v>
       </c>
       <c r="L36" s="43" t="b">
-        <f t="shared" ref="L36:L46" ca="1" si="5">OR(L$33,K36)</f>
+        <f t="shared" ref="L36:L46" ca="1" si="4">OR(L$33,K36)</f>
         <v>1</v>
       </c>
       <c r="M36" s="43" t="b">
@@ -7761,7 +7712,7 @@
         <v>#DIV/0!</v>
       </c>
       <c r="Q36" s="43" t="e">
-        <f t="shared" ref="Q36:Q46" si="6">OR(P36,Q$32)</f>
+        <f t="shared" ref="Q36:Q46" si="5">OR(P36,Q$32)</f>
         <v>#DIV/0!</v>
       </c>
       <c r="R36" s="43" t="e">
@@ -7782,21 +7733,21 @@
         <f>IF(D$2="Your Name Here","Enter Name",ROUND(_xlfn.NORM.INV(Random!D47,20,15),1))</f>
         <v>Enter Name</v>
       </c>
-      <c r="D37" s="153"/>
-      <c r="E37" s="154"/>
-      <c r="F37" s="154"/>
-      <c r="G37" s="154"/>
-      <c r="H37" s="155"/>
+      <c r="D37" s="160"/>
+      <c r="E37" s="161"/>
+      <c r="F37" s="161"/>
+      <c r="G37" s="161"/>
+      <c r="H37" s="162"/>
       <c r="K37" s="43" t="b">
         <f>'Water Quality'!G12=Solution!G12</f>
         <v>1</v>
       </c>
       <c r="L37" s="43" t="b">
-        <f t="shared" ca="1" si="5"/>
+        <f t="shared" ca="1" si="4"/>
         <v>1</v>
       </c>
       <c r="M37" s="43" t="b">
-        <f t="shared" ref="M37:M46" ca="1" si="7">AND(L$32,K37)</f>
+        <f t="shared" ref="M37:M46" ca="1" si="6">AND(L$32,K37)</f>
         <v>0</v>
       </c>
       <c r="P37" s="43" t="e">
@@ -7804,11 +7755,11 @@
         <v>#DIV/0!</v>
       </c>
       <c r="Q37" s="43" t="e">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>#DIV/0!</v>
       </c>
       <c r="R37" s="43" t="e">
-        <f t="shared" ref="R37:R46" ca="1" si="8">AND(Q$31,P37)</f>
+        <f t="shared" ref="R37:R46" ca="1" si="7">AND(Q$31,P37)</f>
         <v>#DIV/0!</v>
       </c>
       <c r="AK37" s="43">
@@ -7825,21 +7776,21 @@
         <f>IF(D$2="Your Name Here","Enter Name",ROUND(_xlfn.NORM.INV(Random!D48,20,15),1))</f>
         <v>Enter Name</v>
       </c>
-      <c r="D38" s="153"/>
-      <c r="E38" s="154"/>
-      <c r="F38" s="154"/>
-      <c r="G38" s="154"/>
-      <c r="H38" s="155"/>
+      <c r="D38" s="160"/>
+      <c r="E38" s="161"/>
+      <c r="F38" s="161"/>
+      <c r="G38" s="161"/>
+      <c r="H38" s="162"/>
       <c r="K38" s="43" t="b">
         <f>'Water Quality'!G13=Solution!G13</f>
         <v>1</v>
       </c>
       <c r="L38" s="43" t="b">
-        <f t="shared" ca="1" si="5"/>
+        <f t="shared" ca="1" si="4"/>
         <v>1</v>
       </c>
       <c r="M38" s="43" t="b">
-        <f t="shared" ca="1" si="7"/>
+        <f t="shared" ca="1" si="6"/>
         <v>0</v>
       </c>
       <c r="P38" s="43" t="e">
@@ -7847,11 +7798,11 @@
         <v>#DIV/0!</v>
       </c>
       <c r="Q38" s="43" t="e">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>#DIV/0!</v>
       </c>
       <c r="R38" s="43" t="e">
-        <f t="shared" ca="1" si="8"/>
+        <f t="shared" ca="1" si="7"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AK38" s="43">
@@ -7868,21 +7819,21 @@
         <f>IF(D$2="Your Name Here","Enter Name",ROUND(_xlfn.NORM.INV(Random!D49,20,15),1))</f>
         <v>Enter Name</v>
       </c>
-      <c r="D39" s="153"/>
-      <c r="E39" s="154"/>
-      <c r="F39" s="154"/>
-      <c r="G39" s="154"/>
-      <c r="H39" s="155"/>
+      <c r="D39" s="160"/>
+      <c r="E39" s="161"/>
+      <c r="F39" s="161"/>
+      <c r="G39" s="161"/>
+      <c r="H39" s="162"/>
       <c r="K39" s="43" t="b">
         <f>'Water Quality'!G14=Solution!G14</f>
         <v>1</v>
       </c>
       <c r="L39" s="43" t="b">
-        <f t="shared" ca="1" si="5"/>
+        <f t="shared" ca="1" si="4"/>
         <v>1</v>
       </c>
       <c r="M39" s="43" t="b">
-        <f t="shared" ca="1" si="7"/>
+        <f t="shared" ca="1" si="6"/>
         <v>0</v>
       </c>
       <c r="P39" s="43" t="e">
@@ -7890,11 +7841,11 @@
         <v>#DIV/0!</v>
       </c>
       <c r="Q39" s="43" t="e">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>#DIV/0!</v>
       </c>
       <c r="R39" s="43" t="e">
-        <f t="shared" ca="1" si="8"/>
+        <f t="shared" ca="1" si="7"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AK39" s="43">
@@ -7911,21 +7862,21 @@
         <f>IF(D$2="Your Name Here","Enter Name",ROUND(_xlfn.NORM.INV(Random!D50,20,15),1))</f>
         <v>Enter Name</v>
       </c>
-      <c r="D40" s="156"/>
-      <c r="E40" s="157"/>
-      <c r="F40" s="157"/>
-      <c r="G40" s="157"/>
-      <c r="H40" s="158"/>
+      <c r="D40" s="163"/>
+      <c r="E40" s="164"/>
+      <c r="F40" s="164"/>
+      <c r="G40" s="164"/>
+      <c r="H40" s="165"/>
       <c r="K40" s="43" t="b">
         <f>'Water Quality'!G15=Solution!G15</f>
         <v>1</v>
       </c>
       <c r="L40" s="43" t="b">
-        <f t="shared" ca="1" si="5"/>
+        <f t="shared" ca="1" si="4"/>
         <v>1</v>
       </c>
       <c r="M40" s="43" t="b">
-        <f t="shared" ca="1" si="7"/>
+        <f t="shared" ca="1" si="6"/>
         <v>0</v>
       </c>
       <c r="P40" s="43" t="e">
@@ -7933,11 +7884,11 @@
         <v>#DIV/0!</v>
       </c>
       <c r="Q40" s="43" t="e">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>#DIV/0!</v>
       </c>
       <c r="R40" s="43" t="e">
-        <f t="shared" ca="1" si="8"/>
+        <f t="shared" ca="1" si="7"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AK40" s="43">
@@ -7959,11 +7910,11 @@
         <v>1</v>
       </c>
       <c r="L41" s="43" t="b">
-        <f t="shared" ca="1" si="5"/>
+        <f t="shared" ca="1" si="4"/>
         <v>1</v>
       </c>
       <c r="M41" s="43" t="b">
-        <f t="shared" ca="1" si="7"/>
+        <f t="shared" ca="1" si="6"/>
         <v>0</v>
       </c>
       <c r="P41" s="43" t="e">
@@ -7971,11 +7922,11 @@
         <v>#DIV/0!</v>
       </c>
       <c r="Q41" s="43" t="e">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>#DIV/0!</v>
       </c>
       <c r="R41" s="43" t="e">
-        <f t="shared" ca="1" si="8"/>
+        <f t="shared" ca="1" si="7"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AK41" s="43">
@@ -7997,11 +7948,11 @@
         <v>1</v>
       </c>
       <c r="L42" s="43" t="b">
-        <f t="shared" ca="1" si="5"/>
+        <f t="shared" ca="1" si="4"/>
         <v>1</v>
       </c>
       <c r="M42" s="43" t="b">
-        <f t="shared" ca="1" si="7"/>
+        <f t="shared" ca="1" si="6"/>
         <v>0</v>
       </c>
       <c r="P42" s="43" t="e">
@@ -8009,11 +7960,11 @@
         <v>#DIV/0!</v>
       </c>
       <c r="Q42" s="43" t="e">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>#DIV/0!</v>
       </c>
       <c r="R42" s="43" t="e">
-        <f t="shared" ca="1" si="8"/>
+        <f t="shared" ca="1" si="7"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AK42" s="43">
@@ -8035,11 +7986,11 @@
         <v>1</v>
       </c>
       <c r="L43" s="43" t="b">
-        <f t="shared" ca="1" si="5"/>
+        <f t="shared" ca="1" si="4"/>
         <v>1</v>
       </c>
       <c r="M43" s="43" t="b">
-        <f t="shared" ca="1" si="7"/>
+        <f t="shared" ca="1" si="6"/>
         <v>0</v>
       </c>
       <c r="P43" s="43" t="e">
@@ -8047,11 +7998,11 @@
         <v>#DIV/0!</v>
       </c>
       <c r="Q43" s="43" t="e">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>#DIV/0!</v>
       </c>
       <c r="R43" s="43" t="e">
-        <f t="shared" ca="1" si="8"/>
+        <f t="shared" ca="1" si="7"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AK43" s="43">
@@ -8073,11 +8024,11 @@
         <v>1</v>
       </c>
       <c r="L44" s="43" t="b">
-        <f t="shared" ca="1" si="5"/>
+        <f t="shared" ca="1" si="4"/>
         <v>1</v>
       </c>
       <c r="M44" s="43" t="b">
-        <f t="shared" ca="1" si="7"/>
+        <f t="shared" ca="1" si="6"/>
         <v>0</v>
       </c>
       <c r="P44" s="43" t="e">
@@ -8085,11 +8036,11 @@
         <v>#DIV/0!</v>
       </c>
       <c r="Q44" s="43" t="e">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>#DIV/0!</v>
       </c>
       <c r="R44" s="43" t="e">
-        <f t="shared" ca="1" si="8"/>
+        <f t="shared" ca="1" si="7"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AK44" s="43">
@@ -8111,11 +8062,11 @@
         <v>1</v>
       </c>
       <c r="L45" s="43" t="b">
-        <f t="shared" ca="1" si="5"/>
+        <f t="shared" ca="1" si="4"/>
         <v>1</v>
       </c>
       <c r="M45" s="43" t="b">
-        <f t="shared" ca="1" si="7"/>
+        <f t="shared" ca="1" si="6"/>
         <v>0</v>
       </c>
       <c r="P45" s="43" t="e">
@@ -8123,11 +8074,11 @@
         <v>#DIV/0!</v>
       </c>
       <c r="Q45" s="43" t="e">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>#DIV/0!</v>
       </c>
       <c r="R45" s="43" t="e">
-        <f t="shared" ca="1" si="8"/>
+        <f t="shared" ca="1" si="7"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AK45" s="43">
@@ -8149,11 +8100,11 @@
         <v>1</v>
       </c>
       <c r="L46" s="43" t="b">
-        <f t="shared" ca="1" si="5"/>
+        <f t="shared" ca="1" si="4"/>
         <v>1</v>
       </c>
       <c r="M46" s="43" t="b">
-        <f t="shared" ca="1" si="7"/>
+        <f t="shared" ca="1" si="6"/>
         <v>0</v>
       </c>
       <c r="P46" s="43" t="e">
@@ -8161,11 +8112,11 @@
         <v>#DIV/0!</v>
       </c>
       <c r="Q46" s="43" t="e">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>#DIV/0!</v>
       </c>
       <c r="R46" s="43" t="e">
-        <f t="shared" ca="1" si="8"/>
+        <f t="shared" ca="1" si="7"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AK46" s="43">
@@ -8469,7 +8420,7 @@
     </row>
     <row r="68" spans="1:37">
       <c r="A68" s="46">
-        <f t="shared" ref="A68:A103" si="9">A67+1</f>
+        <f t="shared" ref="A68:A103" si="8">A67+1</f>
         <v>67</v>
       </c>
       <c r="B68" s="46" t="str">
@@ -8477,13 +8428,13 @@
         <v>Enter Name</v>
       </c>
       <c r="AK68" s="43">
-        <f t="shared" ref="AK68:AK103" si="10">MOD(AK67*1103515245 + 12345,9172)</f>
+        <f t="shared" ref="AK68:AK103" si="9">MOD(AK67*1103515245 + 12345,9172)</f>
         <v>8390</v>
       </c>
     </row>
     <row r="69" spans="1:37">
       <c r="A69" s="46">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>68</v>
       </c>
       <c r="B69" s="46" t="str">
@@ -8491,13 +8442,13 @@
         <v>Enter Name</v>
       </c>
       <c r="AK69" s="43">
-        <f t="shared" si="10"/>
+        <f t="shared" si="9"/>
         <v>4007</v>
       </c>
     </row>
     <row r="70" spans="1:37">
       <c r="A70" s="46">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>69</v>
       </c>
       <c r="B70" s="46" t="str">
@@ -8505,13 +8456,13 @@
         <v>Enter Name</v>
       </c>
       <c r="AK70" s="43">
-        <f t="shared" si="10"/>
+        <f t="shared" si="9"/>
         <v>4764</v>
       </c>
     </row>
     <row r="71" spans="1:37">
       <c r="A71" s="46">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>70</v>
       </c>
       <c r="B71" s="46" t="str">
@@ -8519,13 +8470,13 @@
         <v>Enter Name</v>
       </c>
       <c r="AK71" s="43">
-        <f t="shared" si="10"/>
+        <f t="shared" si="9"/>
         <v>3769</v>
       </c>
     </row>
     <row r="72" spans="1:37">
       <c r="A72" s="46">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>71</v>
       </c>
       <c r="B72" s="46" t="str">
@@ -8533,13 +8484,13 @@
         <v>Enter Name</v>
       </c>
       <c r="AK72" s="43">
-        <f t="shared" si="10"/>
+        <f t="shared" si="9"/>
         <v>1030</v>
       </c>
     </row>
     <row r="73" spans="1:37">
       <c r="A73" s="46">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>72</v>
       </c>
       <c r="B73" s="46" t="str">
@@ -8547,13 +8498,13 @@
         <v>Enter Name</v>
       </c>
       <c r="AK73" s="43">
-        <f t="shared" si="10"/>
+        <f t="shared" si="9"/>
         <v>4303</v>
       </c>
     </row>
     <row r="74" spans="1:37">
       <c r="A74" s="46">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>73</v>
       </c>
       <c r="B74" s="46" t="str">
@@ -8561,13 +8512,13 @@
         <v>Enter Name</v>
       </c>
       <c r="AK74" s="43">
-        <f t="shared" si="10"/>
+        <f t="shared" si="9"/>
         <v>7404</v>
       </c>
     </row>
     <row r="75" spans="1:37">
       <c r="A75" s="46">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>74</v>
       </c>
       <c r="B75" s="46" t="str">
@@ -8575,13 +8526,13 @@
         <v>Enter Name</v>
       </c>
       <c r="AK75" s="43">
-        <f t="shared" si="10"/>
+        <f t="shared" si="9"/>
         <v>4261</v>
       </c>
     </row>
     <row r="76" spans="1:37">
       <c r="A76" s="46">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>75</v>
       </c>
       <c r="B76" s="46" t="str">
@@ -8589,13 +8540,13 @@
         <v>Enter Name</v>
       </c>
       <c r="AK76" s="43">
-        <f t="shared" si="10"/>
+        <f t="shared" si="9"/>
         <v>5666</v>
       </c>
     </row>
     <row r="77" spans="1:37">
       <c r="A77" s="46">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>76</v>
       </c>
       <c r="B77" s="46" t="str">
@@ -8603,13 +8554,13 @@
         <v>Enter Name</v>
       </c>
       <c r="AK77" s="43">
-        <f t="shared" si="10"/>
+        <f t="shared" si="9"/>
         <v>39</v>
       </c>
     </row>
     <row r="78" spans="1:37">
       <c r="A78" s="46">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>77</v>
       </c>
       <c r="B78" s="46" t="str">
@@ -8617,13 +8568,13 @@
         <v>Enter Name</v>
       </c>
       <c r="AK78" s="43">
-        <f t="shared" si="10"/>
+        <f t="shared" si="9"/>
         <v>856</v>
       </c>
     </row>
     <row r="79" spans="1:37">
       <c r="A79" s="46">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>78</v>
       </c>
       <c r="B79" s="46" t="str">
@@ -8631,13 +8582,13 @@
         <v>Enter Name</v>
       </c>
       <c r="AK79" s="43">
-        <f t="shared" si="10"/>
+        <f t="shared" si="9"/>
         <v>7585</v>
       </c>
     </row>
     <row r="80" spans="1:37">
       <c r="A80" s="46">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>79</v>
       </c>
       <c r="B80" s="46" t="str">
@@ -8645,13 +8596,13 @@
         <v>Enter Name</v>
       </c>
       <c r="AK80" s="43">
-        <f t="shared" si="10"/>
+        <f t="shared" si="9"/>
         <v>4326</v>
       </c>
     </row>
     <row r="81" spans="1:37">
       <c r="A81" s="46">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>80</v>
       </c>
       <c r="B81" s="46" t="str">
@@ -8659,13 +8610,13 @@
         <v>Enter Name</v>
       </c>
       <c r="AK81" s="43">
-        <f t="shared" si="10"/>
+        <f t="shared" si="9"/>
         <v>7919</v>
       </c>
     </row>
     <row r="82" spans="1:37">
       <c r="A82" s="46">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>81</v>
       </c>
       <c r="B82" s="46" t="str">
@@ -8673,13 +8624,13 @@
         <v>Enter Name</v>
       </c>
       <c r="AK82" s="43">
-        <f t="shared" si="10"/>
+        <f t="shared" si="9"/>
         <v>240</v>
       </c>
     </row>
     <row r="83" spans="1:37">
       <c r="A83" s="46">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>82</v>
       </c>
       <c r="B83" s="46" t="str">
@@ -8687,13 +8638,13 @@
         <v>Enter Name</v>
       </c>
       <c r="AK83" s="43">
-        <f t="shared" si="10"/>
+        <f t="shared" si="9"/>
         <v>6553</v>
       </c>
     </row>
     <row r="84" spans="1:37">
       <c r="A84" s="46">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>83</v>
       </c>
       <c r="B84" s="46" t="str">
@@ -8701,13 +8652,13 @@
         <v>Enter Name</v>
       </c>
       <c r="AK84" s="43">
-        <f t="shared" si="10"/>
+        <f t="shared" si="9"/>
         <v>3550</v>
       </c>
     </row>
     <row r="85" spans="1:37">
       <c r="A85" s="46">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>84</v>
       </c>
       <c r="B85" s="46" t="str">
@@ -8715,13 +8666,13 @@
         <v>Enter Name</v>
       </c>
       <c r="AK85" s="43">
-        <f t="shared" si="10"/>
+        <f t="shared" si="9"/>
         <v>7691</v>
       </c>
     </row>
     <row r="86" spans="1:37">
       <c r="A86" s="46">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>85</v>
       </c>
       <c r="B86" s="46" t="str">
@@ -8729,13 +8680,13 @@
         <v>Enter Name</v>
       </c>
       <c r="AK86" s="43">
-        <f t="shared" si="10"/>
+        <f t="shared" si="9"/>
         <v>3908</v>
       </c>
     </row>
     <row r="87" spans="1:37">
       <c r="A87" s="46">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>86</v>
       </c>
       <c r="B87" s="46" t="str">
@@ -8743,13 +8694,13 @@
         <v>Enter Name</v>
       </c>
       <c r="AK87" s="43">
-        <f t="shared" si="10"/>
+        <f t="shared" si="9"/>
         <v>8529</v>
       </c>
     </row>
     <row r="88" spans="1:37">
       <c r="A88" s="46">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>87</v>
       </c>
       <c r="B88" s="46" t="str">
@@ -8757,13 +8708,13 @@
         <v>Enter Name</v>
       </c>
       <c r="AK88" s="43">
-        <f t="shared" si="10"/>
+        <f t="shared" si="9"/>
         <v>2334</v>
       </c>
     </row>
     <row r="89" spans="1:37">
       <c r="A89" s="46">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>88</v>
       </c>
       <c r="B89" s="46" t="str">
@@ -8771,13 +8722,13 @@
         <v>Enter Name</v>
       </c>
       <c r="AK89" s="43">
-        <f t="shared" si="10"/>
+        <f t="shared" si="9"/>
         <v>2795</v>
       </c>
     </row>
     <row r="90" spans="1:37">
       <c r="A90" s="46">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>89</v>
       </c>
       <c r="B90" s="46" t="str">
@@ -8785,13 +8736,13 @@
         <v>Enter Name</v>
       </c>
       <c r="AK90" s="43">
-        <f t="shared" si="10"/>
+        <f t="shared" si="9"/>
         <v>8332</v>
       </c>
     </row>
     <row r="91" spans="1:37">
       <c r="A91" s="46">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>90</v>
       </c>
       <c r="B91" s="46" t="str">
@@ -8799,13 +8750,13 @@
         <v>Enter Name</v>
       </c>
       <c r="AK91" s="43">
-        <f t="shared" si="10"/>
+        <f t="shared" si="9"/>
         <v>5101</v>
       </c>
     </row>
     <row r="92" spans="1:37">
       <c r="A92" s="46">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>91</v>
       </c>
       <c r="B92" s="46" t="str">
@@ -8813,13 +8764,13 @@
         <v>Enter Name</v>
       </c>
       <c r="AK92" s="43">
-        <f t="shared" si="10"/>
+        <f t="shared" si="9"/>
         <v>3738</v>
       </c>
     </row>
     <row r="93" spans="1:37">
       <c r="A93" s="46">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>92</v>
       </c>
       <c r="B93" s="46" t="str">
@@ -8827,13 +8778,13 @@
         <v>Enter Name</v>
       </c>
       <c r="AK93" s="43">
-        <f t="shared" si="10"/>
+        <f t="shared" si="9"/>
         <v>1931</v>
       </c>
     </row>
     <row r="94" spans="1:37">
       <c r="A94" s="46">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>93</v>
       </c>
       <c r="B94" s="46" t="str">
@@ -8841,13 +8792,13 @@
         <v>Enter Name</v>
       </c>
       <c r="AK94" s="43">
-        <f t="shared" si="10"/>
+        <f t="shared" si="9"/>
         <v>5336</v>
       </c>
     </row>
     <row r="95" spans="1:37">
       <c r="A95" s="46">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>94</v>
       </c>
       <c r="B95" s="46" t="str">
@@ -8855,13 +8806,13 @@
         <v>Enter Name</v>
       </c>
       <c r="AK95" s="43">
-        <f t="shared" si="10"/>
+        <f t="shared" si="9"/>
         <v>3417</v>
       </c>
     </row>
     <row r="96" spans="1:37">
       <c r="A96" s="46">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>95</v>
       </c>
       <c r="B96" s="46" t="str">
@@ -8869,13 +8820,13 @@
         <v>Enter Name</v>
       </c>
       <c r="AK96" s="43">
-        <f t="shared" si="10"/>
+        <f t="shared" si="9"/>
         <v>8302</v>
       </c>
     </row>
     <row r="97" spans="1:37">
       <c r="A97" s="46">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>96</v>
       </c>
       <c r="B97" s="46" t="str">
@@ -8883,13 +8834,13 @@
         <v>Enter Name</v>
       </c>
       <c r="AK97" s="43">
-        <f t="shared" si="10"/>
+        <f t="shared" si="9"/>
         <v>1239</v>
       </c>
     </row>
     <row r="98" spans="1:37">
       <c r="A98" s="46">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>97</v>
       </c>
       <c r="B98" s="46" t="str">
@@ -8897,13 +8848,13 @@
         <v>Enter Name</v>
       </c>
       <c r="AK98" s="43">
-        <f t="shared" si="10"/>
+        <f t="shared" si="9"/>
         <v>8584</v>
       </c>
     </row>
     <row r="99" spans="1:37">
       <c r="A99" s="46">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>98</v>
       </c>
       <c r="B99" s="46" t="str">
@@ -8911,13 +8862,13 @@
         <v>Enter Name</v>
       </c>
       <c r="AK99" s="43">
-        <f t="shared" si="10"/>
+        <f t="shared" si="9"/>
         <v>6357</v>
       </c>
     </row>
     <row r="100" spans="1:37">
       <c r="A100" s="46">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>99</v>
       </c>
       <c r="B100" s="46" t="str">
@@ -8925,13 +8876,13 @@
         <v>Enter Name</v>
       </c>
       <c r="AK100" s="43">
-        <f t="shared" si="10"/>
+        <f t="shared" si="9"/>
         <v>1554</v>
       </c>
     </row>
     <row r="101" spans="1:37">
       <c r="A101" s="46">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>100</v>
       </c>
       <c r="B101" s="46" t="str">
@@ -8939,13 +8890,13 @@
         <v>Enter Name</v>
       </c>
       <c r="AK101" s="43">
-        <f t="shared" si="10"/>
+        <f t="shared" si="9"/>
         <v>3275</v>
       </c>
     </row>
     <row r="102" spans="1:37">
       <c r="A102" s="46">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>101</v>
       </c>
       <c r="B102" s="46" t="str">
@@ -8953,13 +8904,13 @@
         <v>Enter Name</v>
       </c>
       <c r="AK102" s="43">
-        <f t="shared" si="10"/>
+        <f t="shared" si="9"/>
         <v>5920</v>
       </c>
     </row>
     <row r="103" spans="1:37">
       <c r="A103" s="46">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>102</v>
       </c>
       <c r="B103" s="46" t="str">
@@ -8967,12 +8918,12 @@
         <v>Enter Name</v>
       </c>
       <c r="AK103" s="43">
-        <f t="shared" si="10"/>
+        <f t="shared" si="9"/>
         <v>941</v>
       </c>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="2lm+KzlfhBBr/oqMv6QFd1DRMVKg4lvdlQU9TfWvAf8oMfVAmia3Xj8EmGsuo2yD4WGbP1hPcIkVVhxKrjyOqA==" saltValue="1HQzKTEeJ8xP3itMRDb9IQ==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="dDUi1CJseNMyE8aGANYgAz66Evc8HOEXri92JnAymyteplit9tNtJI27MSfmOFS6Bg5n3iXWmq0g81nO1Dqsvg==" saltValue="E23xxHiqqRs5AcThDrYNVw==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
   <mergeCells count="9">
     <mergeCell ref="J10:O23"/>
     <mergeCell ref="D24:H27"/>
@@ -19482,511 +19433,511 @@
     <row r="2" spans="1:1">
       <c r="A2" s="3">
         <f ca="1">ROUND(NORMINV(RAND(),68,3.75),1)</f>
-        <v>61.5</v>
+        <v>67</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="3">
         <f t="shared" ref="A3:A66" ca="1" si="0">ROUND(NORMINV(RAND(),68,3.75),1)</f>
-        <v>71.099999999999994</v>
+        <v>62.4</v>
       </c>
     </row>
     <row r="4" spans="1:1">
       <c r="A4" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>68.400000000000006</v>
+        <v>69.400000000000006</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>69.099999999999994</v>
+        <v>65.599999999999994</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>73.400000000000006</v>
+        <v>73.099999999999994</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>67</v>
+        <v>64.400000000000006</v>
       </c>
     </row>
     <row r="8" spans="1:1">
       <c r="A8" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>70.7</v>
+        <v>71.400000000000006</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>69.8</v>
+        <v>71.7</v>
       </c>
     </row>
     <row r="10" spans="1:1">
       <c r="A10" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>71.099999999999994</v>
+        <v>67.7</v>
       </c>
     </row>
     <row r="11" spans="1:1">
       <c r="A11" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>73.7</v>
+        <v>72</v>
       </c>
     </row>
     <row r="12" spans="1:1">
       <c r="A12" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>65.5</v>
+        <v>68.3</v>
       </c>
     </row>
     <row r="13" spans="1:1">
       <c r="A13" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>62.7</v>
+        <v>64.400000000000006</v>
       </c>
     </row>
     <row r="14" spans="1:1">
       <c r="A14" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>65.7</v>
+        <v>68.3</v>
       </c>
     </row>
     <row r="15" spans="1:1">
       <c r="A15" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>67.900000000000006</v>
+        <v>66.400000000000006</v>
       </c>
     </row>
     <row r="16" spans="1:1">
       <c r="A16" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>69.3</v>
+        <v>75.2</v>
       </c>
     </row>
     <row r="17" spans="1:1">
       <c r="A17" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>67.599999999999994</v>
+        <v>54.9</v>
       </c>
     </row>
     <row r="18" spans="1:1">
       <c r="A18" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>64.099999999999994</v>
+        <v>63.8</v>
       </c>
     </row>
     <row r="19" spans="1:1">
       <c r="A19" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>69.7</v>
+        <v>65</v>
       </c>
     </row>
     <row r="20" spans="1:1">
       <c r="A20" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>69.5</v>
+        <v>68.2</v>
       </c>
     </row>
     <row r="21" spans="1:1">
       <c r="A21" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>71.400000000000006</v>
+        <v>61.3</v>
       </c>
     </row>
     <row r="22" spans="1:1">
       <c r="A22" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>68.099999999999994</v>
+        <v>71.099999999999994</v>
       </c>
     </row>
     <row r="23" spans="1:1">
       <c r="A23" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>64.599999999999994</v>
+        <v>69.599999999999994</v>
       </c>
     </row>
     <row r="24" spans="1:1">
       <c r="A24" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>72.599999999999994</v>
+        <v>65.400000000000006</v>
       </c>
     </row>
     <row r="25" spans="1:1">
       <c r="A25" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>67.400000000000006</v>
+        <v>68</v>
       </c>
     </row>
     <row r="26" spans="1:1">
       <c r="A26" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>64.900000000000006</v>
+        <v>67.099999999999994</v>
       </c>
     </row>
     <row r="27" spans="1:1">
       <c r="A27" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>66.8</v>
+        <v>71.400000000000006</v>
       </c>
     </row>
     <row r="28" spans="1:1">
       <c r="A28" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>64.5</v>
+        <v>69.400000000000006</v>
       </c>
     </row>
     <row r="29" spans="1:1">
       <c r="A29" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>70.2</v>
+        <v>65.7</v>
       </c>
     </row>
     <row r="30" spans="1:1">
       <c r="A30" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>69.2</v>
+        <v>69.7</v>
       </c>
     </row>
     <row r="31" spans="1:1">
       <c r="A31" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>67.099999999999994</v>
+        <v>66</v>
       </c>
     </row>
     <row r="32" spans="1:1">
       <c r="A32" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>68.8</v>
+        <v>69.5</v>
       </c>
     </row>
     <row r="33" spans="1:1">
       <c r="A33" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>65.2</v>
+        <v>73.3</v>
       </c>
     </row>
     <row r="34" spans="1:1">
       <c r="A34" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>58.9</v>
+        <v>69.599999999999994</v>
       </c>
     </row>
     <row r="35" spans="1:1">
       <c r="A35" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>68.8</v>
+        <v>68.099999999999994</v>
       </c>
     </row>
     <row r="36" spans="1:1">
       <c r="A36" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>63.2</v>
+        <v>73</v>
       </c>
     </row>
     <row r="37" spans="1:1">
       <c r="A37" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>69.5</v>
+        <v>70.900000000000006</v>
       </c>
     </row>
     <row r="38" spans="1:1">
       <c r="A38" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>73.8</v>
+        <v>66.5</v>
       </c>
     </row>
     <row r="39" spans="1:1">
       <c r="A39" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>69.400000000000006</v>
+        <v>74.900000000000006</v>
       </c>
     </row>
     <row r="40" spans="1:1">
       <c r="A40" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>72.3</v>
+        <v>72</v>
       </c>
     </row>
     <row r="41" spans="1:1">
       <c r="A41" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>72.8</v>
+        <v>62.4</v>
       </c>
     </row>
     <row r="42" spans="1:1">
       <c r="A42" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>66.900000000000006</v>
+        <v>68.400000000000006</v>
       </c>
     </row>
     <row r="43" spans="1:1">
       <c r="A43" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>65.900000000000006</v>
+        <v>69.599999999999994</v>
       </c>
     </row>
     <row r="44" spans="1:1">
       <c r="A44" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>64.7</v>
+        <v>77.2</v>
       </c>
     </row>
     <row r="45" spans="1:1">
       <c r="A45" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>61.4</v>
+        <v>69</v>
       </c>
     </row>
     <row r="46" spans="1:1">
       <c r="A46" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>67.5</v>
+        <v>67.8</v>
       </c>
     </row>
     <row r="47" spans="1:1">
       <c r="A47" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>68.099999999999994</v>
+        <v>75.900000000000006</v>
       </c>
     </row>
     <row r="48" spans="1:1">
       <c r="A48" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>68.8</v>
+        <v>67.900000000000006</v>
       </c>
     </row>
     <row r="49" spans="1:1">
       <c r="A49" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>73.2</v>
+        <v>66.3</v>
       </c>
     </row>
     <row r="50" spans="1:1">
       <c r="A50" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>66</v>
+        <v>71.900000000000006</v>
       </c>
     </row>
     <row r="51" spans="1:1">
       <c r="A51" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>66.3</v>
+        <v>64.2</v>
       </c>
     </row>
     <row r="52" spans="1:1">
       <c r="A52" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>65</v>
+        <v>67.099999999999994</v>
       </c>
     </row>
     <row r="53" spans="1:1">
       <c r="A53" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>66.900000000000006</v>
+        <v>73.3</v>
       </c>
     </row>
     <row r="54" spans="1:1">
       <c r="A54" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>65.599999999999994</v>
+        <v>69.3</v>
       </c>
     </row>
     <row r="55" spans="1:1">
       <c r="A55" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>67.5</v>
+        <v>61.6</v>
       </c>
     </row>
     <row r="56" spans="1:1">
       <c r="A56" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>70.900000000000006</v>
+        <v>67.8</v>
       </c>
     </row>
     <row r="57" spans="1:1">
       <c r="A57" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>68.400000000000006</v>
+        <v>73.099999999999994</v>
       </c>
     </row>
     <row r="58" spans="1:1">
       <c r="A58" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>69.900000000000006</v>
+        <v>66.2</v>
       </c>
     </row>
     <row r="59" spans="1:1">
       <c r="A59" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>63.9</v>
+        <v>71.599999999999994</v>
       </c>
     </row>
     <row r="60" spans="1:1">
       <c r="A60" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>60.2</v>
+        <v>62.1</v>
       </c>
     </row>
     <row r="61" spans="1:1">
       <c r="A61" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>65.7</v>
+        <v>79.8</v>
       </c>
     </row>
     <row r="62" spans="1:1">
       <c r="A62" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>63.3</v>
+        <v>67.099999999999994</v>
       </c>
     </row>
     <row r="63" spans="1:1">
       <c r="A63" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>75.8</v>
+        <v>67.7</v>
       </c>
     </row>
     <row r="64" spans="1:1">
       <c r="A64" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>68.400000000000006</v>
+        <v>67.3</v>
       </c>
     </row>
     <row r="65" spans="1:1">
       <c r="A65" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>60.3</v>
+        <v>72</v>
       </c>
     </row>
     <row r="66" spans="1:1">
       <c r="A66" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>70.5</v>
+        <v>70.3</v>
       </c>
     </row>
     <row r="67" spans="1:1">
       <c r="A67" s="3">
         <f t="shared" ref="A67:A103" ca="1" si="1">ROUND(NORMINV(RAND(),68,3.75),1)</f>
-        <v>68.3</v>
+        <v>67.5</v>
       </c>
     </row>
     <row r="68" spans="1:1">
       <c r="A68" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>62.8</v>
+        <v>72.3</v>
       </c>
     </row>
     <row r="69" spans="1:1">
       <c r="A69" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>67</v>
+        <v>67.099999999999994</v>
       </c>
     </row>
     <row r="70" spans="1:1">
       <c r="A70" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>68</v>
+        <v>75.5</v>
       </c>
     </row>
     <row r="71" spans="1:1">
       <c r="A71" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>67.8</v>
+        <v>62.8</v>
       </c>
     </row>
     <row r="72" spans="1:1">
       <c r="A72" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>71.400000000000006</v>
+        <v>69.2</v>
       </c>
     </row>
     <row r="73" spans="1:1">
       <c r="A73" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>62.9</v>
+        <v>70.900000000000006</v>
       </c>
     </row>
     <row r="74" spans="1:1">
       <c r="A74" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>73</v>
+        <v>73.3</v>
       </c>
     </row>
     <row r="75" spans="1:1">
       <c r="A75" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>69.3</v>
+        <v>68.3</v>
       </c>
     </row>
     <row r="76" spans="1:1">
       <c r="A76" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>65.5</v>
+        <v>65.2</v>
       </c>
     </row>
     <row r="77" spans="1:1">
       <c r="A77" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>62.8</v>
+        <v>66.900000000000006</v>
       </c>
     </row>
     <row r="78" spans="1:1">
       <c r="A78" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>62.1</v>
+        <v>69.5</v>
       </c>
     </row>
     <row r="79" spans="1:1">
       <c r="A79" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>66.3</v>
+        <v>72.8</v>
       </c>
     </row>
     <row r="80" spans="1:1">
       <c r="A80" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>73.599999999999994</v>
+        <v>73.900000000000006</v>
       </c>
     </row>
     <row r="81" spans="1:1">
       <c r="A81" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>65.3</v>
+        <v>72.2</v>
       </c>
     </row>
     <row r="82" spans="1:1">
       <c r="A82" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>77.3</v>
+        <v>65.2</v>
       </c>
     </row>
     <row r="83" spans="1:1">
       <c r="A83" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>66.3</v>
+        <v>69.900000000000006</v>
       </c>
     </row>
     <row r="84" spans="1:1">
       <c r="A84" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>72.5</v>
+        <v>72.2</v>
       </c>
     </row>
     <row r="85" spans="1:1">
       <c r="A85" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>73.599999999999994</v>
+        <v>63.2</v>
       </c>
     </row>
     <row r="86" spans="1:1">
       <c r="A86" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>67.7</v>
+        <v>63.1</v>
       </c>
     </row>
     <row r="87" spans="1:1">
@@ -19998,97 +19949,97 @@
     <row r="88" spans="1:1">
       <c r="A88" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>64.599999999999994</v>
+        <v>62.1</v>
       </c>
     </row>
     <row r="89" spans="1:1">
       <c r="A89" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>66.8</v>
+        <v>71.400000000000006</v>
       </c>
     </row>
     <row r="90" spans="1:1">
       <c r="A90" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>69.5</v>
+        <v>66.8</v>
       </c>
     </row>
     <row r="91" spans="1:1">
       <c r="A91" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>63.6</v>
+        <v>70.900000000000006</v>
       </c>
     </row>
     <row r="92" spans="1:1">
       <c r="A92" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>69</v>
+        <v>74.3</v>
       </c>
     </row>
     <row r="93" spans="1:1">
       <c r="A93" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>66.8</v>
+        <v>63.9</v>
       </c>
     </row>
     <row r="94" spans="1:1">
       <c r="A94" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>62.6</v>
+        <v>67.3</v>
       </c>
     </row>
     <row r="95" spans="1:1">
       <c r="A95" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>61</v>
+        <v>64.099999999999994</v>
       </c>
     </row>
     <row r="96" spans="1:1">
       <c r="A96" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>65.900000000000006</v>
+        <v>63.7</v>
       </c>
     </row>
     <row r="97" spans="1:1">
       <c r="A97" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>68.599999999999994</v>
+        <v>63.8</v>
       </c>
     </row>
     <row r="98" spans="1:1">
       <c r="A98" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>66.099999999999994</v>
+        <v>69</v>
       </c>
     </row>
     <row r="99" spans="1:1">
       <c r="A99" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>65.400000000000006</v>
+        <v>68.099999999999994</v>
       </c>
     </row>
     <row r="100" spans="1:1">
       <c r="A100" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>69.5</v>
+        <v>67.099999999999994</v>
       </c>
     </row>
     <row r="101" spans="1:1">
       <c r="A101" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>71.8</v>
+        <v>68</v>
       </c>
     </row>
     <row r="102" spans="1:1">
       <c r="A102" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>69</v>
+        <v>68.900000000000006</v>
       </c>
     </row>
     <row r="103" spans="1:1">
       <c r="A103" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>67.900000000000006</v>
+        <v>72.5</v>
       </c>
     </row>
   </sheetData>
@@ -20108,78 +20059,78 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="2" spans="2:8">
-      <c r="B2" s="171" t="s">
+      <c r="B2" s="178" t="s">
         <v>500</v>
       </c>
-      <c r="C2" s="171"/>
-      <c r="D2" s="171"/>
-      <c r="E2" s="171"/>
-      <c r="F2" s="171"/>
-      <c r="G2" s="171"/>
-      <c r="H2" s="171"/>
+      <c r="C2" s="178"/>
+      <c r="D2" s="178"/>
+      <c r="E2" s="178"/>
+      <c r="F2" s="178"/>
+      <c r="G2" s="178"/>
+      <c r="H2" s="178"/>
     </row>
     <row r="3" spans="2:8">
-      <c r="B3" s="171"/>
-      <c r="C3" s="171"/>
-      <c r="D3" s="171"/>
-      <c r="E3" s="171"/>
-      <c r="F3" s="171"/>
-      <c r="G3" s="171"/>
-      <c r="H3" s="171"/>
+      <c r="B3" s="178"/>
+      <c r="C3" s="178"/>
+      <c r="D3" s="178"/>
+      <c r="E3" s="178"/>
+      <c r="F3" s="178"/>
+      <c r="G3" s="178"/>
+      <c r="H3" s="178"/>
     </row>
     <row r="4" spans="2:8">
-      <c r="B4" s="171"/>
-      <c r="C4" s="171"/>
-      <c r="D4" s="171"/>
-      <c r="E4" s="171"/>
-      <c r="F4" s="171"/>
-      <c r="G4" s="171"/>
-      <c r="H4" s="171"/>
+      <c r="B4" s="178"/>
+      <c r="C4" s="178"/>
+      <c r="D4" s="178"/>
+      <c r="E4" s="178"/>
+      <c r="F4" s="178"/>
+      <c r="G4" s="178"/>
+      <c r="H4" s="178"/>
     </row>
     <row r="5" spans="2:8">
-      <c r="B5" s="171"/>
-      <c r="C5" s="171"/>
-      <c r="D5" s="171"/>
-      <c r="E5" s="171"/>
-      <c r="F5" s="171"/>
-      <c r="G5" s="171"/>
-      <c r="H5" s="171"/>
+      <c r="B5" s="178"/>
+      <c r="C5" s="178"/>
+      <c r="D5" s="178"/>
+      <c r="E5" s="178"/>
+      <c r="F5" s="178"/>
+      <c r="G5" s="178"/>
+      <c r="H5" s="178"/>
     </row>
     <row r="6" spans="2:8">
-      <c r="B6" s="171"/>
-      <c r="C6" s="171"/>
-      <c r="D6" s="171"/>
-      <c r="E6" s="171"/>
-      <c r="F6" s="171"/>
-      <c r="G6" s="171"/>
-      <c r="H6" s="171"/>
+      <c r="B6" s="178"/>
+      <c r="C6" s="178"/>
+      <c r="D6" s="178"/>
+      <c r="E6" s="178"/>
+      <c r="F6" s="178"/>
+      <c r="G6" s="178"/>
+      <c r="H6" s="178"/>
     </row>
     <row r="7" spans="2:8">
-      <c r="B7" s="171"/>
-      <c r="C7" s="171"/>
-      <c r="D7" s="171"/>
-      <c r="E7" s="171"/>
-      <c r="F7" s="171"/>
-      <c r="G7" s="171"/>
-      <c r="H7" s="171"/>
+      <c r="B7" s="178"/>
+      <c r="C7" s="178"/>
+      <c r="D7" s="178"/>
+      <c r="E7" s="178"/>
+      <c r="F7" s="178"/>
+      <c r="G7" s="178"/>
+      <c r="H7" s="178"/>
     </row>
     <row r="8" spans="2:8">
-      <c r="B8" s="171"/>
-      <c r="C8" s="171"/>
-      <c r="D8" s="171"/>
-      <c r="E8" s="171"/>
-      <c r="F8" s="171"/>
-      <c r="G8" s="171"/>
-      <c r="H8" s="171"/>
+      <c r="B8" s="178"/>
+      <c r="C8" s="178"/>
+      <c r="D8" s="178"/>
+      <c r="E8" s="178"/>
+      <c r="F8" s="178"/>
+      <c r="G8" s="178"/>
+      <c r="H8" s="178"/>
     </row>
     <row r="9" spans="2:8">
-      <c r="B9" s="171"/>
-      <c r="C9" s="171"/>
-      <c r="D9" s="171"/>
-      <c r="E9" s="171"/>
-      <c r="F9" s="171"/>
-      <c r="G9" s="171"/>
-      <c r="H9" s="171"/>
+      <c r="B9" s="178"/>
+      <c r="C9" s="178"/>
+      <c r="D9" s="178"/>
+      <c r="E9" s="178"/>
+      <c r="F9" s="178"/>
+      <c r="G9" s="178"/>
+      <c r="H9" s="178"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -20191,25 +20142,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="cca9fd2d-ef84-45c9-8063-8f4bd4c29606">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101002C289946819CFF499E91D197BC975371" ma:contentTypeVersion="13" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="674b7a4e239a9748c7aaa97e309327a4">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="cca9fd2d-ef84-45c9-8063-8f4bd4c29606" xmlns:ns3="18557d39-01b8-4d71-9479-3fad465290ae" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="600253478e594d1349e02792803dc53a" ns2:_="" ns3:_="">
     <xsd:import namespace="cca9fd2d-ef84-45c9-8063-8f4bd4c29606"/>
@@ -20426,25 +20358,26 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{17F1EF20-95AB-4016-A693-6625F3A67214}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="cca9fd2d-ef84-45c9-8063-8f4bd4c29606">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{924A8F3D-57F5-4941-A32A-55B7F7F7AF07}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="cca9fd2d-ef84-45c9-8063-8f4bd4c29606"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8F527DFD-99D6-4A6C-AC9B-EC23CCFE992B}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -20461,4 +20394,22 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{924A8F3D-57F5-4941-A32A-55B7F7F7AF07}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="cca9fd2d-ef84-45c9-8063-8f4bd4c29606"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{17F1EF20-95AB-4016-A693-6625F3A67214}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/144/DQ Templates and Instructions/Topic 5 DQ 2/Topic 5 DQ 2.xlsx
+++ b/144/DQ Templates and Instructions/Topic 5 DQ 2/Topic 5 DQ 2.xlsx
@@ -8,22 +8,23 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://gcumail.sharepoint.com/sites/MathematicsProgramFacultyStaff-MATOFTF/Shared Documents/MATOFTF/ALEKS/DQ Templates and Instructions/Topic 5 DQ 2/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="10" documentId="8_{46C128A8-172E-4984-BBC3-77234BE2C9F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D338C630-11E0-41E6-A46A-5F84BCDDE0F7}"/>
+  <xr:revisionPtr revIDLastSave="51" documentId="13_ncr:1_{A43B0896-41E1-48A5-9A05-3AFD9717E55F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BA9969BC-8247-42B9-81D1-759464343890}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="649" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Goals and Instructions" sheetId="7" r:id="rId1"/>
     <sheet name="Water Quality" sheetId="4" r:id="rId2"/>
-    <sheet name="Solution" sheetId="9" state="hidden" r:id="rId3"/>
-    <sheet name="Random" sheetId="6" state="hidden" r:id="rId4"/>
-    <sheet name="Data" sheetId="5" state="hidden" r:id="rId5"/>
-    <sheet name="Sheet1" sheetId="8" state="hidden" r:id="rId6"/>
+    <sheet name="Users" sheetId="10" state="hidden" r:id="rId3"/>
+    <sheet name="Solution" sheetId="9" state="hidden" r:id="rId4"/>
+    <sheet name="Random" sheetId="6" state="hidden" r:id="rId5"/>
+    <sheet name="Data" sheetId="5" state="hidden" r:id="rId6"/>
+    <sheet name="Sheet1" sheetId="8" state="hidden" r:id="rId7"/>
   </sheets>
   <definedNames>
     <definedName name="Z_8A50E3A6_4261_4BD1_A94F_918D0E3EEAC3_.wvu.Cols" localSheetId="1" hidden="1">'Water Quality'!$AK:$AK</definedName>
   </definedNames>
-  <calcPr calcId="191028"/>
+  <calcPr calcId="191028" iterate="1"/>
   <customWorkbookViews>
     <customWorkbookView name="Richard Ketchersid - Personal View" guid="{8A50E3A6-4261-4BD1-A94F-918D0E3EEAC3}" mergeInterval="0" personalView="1" xWindow="2282" yWindow="53" windowWidth="1440" windowHeight="762" tabRatio="649" activeSheetId="4" showComments="commIndAndComment"/>
   </customWorkbookViews>
@@ -49,20 +50,14 @@
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
+    <author>tc={4DED145D-9386-4D2F-86D3-6933C31D540A}</author>
     <author>tc={B05C9DDC-E061-4B91-8296-E0F41DA1E339}</author>
-    <author>tc={4DED145D-9386-4D2F-86D3-6933C31D540A}</author>
-    <author>tc={7D93A252-A397-45CF-87F5-D3804D5EAFA7}</author>
+    <author>tc={3A97C018-B925-41F6-8DEA-029261E073A3}</author>
+    <author>tc={E3379479-E25D-4AA9-8D56-A93E7337011B}</author>
+    <author>tc={6CD78731-8151-4E00-9CA4-A552B028C4D6}</author>
   </authors>
   <commentList>
-    <comment ref="F2" authorId="0" shapeId="0" xr:uid="{B05C9DDC-E061-4B91-8296-E0F41DA1E339}">
-      <text>
-        <t>[Threaded comment]
-Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-    https://www.loom.com/share/d75e2dbd00674adc8cc09d59d90c3a7d?sid=50a5c7ae-f145-4875-bf35-04ec7babbbb8</t>
-      </text>
-    </comment>
-    <comment ref="F3" authorId="1" shapeId="0" xr:uid="{4DED145D-9386-4D2F-86D3-6933C31D540A}">
+    <comment ref="F4" authorId="0" shapeId="0" xr:uid="{4DED145D-9386-4D2F-86D3-6933C31D540A}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -70,12 +65,36 @@
     https://www.loom.com/share/4e999e54029a43d8b7b58d21e26817f7?sid=a1a57bba-9bd0-4ab2-994a-0c2b2c65ef01</t>
       </text>
     </comment>
-    <comment ref="F4" authorId="2" shapeId="0" xr:uid="{7D93A252-A397-45CF-87F5-D3804D5EAFA7}">
+    <comment ref="F8" authorId="1" shapeId="0" xr:uid="{B05C9DDC-E061-4B91-8296-E0F41DA1E339}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
 Comment:
-    https://www.loom.com/share/2c7609c4acb140e0b9aa4a95e0ae0440</t>
+    https://www.loom.com/share/3ecf9b18779349b9bed65afd8204a0dd</t>
+      </text>
+    </comment>
+    <comment ref="J29" authorId="2" shapeId="0" xr:uid="{3A97C018-B925-41F6-8DEA-029261E073A3}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    https://www.loom.com/share/8b1a7197f71f4ce786d6106b3a6ee1a6</t>
+      </text>
+    </comment>
+    <comment ref="J30" authorId="3" shapeId="0" xr:uid="{E3379479-E25D-4AA9-8D56-A93E7337011B}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    https://www.loom.com/share/fdc9ace994254c40ae04947dbe3675ce</t>
+      </text>
+    </comment>
+    <comment ref="J31" authorId="4" shapeId="0" xr:uid="{6CD78731-8151-4E00-9CA4-A552B028C4D6}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    https://www.loom.com/share/e6da8764222d484ba28f05da62330ca0</t>
       </text>
     </comment>
   </commentList>
@@ -119,7 +138,7 @@
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
   <metadataTypes count="1">
     <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
   </metadataTypes>
@@ -141,7 +160,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="532" uniqueCount="502">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="537" uniqueCount="510">
   <si>
     <t>Excel Skills Learned</t>
   </si>
@@ -1731,7 +1750,31 @@
     <t>Open this sheet in Excel to complete it.</t>
   </si>
   <si>
+    <t>Names</t>
+  </si>
+  <si>
+    <t>Reset</t>
+  </si>
+  <si>
+    <t>Video for Frequency Distribution</t>
+  </si>
+  <si>
+    <t>Video for using the built-in histogram chart</t>
+  </si>
+  <si>
+    <t>Video for using a bar chart for the histogram</t>
+  </si>
+  <si>
+    <t>Video using online Excel - both variants</t>
+  </si>
+  <si>
     <t>Your Name Here</t>
+  </si>
+  <si>
+    <t>Put your histogram here. Make sure to label the x-axis appropriately using the "Center of Bin" data. Also, make sure to set the chart title and add and set the axis titles. The x-axis title must be a valid name for the data.</t>
+  </si>
+  <si>
+    <t>Choose whichever of these methods you want to use:</t>
   </si>
 </sst>
 </file>
@@ -2500,11 +2543,12 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="179">
+  <cellXfs count="188">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
@@ -2633,18 +2677,6 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="right"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="39" xfId="0" applyFill="1" applyBorder="1" applyProtection="1">
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="4" borderId="40" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyProtection="1">
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="28" xfId="0" applyFill="1" applyBorder="1" applyProtection="1">
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="4" borderId="18" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyProtection="1">
       <protection hidden="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -2811,21 +2843,28 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="43" xfId="0" applyBorder="1" applyProtection="1">
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="28" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection hidden="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
+    <xf numFmtId="9" fontId="0" fillId="4" borderId="18" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection hidden="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="39" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="4" borderId="40" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection hidden="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="7" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2836,6 +2875,22 @@
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="7" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="27" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
@@ -3026,6 +3081,33 @@
       <alignment horizontal="center" vertical="center"/>
       <protection hidden="1"/>
     </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="29" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="30" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="31" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" indent="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" indent="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" indent="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
       <protection hidden="1"/>
@@ -3182,17 +3264,25 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="3">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Percent" xfId="2" builtinId="5"/>
   </cellStyles>
-  <dxfs count="8">
+  <dxfs count="9">
     <dxf>
       <fill>
         <patternFill>
           <bgColor rgb="FFFFFF00"/>
         </patternFill>
       </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color rgb="FF00B050"/>
+      </font>
     </dxf>
     <dxf>
       <font>
@@ -3262,918 +3352,7 @@
 </styleSheet>
 </file>
 
-<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
-  <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
-  <c:roundedCorners val="0"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
-      <c14:style val="102"/>
-    </mc:Choice>
-    <mc:Fallback>
-      <c:style val="2"/>
-    </mc:Fallback>
-  </mc:AlternateContent>
-  <c:chart>
-    <c:title>
-      <c:overlay val="0"/>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-      <c:txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr>
-            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="65000"/>
-                  <a:lumOff val="35000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:pPr>
-          <a:endParaRPr lang="en-US"/>
-        </a:p>
-      </c:txPr>
-    </c:title>
-    <c:autoTitleDeleted val="0"/>
-    <c:plotArea>
-      <c:layout/>
-      <c:barChart>
-        <c:barDir val="col"/>
-        <c:grouping val="clustered"/>
-        <c:varyColors val="0"/>
-        <c:ser>
-          <c:idx val="0"/>
-          <c:order val="0"/>
-          <c:spPr>
-            <a:solidFill>
-              <a:schemeClr val="accent1"/>
-            </a:solidFill>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:invertIfNegative val="0"/>
-          <c:dLbls>
-            <c:spPr>
-              <a:noFill/>
-              <a:ln>
-                <a:noFill/>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-            <c:txPr>
-              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
-                <a:spAutoFit/>
-              </a:bodyPr>
-              <a:lstStyle/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                    <a:solidFill>
-                      <a:schemeClr val="tx1">
-                        <a:lumMod val="75000"/>
-                        <a:lumOff val="25000"/>
-                      </a:schemeClr>
-                    </a:solidFill>
-                    <a:latin typeface="+mn-lt"/>
-                    <a:ea typeface="+mn-ea"/>
-                    <a:cs typeface="+mn-cs"/>
-                  </a:defRPr>
-                </a:pPr>
-                <a:endParaRPr lang="en-US"/>
-              </a:p>
-            </c:txPr>
-            <c:showLegendKey val="0"/>
-            <c:showVal val="1"/>
-            <c:showCatName val="0"/>
-            <c:showSerName val="0"/>
-            <c:showPercent val="0"/>
-            <c:showBubbleSize val="0"/>
-            <c:showLeaderLines val="0"/>
-            <c:extLst>
-              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                <c15:showLeaderLines val="1"/>
-                <c15:leaderLines>
-                  <c:spPr>
-                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-                      <a:solidFill>
-                        <a:schemeClr val="tx1">
-                          <a:lumMod val="35000"/>
-                          <a:lumOff val="65000"/>
-                        </a:schemeClr>
-                      </a:solidFill>
-                      <a:round/>
-                    </a:ln>
-                    <a:effectLst/>
-                  </c:spPr>
-                </c15:leaderLines>
-              </c:ext>
-            </c:extLst>
-          </c:dLbls>
-          <c:cat>
-            <c:numRef>
-              <c:f>'Water Quality'!$F$11:$F$21</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="11"/>
-              </c:numCache>
-            </c:numRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:f>'Water Quality'!$G$11:$G$21</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="11"/>
-              </c:numCache>
-            </c:numRef>
-          </c:val>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-6E8B-46E2-9109-70E6BFCC4A14}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:dLbls>
-          <c:showLegendKey val="0"/>
-          <c:showVal val="0"/>
-          <c:showCatName val="0"/>
-          <c:showSerName val="0"/>
-          <c:showPercent val="0"/>
-          <c:showBubbleSize val="0"/>
-        </c:dLbls>
-        <c:gapWidth val="219"/>
-        <c:overlap val="-27"/>
-        <c:axId val="196616711"/>
-        <c:axId val="196618759"/>
-      </c:barChart>
-      <c:catAx>
-        <c:axId val="196616711"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:delete val="0"/>
-        <c:axPos val="b"/>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
-        <c:majorTickMark val="none"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="nextTo"/>
-        <c:spPr>
-          <a:noFill/>
-          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-            <a:solidFill>
-              <a:schemeClr val="tx1">
-                <a:lumMod val="15000"/>
-                <a:lumOff val="85000"/>
-              </a:schemeClr>
-            </a:solidFill>
-            <a:round/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:endParaRPr lang="en-US"/>
-          </a:p>
-        </c:txPr>
-        <c:crossAx val="196618759"/>
-        <c:crosses val="autoZero"/>
-        <c:auto val="1"/>
-        <c:lblAlgn val="ctr"/>
-        <c:lblOffset val="100"/>
-        <c:noMultiLvlLbl val="0"/>
-      </c:catAx>
-      <c:valAx>
-        <c:axId val="196618759"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:delete val="0"/>
-        <c:axPos val="l"/>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
-        <c:majorTickMark val="none"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="nextTo"/>
-        <c:spPr>
-          <a:noFill/>
-          <a:ln>
-            <a:noFill/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:endParaRPr lang="en-US"/>
-          </a:p>
-        </c:txPr>
-        <c:crossAx val="196616711"/>
-        <c:crosses val="autoZero"/>
-        <c:crossBetween val="between"/>
-      </c:valAx>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-    </c:plotArea>
-    <c:legend>
-      <c:legendPos val="b"/>
-      <c:overlay val="0"/>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-      <c:txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr>
-            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="65000"/>
-                  <a:lumOff val="35000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:pPr>
-          <a:endParaRPr lang="en-US"/>
-        </a:p>
-      </c:txPr>
-    </c:legend>
-    <c:plotVisOnly val="1"/>
-    <c:dispBlanksAs val="gap"/>
-    <c:showDLblsOverMax val="0"/>
-  </c:chart>
-  <c:spPr>
-    <a:solidFill>
-      <a:schemeClr val="bg1"/>
-    </a:solidFill>
-    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-      <a:solidFill>
-        <a:schemeClr val="tx1">
-          <a:lumMod val="15000"/>
-          <a:lumOff val="85000"/>
-        </a:schemeClr>
-      </a:solidFill>
-      <a:round/>
-    </a:ln>
-    <a:effectLst/>
-  </c:spPr>
-  <c:txPr>
-    <a:bodyPr/>
-    <a:lstStyle/>
-    <a:p>
-      <a:pPr>
-        <a:defRPr/>
-      </a:pPr>
-      <a:endParaRPr lang="en-US"/>
-    </a:p>
-  </c:txPr>
-  <c:printSettings>
-    <c:headerFooter/>
-    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
-    <c:pageSetup/>
-  </c:printSettings>
-</c:chartSpace>
-</file>
-
-<file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
-  <a:schemeClr val="accent1"/>
-  <a:schemeClr val="accent2"/>
-  <a:schemeClr val="accent3"/>
-  <a:schemeClr val="accent4"/>
-  <a:schemeClr val="accent5"/>
-  <a:schemeClr val="accent6"/>
-  <cs:variation/>
-  <cs:variation>
-    <a:lumMod val="60000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="80000"/>
-    <a:lumOff val="20000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="80000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="60000"/>
-    <a:lumOff val="40000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="50000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="70000"/>
-    <a:lumOff val="30000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="70000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="50000"/>
-    <a:lumOff val="50000"/>
-  </cs:variation>
-</cs:colorStyle>
-</file>
-
-<file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="201">
-  <cs:axisTitle>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="1000" kern="1200"/>
-  </cs:axisTitle>
-  <cs:categoryAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:categoryAxis>
-  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="bg1"/>
-      </a:solidFill>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="1000" kern="1200"/>
-  </cs:chartArea>
-  <cs:dataLabel>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="75000"/>
-        <a:lumOff val="25000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:dataLabel>
-  <cs:dataLabelCallout>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="lt1"/>
-      </a:solidFill>
-      <a:ln>
-        <a:solidFill>
-          <a:schemeClr val="dk1">
-            <a:lumMod val="25000"/>
-            <a:lumOff val="75000"/>
-          </a:schemeClr>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
-      <a:spAutoFit/>
-    </cs:bodyPr>
-  </cs:dataLabelCallout>
-  <cs:dataPoint>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="1">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-  </cs:dataPoint>
-  <cs:dataPoint3D>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="1">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-  </cs:dataPoint3D>
-  <cs:dataPointLine>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="1"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="28575" cap="rnd">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dataPointLine>
-  <cs:dataPointMarker>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="1">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-  </cs:dataPointMarker>
-  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
-  <cs:dataPointWireframe>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="1"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="rnd">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dataPointWireframe>
-  <cs:dataTable>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:noFill/>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:dataTable>
-  <cs:downBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="dk1">
-          <a:lumMod val="65000"/>
-          <a:lumOff val="35000"/>
-        </a:schemeClr>
-      </a:solidFill>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
-          </a:schemeClr>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-  </cs:downBar>
-  <cs:dropLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dropLine>
-  <cs:errorBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:errorBar>
-  <cs:floor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:noFill/>
-      <a:ln>
-        <a:noFill/>
-      </a:ln>
-    </cs:spPr>
-  </cs:floor>
-  <cs:gridlineMajor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:gridlineMajor>
-  <cs:gridlineMinor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="5000"/>
-            <a:lumOff val="95000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:gridlineMinor>
-  <cs:hiLoLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="75000"/>
-            <a:lumOff val="25000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:hiLoLine>
-  <cs:leaderLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:leaderLine>
-  <cs:legend>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:legend>
-  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-  </cs:plotArea>
-  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-  </cs:plotArea3D>
-  <cs:seriesAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:seriesAxis>
-  <cs:seriesLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:seriesLine>
-  <cs:title>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
-  </cs:title>
-  <cs:trendline>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="19050" cap="rnd">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:prstDash val="sysDot"/>
-      </a:ln>
-    </cs:spPr>
-  </cs:trendline>
-  <cs:trendlineLabel>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:trendlineLabel>
-  <cs:upBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="lt1"/>
-      </a:solidFill>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-  </cs:upBar>
-  <cs:valueAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:valueAxis>
-  <cs:wall>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:noFill/>
-      <a:ln>
-        <a:noFill/>
-      </a:ln>
-    </cs:spPr>
-  </cs:wall>
-</cs:chartStyle>
-</file>
-
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>533400</xdr:colOff>
-      <xdr:row>68</xdr:row>
-      <xdr:rowOff>57150</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>238125</xdr:colOff>
-      <xdr:row>82</xdr:row>
-      <xdr:rowOff>133350</xdr:rowOff>
-    </xdr:to>
-    <xdr:graphicFrame macro="">
-      <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="3" name="Chart 2">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F9F84009-72B9-B787-3157-8ECAE911AF38}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvGraphicFramePr/>
-      </xdr:nvGraphicFramePr>
-      <xdr:xfrm>
-        <a:off x="0" y="0"/>
-        <a:ext cx="0" cy="0"/>
-      </xdr:xfrm>
-      <a:graphic>
-        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
-        </a:graphicData>
-      </a:graphic>
-    </xdr:graphicFrame>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-</xdr:wsDr>
-</file>
-
-<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:oneCellAnchor>
     <xdr:from>
@@ -4504,16 +3683,7 @@
 
 <file path=xl/threadedComments/threadedComment1.xml><?xml version="1.0" encoding="utf-8"?>
 <ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <threadedComment ref="F2" dT="2026-07-16T19:58:59.69" personId="{7D363727-7BC8-4A19-85A9-62EDC04791BF}" id="{B05C9DDC-E061-4B91-8296-E0F41DA1E339}">
-    <text>https://www.loom.com/share/d75e2dbd00674adc8cc09d59d90c3a7d?sid=50a5c7ae-f145-4875-bf35-04ec7babbbb8</text>
-    <extLst>
-      <x:ext xmlns:xltc2="http://schemas.microsoft.com/office/spreadsheetml/2020/threadedcomments2" uri="{F7C98A9C-CBB3-438F-8F68-D28B6AF4A901}">
-        <xltc2:checksum>923284797</xltc2:checksum>
-        <xltc2:hyperlink startIndex="0" length="100" url="https://www.loom.com/share/d75e2dbd00674adc8cc09d59d90c3a7d?sid=50a5c7ae-f145-4875-bf35-04ec7babbbb8"/>
-      </x:ext>
-    </extLst>
-  </threadedComment>
-  <threadedComment ref="F3" dT="2026-07-16T19:59:17.40" personId="{7D363727-7BC8-4A19-85A9-62EDC04791BF}" id="{4DED145D-9386-4D2F-86D3-6933C31D540A}">
+  <threadedComment ref="F4" dT="2026-07-16T19:59:17.40" personId="{7D363727-7BC8-4A19-85A9-62EDC04791BF}" id="{4DED145D-9386-4D2F-86D3-6933C31D540A}">
     <text>https://www.loom.com/share/4e999e54029a43d8b7b58d21e26817f7?sid=a1a57bba-9bd0-4ab2-994a-0c2b2c65ef01</text>
     <extLst>
       <x:ext xmlns:xltc2="http://schemas.microsoft.com/office/spreadsheetml/2020/threadedcomments2" uri="{F7C98A9C-CBB3-438F-8F68-D28B6AF4A901}">
@@ -4522,12 +3692,39 @@
       </x:ext>
     </extLst>
   </threadedComment>
-  <threadedComment ref="F4" dT="2026-07-16T19:59:39.06" personId="{7D363727-7BC8-4A19-85A9-62EDC04791BF}" id="{7D93A252-A397-45CF-87F5-D3804D5EAFA7}">
-    <text>https://www.loom.com/share/2c7609c4acb140e0b9aa4a95e0ae0440</text>
+  <threadedComment ref="F8" dT="2026-07-16T19:58:59.69" personId="{7D363727-7BC8-4A19-85A9-62EDC04791BF}" id="{B05C9DDC-E061-4B91-8296-E0F41DA1E339}">
+    <text>https://www.loom.com/share/3ecf9b18779349b9bed65afd8204a0dd</text>
     <extLst>
       <x:ext xmlns:xltc2="http://schemas.microsoft.com/office/spreadsheetml/2020/threadedcomments2" uri="{F7C98A9C-CBB3-438F-8F68-D28B6AF4A901}">
-        <xltc2:checksum>2001432892</xltc2:checksum>
-        <xltc2:hyperlink startIndex="0" length="59" url="https://www.loom.com/share/2c7609c4acb140e0b9aa4a95e0ae0440"/>
+        <xltc2:checksum>2852358914</xltc2:checksum>
+        <xltc2:hyperlink startIndex="0" length="59" url="https://www.loom.com/share/3ecf9b18779349b9bed65afd8204a0dd"/>
+      </x:ext>
+    </extLst>
+  </threadedComment>
+  <threadedComment ref="J29" dT="2026-08-26T03:58:45.98" personId="{7D363727-7BC8-4A19-85A9-62EDC04791BF}" id="{3A97C018-B925-41F6-8DEA-029261E073A3}">
+    <text>https://www.loom.com/share/8b1a7197f71f4ce786d6106b3a6ee1a6</text>
+    <extLst>
+      <x:ext xmlns:xltc2="http://schemas.microsoft.com/office/spreadsheetml/2020/threadedcomments2" uri="{F7C98A9C-CBB3-438F-8F68-D28B6AF4A901}">
+        <xltc2:checksum>1097453811</xltc2:checksum>
+        <xltc2:hyperlink startIndex="0" length="59" url="https://www.loom.com/share/8b1a7197f71f4ce786d6106b3a6ee1a6"/>
+      </x:ext>
+    </extLst>
+  </threadedComment>
+  <threadedComment ref="J30" dT="2026-08-26T04:08:00.99" personId="{7D363727-7BC8-4A19-85A9-62EDC04791BF}" id="{E3379479-E25D-4AA9-8D56-A93E7337011B}">
+    <text>https://www.loom.com/share/fdc9ace994254c40ae04947dbe3675ce</text>
+    <extLst>
+      <x:ext xmlns:xltc2="http://schemas.microsoft.com/office/spreadsheetml/2020/threadedcomments2" uri="{F7C98A9C-CBB3-438F-8F68-D28B6AF4A901}">
+        <xltc2:checksum>894370059</xltc2:checksum>
+        <xltc2:hyperlink startIndex="0" length="59" url="https://www.loom.com/share/fdc9ace994254c40ae04947dbe3675ce"/>
+      </x:ext>
+    </extLst>
+  </threadedComment>
+  <threadedComment ref="J31" dT="2026-08-26T04:24:55.97" personId="{7D363727-7BC8-4A19-85A9-62EDC04791BF}" id="{6CD78731-8151-4E00-9CA4-A552B028C4D6}">
+    <text>https://www.loom.com/share/e6da8764222d484ba28f05da62330ca0</text>
+    <extLst>
+      <x:ext xmlns:xltc2="http://schemas.microsoft.com/office/spreadsheetml/2020/threadedcomments2" uri="{F7C98A9C-CBB3-438F-8F68-D28B6AF4A901}">
+        <xltc2:checksum>1965023792</xltc2:checksum>
+        <xltc2:hyperlink startIndex="0" length="59" url="https://www.loom.com/share/e6da8764222d484ba28f05da62330ca0"/>
       </x:ext>
     </extLst>
   </threadedComment>
@@ -4579,56 +3776,56 @@
       <c r="B3" s="15" t="s">
         <v>0</v>
       </c>
-      <c r="D3" s="91" t="s">
-        <v>1</v>
-      </c>
-      <c r="E3" s="92"/>
-      <c r="F3" s="92"/>
-      <c r="G3" s="92"/>
-      <c r="H3" s="92"/>
-      <c r="I3" s="93"/>
+      <c r="D3" s="93" t="s">
+        <v>1</v>
+      </c>
+      <c r="E3" s="94"/>
+      <c r="F3" s="94"/>
+      <c r="G3" s="94"/>
+      <c r="H3" s="94"/>
+      <c r="I3" s="95"/>
     </row>
     <row r="4" spans="2:9">
       <c r="B4" t="s">
         <v>2</v>
       </c>
-      <c r="D4" s="94"/>
-      <c r="E4" s="95"/>
-      <c r="F4" s="95"/>
-      <c r="G4" s="95"/>
-      <c r="H4" s="95"/>
-      <c r="I4" s="96"/>
+      <c r="D4" s="96"/>
+      <c r="E4" s="97"/>
+      <c r="F4" s="97"/>
+      <c r="G4" s="97"/>
+      <c r="H4" s="97"/>
+      <c r="I4" s="98"/>
     </row>
     <row r="5" spans="2:9" ht="30">
       <c r="B5" s="17" t="s">
         <v>3</v>
       </c>
-      <c r="D5" s="94"/>
-      <c r="E5" s="95"/>
-      <c r="F5" s="95"/>
-      <c r="G5" s="95"/>
-      <c r="H5" s="95"/>
-      <c r="I5" s="96"/>
+      <c r="D5" s="96"/>
+      <c r="E5" s="97"/>
+      <c r="F5" s="97"/>
+      <c r="G5" s="97"/>
+      <c r="H5" s="97"/>
+      <c r="I5" s="98"/>
     </row>
     <row r="6" spans="2:9" ht="30">
       <c r="B6" s="17" t="s">
         <v>4</v>
       </c>
-      <c r="D6" s="94"/>
-      <c r="E6" s="95"/>
-      <c r="F6" s="95"/>
-      <c r="G6" s="95"/>
-      <c r="H6" s="95"/>
-      <c r="I6" s="96"/>
+      <c r="D6" s="96"/>
+      <c r="E6" s="97"/>
+      <c r="F6" s="97"/>
+      <c r="G6" s="97"/>
+      <c r="H6" s="97"/>
+      <c r="I6" s="98"/>
     </row>
     <row r="7" spans="2:9" ht="15.75" thickBot="1">
       <c r="B7" s="17"/>
-      <c r="D7" s="97"/>
-      <c r="E7" s="98"/>
-      <c r="F7" s="98"/>
-      <c r="G7" s="98"/>
-      <c r="H7" s="98"/>
-      <c r="I7" s="99"/>
+      <c r="D7" s="99"/>
+      <c r="E7" s="100"/>
+      <c r="F7" s="100"/>
+      <c r="G7" s="100"/>
+      <c r="H7" s="100"/>
+      <c r="I7" s="101"/>
     </row>
     <row r="8" spans="2:9">
       <c r="B8" s="16"/>
@@ -4701,7 +3898,7 @@
       <c r="G1" s="22"/>
       <c r="H1" s="22"/>
     </row>
-    <row r="2" spans="1:37" ht="20.25" thickTop="1" thickBot="1">
+    <row r="2" spans="1:37" ht="18.75" thickTop="1" thickBot="1">
       <c r="A2" s="6">
         <v>1</v>
       </c>
@@ -4710,35 +3907,30 @@
         <v>Enter Name</v>
       </c>
       <c r="D2" s="18" t="s">
-        <v>501</v>
+        <v>507</v>
       </c>
       <c r="E2" s="23"/>
-      <c r="F2" s="131" t="s">
-        <v>12</v>
-      </c>
-      <c r="G2" s="132"/>
-      <c r="H2" s="133"/>
-      <c r="J2" s="109" t="s">
+      <c r="J2" s="111" t="s">
         <v>13</v>
       </c>
-      <c r="K2" s="110"/>
-      <c r="M2" s="78">
+      <c r="K2" s="112"/>
+      <c r="M2" s="74">
         <v>15</v>
       </c>
-      <c r="N2" s="136" t="s">
+      <c r="N2" s="138" t="s">
         <v>14</v>
       </c>
-      <c r="O2" s="136"/>
-      <c r="P2" s="136"/>
-      <c r="Q2" s="136"/>
-      <c r="R2" s="136"/>
-      <c r="S2" s="137"/>
+      <c r="O2" s="138"/>
+      <c r="P2" s="138"/>
+      <c r="Q2" s="138"/>
+      <c r="R2" s="138"/>
+      <c r="S2" s="139"/>
       <c r="AK2" s="4">
         <f>MOD(CODE(MID(D2,1,1))*CODE(MID(D2,2,1))*CODE(MID(D2,3,1))*1103515245 + 12345,9172)</f>
         <v>5008</v>
       </c>
     </row>
-    <row r="3" spans="1:37" ht="19.5" thickBot="1">
+    <row r="3" spans="1:37" ht="16.5" thickBot="1">
       <c r="A3" s="6">
         <f>A2+1</f>
         <v>2</v>
@@ -4748,28 +3940,23 @@
         <v>Enter Name</v>
       </c>
       <c r="E3" s="23"/>
-      <c r="F3" s="131" t="s">
-        <v>15</v>
-      </c>
-      <c r="G3" s="132"/>
-      <c r="H3" s="133"/>
       <c r="J3" s="7" t="s">
         <v>16</v>
       </c>
       <c r="K3" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="M3" s="79">
+      <c r="M3" s="75">
         <v>15</v>
       </c>
-      <c r="N3" s="134" t="s">
+      <c r="N3" s="136" t="s">
         <v>18</v>
       </c>
-      <c r="O3" s="134"/>
-      <c r="P3" s="134"/>
-      <c r="Q3" s="134"/>
-      <c r="R3" s="134"/>
-      <c r="S3" s="135"/>
+      <c r="O3" s="136"/>
+      <c r="P3" s="136"/>
+      <c r="Q3" s="136"/>
+      <c r="R3" s="136"/>
+      <c r="S3" s="137"/>
       <c r="AK3" s="4">
         <f>MOD(AK2*1103515245 + 12345,9172)</f>
         <v>6441</v>
@@ -4788,28 +3975,28 @@
         <v>19</v>
       </c>
       <c r="E4" s="25"/>
-      <c r="F4" s="131" t="s">
-        <v>20</v>
-      </c>
-      <c r="G4" s="132"/>
-      <c r="H4" s="133"/>
+      <c r="F4" s="133" t="s">
+        <v>15</v>
+      </c>
+      <c r="G4" s="134"/>
+      <c r="H4" s="135"/>
       <c r="J4" s="9" t="s">
         <v>21</v>
       </c>
       <c r="K4" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="M4" s="80">
+      <c r="M4" s="76">
         <v>16</v>
       </c>
-      <c r="N4" s="82" t="s">
+      <c r="N4" s="78" t="s">
         <v>23</v>
       </c>
-      <c r="O4" s="82"/>
-      <c r="P4" s="82"/>
-      <c r="Q4" s="82"/>
-      <c r="R4" s="82"/>
-      <c r="S4" s="83"/>
+      <c r="O4" s="78"/>
+      <c r="P4" s="78"/>
+      <c r="Q4" s="78"/>
+      <c r="R4" s="78"/>
+      <c r="S4" s="79"/>
       <c r="AK4" s="4">
         <f t="shared" ref="AK4:AK67" si="1">MOD(AK3*1103515245 + 12345,9172)</f>
         <v>5030</v>
@@ -4827,7 +4014,7 @@
       <c r="D5" s="26" t="s">
         <v>24</v>
       </c>
-      <c r="E5" s="88"/>
+      <c r="E5" s="86"/>
       <c r="G5" s="27"/>
       <c r="H5" s="28"/>
       <c r="J5" s="11" t="s">
@@ -4836,17 +4023,17 @@
       <c r="K5" s="10" t="s">
         <v>26</v>
       </c>
-      <c r="M5" s="81">
+      <c r="M5" s="77">
         <v>16</v>
       </c>
-      <c r="N5" s="138" t="s">
+      <c r="N5" s="140" t="s">
         <v>27</v>
       </c>
-      <c r="O5" s="138"/>
-      <c r="P5" s="138"/>
-      <c r="Q5" s="138"/>
-      <c r="R5" s="138"/>
-      <c r="S5" s="139"/>
+      <c r="O5" s="140"/>
+      <c r="P5" s="140"/>
+      <c r="Q5" s="140"/>
+      <c r="R5" s="140"/>
+      <c r="S5" s="141"/>
       <c r="AK5" s="4">
         <f t="shared" si="1"/>
         <v>2547</v>
@@ -4864,9 +4051,9 @@
       <c r="D6" s="29" t="s">
         <v>28</v>
       </c>
-      <c r="E6" s="89"/>
-      <c r="G6" s="77"/>
-      <c r="H6" s="77"/>
+      <c r="E6" s="87"/>
+      <c r="G6" s="73"/>
+      <c r="H6" s="73"/>
       <c r="J6" s="12" t="s">
         <v>29</v>
       </c>
@@ -4890,9 +4077,9 @@
       <c r="D7" s="30" t="s">
         <v>31</v>
       </c>
-      <c r="E7" s="90"/>
-      <c r="G7" s="77"/>
-      <c r="H7" s="77"/>
+      <c r="E7" s="88"/>
+      <c r="G7" s="73"/>
+      <c r="H7" s="73"/>
       <c r="J7" s="13" t="s">
         <v>32</v>
       </c>
@@ -4904,7 +4091,7 @@
         <v>4193</v>
       </c>
     </row>
-    <row r="8" spans="1:37" ht="15.75" thickBot="1">
+    <row r="8" spans="1:37" ht="19.5" thickBot="1">
       <c r="A8" s="6">
         <f t="shared" si="0"/>
         <v>7</v>
@@ -4913,6 +4100,11 @@
         <f>IF(D$2="Your Name Here","Enter Name",ROUND(_xlfn.NORM.INV(Random!D18,20,15),1))</f>
         <v>Enter Name</v>
       </c>
+      <c r="F8" s="133" t="s">
+        <v>503</v>
+      </c>
+      <c r="G8" s="134"/>
+      <c r="H8" s="135"/>
       <c r="AK8" s="4">
         <f>MOD(AK7*1103515245 + 12345,9172)</f>
         <v>8530</v>
@@ -4927,13 +4119,13 @@
         <f>IF(D$2="Your Name Here","Enter Name",ROUND(_xlfn.NORM.INV(Random!D19,20,15),1))</f>
         <v>Enter Name</v>
       </c>
-      <c r="D9" s="119" t="s">
+      <c r="D9" s="121" t="s">
         <v>34</v>
       </c>
-      <c r="E9" s="120"/>
-      <c r="F9" s="120"/>
-      <c r="G9" s="120"/>
-      <c r="H9" s="121"/>
+      <c r="E9" s="122"/>
+      <c r="F9" s="122"/>
+      <c r="G9" s="122"/>
+      <c r="H9" s="123"/>
       <c r="AK9" s="4">
         <f t="shared" si="1"/>
         <v>6743</v>
@@ -4963,14 +4155,14 @@
       <c r="H10" s="33" t="s">
         <v>39</v>
       </c>
-      <c r="J10" s="122" t="s">
+      <c r="J10" s="124" t="s">
         <v>40</v>
       </c>
-      <c r="K10" s="123"/>
-      <c r="L10" s="123"/>
-      <c r="M10" s="123"/>
-      <c r="N10" s="123"/>
-      <c r="O10" s="124"/>
+      <c r="K10" s="125"/>
+      <c r="L10" s="125"/>
+      <c r="M10" s="125"/>
+      <c r="N10" s="125"/>
+      <c r="O10" s="126"/>
       <c r="AK10" s="4">
         <f t="shared" si="1"/>
         <v>6608</v>
@@ -4985,17 +4177,17 @@
         <f>IF(D$2="Your Name Here","Enter Name",ROUND(_xlfn.NORM.INV(Random!D21,20,15),1))</f>
         <v>Enter Name</v>
       </c>
-      <c r="D11" s="84"/>
-      <c r="E11" s="85"/>
-      <c r="F11" s="85"/>
-      <c r="G11" s="85"/>
-      <c r="H11" s="86"/>
-      <c r="J11" s="125"/>
-      <c r="K11" s="126"/>
-      <c r="L11" s="126"/>
-      <c r="M11" s="126"/>
-      <c r="N11" s="126"/>
-      <c r="O11" s="127"/>
+      <c r="D11" s="89"/>
+      <c r="E11" s="90"/>
+      <c r="F11" s="90"/>
+      <c r="G11" s="90"/>
+      <c r="H11" s="91"/>
+      <c r="J11" s="127"/>
+      <c r="K11" s="128"/>
+      <c r="L11" s="128"/>
+      <c r="M11" s="128"/>
+      <c r="N11" s="128"/>
+      <c r="O11" s="129"/>
       <c r="AK11" s="4">
         <f t="shared" si="1"/>
         <v>7573</v>
@@ -5010,17 +4202,17 @@
         <f>IF(D$2="Your Name Here","Enter Name",ROUND(_xlfn.NORM.INV(Random!D22,20,15),1))</f>
         <v>Enter Name</v>
       </c>
-      <c r="D12" s="87"/>
-      <c r="E12" s="85"/>
-      <c r="F12" s="85"/>
-      <c r="G12" s="85"/>
-      <c r="H12" s="86"/>
-      <c r="J12" s="125"/>
-      <c r="K12" s="126"/>
-      <c r="L12" s="126"/>
-      <c r="M12" s="126"/>
-      <c r="N12" s="126"/>
-      <c r="O12" s="127"/>
+      <c r="D12" s="92"/>
+      <c r="E12" s="90"/>
+      <c r="F12" s="90"/>
+      <c r="G12" s="90"/>
+      <c r="H12" s="91"/>
+      <c r="J12" s="127"/>
+      <c r="K12" s="128"/>
+      <c r="L12" s="128"/>
+      <c r="M12" s="128"/>
+      <c r="N12" s="128"/>
+      <c r="O12" s="129"/>
       <c r="AK12" s="4">
         <f t="shared" si="1"/>
         <v>6450</v>
@@ -5035,17 +4227,17 @@
         <f>IF(D$2="Your Name Here","Enter Name",ROUND(_xlfn.NORM.INV(Random!D23,20,15),1))</f>
         <v>Enter Name</v>
       </c>
-      <c r="D13" s="87"/>
-      <c r="E13" s="85"/>
-      <c r="F13" s="85"/>
-      <c r="G13" s="85"/>
-      <c r="H13" s="86"/>
-      <c r="J13" s="125"/>
-      <c r="K13" s="126"/>
-      <c r="L13" s="126"/>
-      <c r="M13" s="126"/>
-      <c r="N13" s="126"/>
-      <c r="O13" s="127"/>
+      <c r="D13" s="92"/>
+      <c r="E13" s="90"/>
+      <c r="F13" s="90"/>
+      <c r="G13" s="90"/>
+      <c r="H13" s="91"/>
+      <c r="J13" s="127"/>
+      <c r="K13" s="128"/>
+      <c r="L13" s="128"/>
+      <c r="M13" s="128"/>
+      <c r="N13" s="128"/>
+      <c r="O13" s="129"/>
       <c r="AK13" s="4">
         <f t="shared" si="1"/>
         <v>8023</v>
@@ -5060,17 +4252,17 @@
         <f>IF(D$2="Your Name Here","Enter Name",ROUND(_xlfn.NORM.INV(Random!D24,20,15),1))</f>
         <v>Enter Name</v>
       </c>
-      <c r="D14" s="87"/>
-      <c r="E14" s="85"/>
-      <c r="F14" s="85"/>
-      <c r="G14" s="85"/>
-      <c r="H14" s="86"/>
-      <c r="J14" s="125"/>
-      <c r="K14" s="126"/>
-      <c r="L14" s="126"/>
-      <c r="M14" s="126"/>
-      <c r="N14" s="126"/>
-      <c r="O14" s="127"/>
+      <c r="D14" s="92"/>
+      <c r="E14" s="90"/>
+      <c r="F14" s="90"/>
+      <c r="G14" s="90"/>
+      <c r="H14" s="91"/>
+      <c r="J14" s="127"/>
+      <c r="K14" s="128"/>
+      <c r="L14" s="128"/>
+      <c r="M14" s="128"/>
+      <c r="N14" s="128"/>
+      <c r="O14" s="129"/>
       <c r="AK14" s="4">
         <f>MOD(AK13*1103515245 + 12345,9172)</f>
         <v>176</v>
@@ -5085,17 +4277,17 @@
         <f>IF(D$2="Your Name Here","Enter Name",ROUND(_xlfn.NORM.INV(Random!D25,20,15),1))</f>
         <v>Enter Name</v>
       </c>
-      <c r="D15" s="87"/>
-      <c r="E15" s="85"/>
-      <c r="F15" s="85"/>
-      <c r="G15" s="85"/>
-      <c r="H15" s="86"/>
-      <c r="J15" s="125"/>
-      <c r="K15" s="126"/>
-      <c r="L15" s="126"/>
-      <c r="M15" s="126"/>
-      <c r="N15" s="126"/>
-      <c r="O15" s="127"/>
+      <c r="D15" s="92"/>
+      <c r="E15" s="90"/>
+      <c r="F15" s="90"/>
+      <c r="G15" s="90"/>
+      <c r="H15" s="91"/>
+      <c r="J15" s="127"/>
+      <c r="K15" s="128"/>
+      <c r="L15" s="128"/>
+      <c r="M15" s="128"/>
+      <c r="N15" s="128"/>
+      <c r="O15" s="129"/>
       <c r="AK15" s="4">
         <f t="shared" si="1"/>
         <v>8709</v>
@@ -5110,17 +4302,17 @@
         <f>IF(D$2="Your Name Here","Enter Name",ROUND(_xlfn.NORM.INV(Random!D26,20,15),1))</f>
         <v>Enter Name</v>
       </c>
-      <c r="D16" s="87"/>
-      <c r="E16" s="85"/>
-      <c r="F16" s="85"/>
-      <c r="G16" s="85"/>
-      <c r="H16" s="86"/>
-      <c r="J16" s="125"/>
-      <c r="K16" s="126"/>
-      <c r="L16" s="126"/>
-      <c r="M16" s="126"/>
-      <c r="N16" s="126"/>
-      <c r="O16" s="127"/>
+      <c r="D16" s="92"/>
+      <c r="E16" s="90"/>
+      <c r="F16" s="90"/>
+      <c r="G16" s="90"/>
+      <c r="H16" s="91"/>
+      <c r="J16" s="127"/>
+      <c r="K16" s="128"/>
+      <c r="L16" s="128"/>
+      <c r="M16" s="128"/>
+      <c r="N16" s="128"/>
+      <c r="O16" s="129"/>
       <c r="AK16" s="4">
         <f t="shared" si="1"/>
         <v>7162</v>
@@ -5135,17 +4327,17 @@
         <f>IF(D$2="Your Name Here","Enter Name",ROUND(_xlfn.NORM.INV(Random!D27,20,15),1))</f>
         <v>Enter Name</v>
       </c>
-      <c r="D17" s="87"/>
-      <c r="E17" s="85"/>
-      <c r="F17" s="85"/>
-      <c r="G17" s="85"/>
-      <c r="H17" s="86"/>
-      <c r="J17" s="125"/>
-      <c r="K17" s="126"/>
-      <c r="L17" s="126"/>
-      <c r="M17" s="126"/>
-      <c r="N17" s="126"/>
-      <c r="O17" s="127"/>
+      <c r="D17" s="92"/>
+      <c r="E17" s="90"/>
+      <c r="F17" s="90"/>
+      <c r="G17" s="90"/>
+      <c r="H17" s="91"/>
+      <c r="J17" s="127"/>
+      <c r="K17" s="128"/>
+      <c r="L17" s="128"/>
+      <c r="M17" s="128"/>
+      <c r="N17" s="128"/>
+      <c r="O17" s="129"/>
       <c r="AK17" s="4">
         <f t="shared" si="1"/>
         <v>1235</v>
@@ -5160,17 +4352,17 @@
         <f>IF(D$2="Your Name Here","Enter Name",ROUND(_xlfn.NORM.INV(Random!D28,20,15),1))</f>
         <v>Enter Name</v>
       </c>
-      <c r="D18" s="87"/>
-      <c r="E18" s="85"/>
-      <c r="F18" s="85"/>
-      <c r="G18" s="85"/>
-      <c r="H18" s="86"/>
-      <c r="J18" s="125"/>
-      <c r="K18" s="126"/>
-      <c r="L18" s="126"/>
-      <c r="M18" s="126"/>
-      <c r="N18" s="126"/>
-      <c r="O18" s="127"/>
+      <c r="D18" s="92"/>
+      <c r="E18" s="90"/>
+      <c r="F18" s="90"/>
+      <c r="G18" s="90"/>
+      <c r="H18" s="91"/>
+      <c r="J18" s="127"/>
+      <c r="K18" s="128"/>
+      <c r="L18" s="128"/>
+      <c r="M18" s="128"/>
+      <c r="N18" s="128"/>
+      <c r="O18" s="129"/>
       <c r="AK18" s="4">
         <f t="shared" si="1"/>
         <v>120</v>
@@ -5185,17 +4377,17 @@
         <f>IF(D$2="Your Name Here","Enter Name",ROUND(_xlfn.NORM.INV(Random!D29,20,15),1))</f>
         <v>Enter Name</v>
       </c>
-      <c r="D19" s="87"/>
-      <c r="E19" s="85"/>
-      <c r="F19" s="85"/>
-      <c r="G19" s="85"/>
-      <c r="H19" s="86"/>
-      <c r="J19" s="125"/>
-      <c r="K19" s="126"/>
-      <c r="L19" s="126"/>
-      <c r="M19" s="126"/>
-      <c r="N19" s="126"/>
-      <c r="O19" s="127"/>
+      <c r="D19" s="92"/>
+      <c r="E19" s="90"/>
+      <c r="F19" s="90"/>
+      <c r="G19" s="90"/>
+      <c r="H19" s="91"/>
+      <c r="J19" s="127"/>
+      <c r="K19" s="128"/>
+      <c r="L19" s="128"/>
+      <c r="M19" s="128"/>
+      <c r="N19" s="128"/>
+      <c r="O19" s="129"/>
       <c r="Q19" s="34"/>
       <c r="AK19" s="4">
         <f t="shared" si="1"/>
@@ -5211,17 +4403,17 @@
         <f>IF(D$2="Your Name Here","Enter Name",ROUND(_xlfn.NORM.INV(Random!D30,20,15),1))</f>
         <v>Enter Name</v>
       </c>
-      <c r="D20" s="87"/>
-      <c r="E20" s="85"/>
-      <c r="F20" s="85"/>
-      <c r="G20" s="85"/>
-      <c r="H20" s="86"/>
-      <c r="J20" s="125"/>
-      <c r="K20" s="126"/>
-      <c r="L20" s="126"/>
-      <c r="M20" s="126"/>
-      <c r="N20" s="126"/>
-      <c r="O20" s="127"/>
+      <c r="D20" s="92"/>
+      <c r="E20" s="90"/>
+      <c r="F20" s="90"/>
+      <c r="G20" s="90"/>
+      <c r="H20" s="91"/>
+      <c r="J20" s="127"/>
+      <c r="K20" s="128"/>
+      <c r="L20" s="128"/>
+      <c r="M20" s="128"/>
+      <c r="N20" s="128"/>
+      <c r="O20" s="129"/>
       <c r="Q20" s="34"/>
       <c r="AK20" s="4">
         <f t="shared" si="1"/>
@@ -5237,17 +4429,17 @@
         <f>IF(D$2="Your Name Here","Enter Name",ROUND(_xlfn.NORM.INV(Random!D31,20,15),1))</f>
         <v>Enter Name</v>
       </c>
-      <c r="D21" s="87"/>
-      <c r="E21" s="85"/>
-      <c r="F21" s="85"/>
-      <c r="G21" s="85"/>
-      <c r="H21" s="86"/>
-      <c r="J21" s="125"/>
-      <c r="K21" s="126"/>
-      <c r="L21" s="126"/>
-      <c r="M21" s="126"/>
-      <c r="N21" s="126"/>
-      <c r="O21" s="127"/>
+      <c r="D21" s="92"/>
+      <c r="E21" s="90"/>
+      <c r="F21" s="90"/>
+      <c r="G21" s="90"/>
+      <c r="H21" s="91"/>
+      <c r="J21" s="127"/>
+      <c r="K21" s="128"/>
+      <c r="L21" s="128"/>
+      <c r="M21" s="128"/>
+      <c r="N21" s="128"/>
+      <c r="O21" s="129"/>
       <c r="AK21" s="4">
         <f t="shared" si="1"/>
         <v>7051</v>
@@ -5265,20 +4457,20 @@
       <c r="F22" s="35" t="s">
         <v>41</v>
       </c>
-      <c r="G22" s="39">
+      <c r="G22" s="82">
         <f>SUM(G11:G21)</f>
         <v>0</v>
       </c>
-      <c r="H22" s="40">
+      <c r="H22" s="83">
         <f>SUM(H11:H21)</f>
         <v>0</v>
       </c>
-      <c r="J22" s="125"/>
-      <c r="K22" s="126"/>
-      <c r="L22" s="126"/>
-      <c r="M22" s="126"/>
-      <c r="N22" s="126"/>
-      <c r="O22" s="127"/>
+      <c r="J22" s="127"/>
+      <c r="K22" s="128"/>
+      <c r="L22" s="128"/>
+      <c r="M22" s="128"/>
+      <c r="N22" s="128"/>
+      <c r="O22" s="129"/>
       <c r="AK22" s="4">
         <f t="shared" si="1"/>
         <v>7124</v>
@@ -5296,18 +4488,18 @@
       <c r="F23" s="36" t="s">
         <v>42</v>
       </c>
-      <c r="G23" s="37">
+      <c r="G23" s="84">
         <v>102</v>
       </c>
-      <c r="H23" s="38">
-        <v>1</v>
-      </c>
-      <c r="J23" s="128"/>
-      <c r="K23" s="129"/>
-      <c r="L23" s="129"/>
-      <c r="M23" s="129"/>
-      <c r="N23" s="129"/>
-      <c r="O23" s="130"/>
+      <c r="H23" s="85">
+        <v>1</v>
+      </c>
+      <c r="J23" s="130"/>
+      <c r="K23" s="131"/>
+      <c r="L23" s="131"/>
+      <c r="M23" s="131"/>
+      <c r="N23" s="131"/>
+      <c r="O23" s="132"/>
       <c r="AK23" s="4">
         <f t="shared" si="1"/>
         <v>7961</v>
@@ -5322,13 +4514,13 @@
         <f>IF(D$2="Your Name Here","Enter Name",ROUND(_xlfn.NORM.INV(Random!D34,20,15),1))</f>
         <v>Enter Name</v>
       </c>
-      <c r="D24" s="111" t="s">
+      <c r="D24" s="113" t="s">
         <v>43</v>
       </c>
-      <c r="E24" s="112"/>
-      <c r="F24" s="113"/>
-      <c r="G24" s="113"/>
-      <c r="H24" s="114"/>
+      <c r="E24" s="114"/>
+      <c r="F24" s="115"/>
+      <c r="G24" s="115"/>
+      <c r="H24" s="116"/>
       <c r="AK24" s="4">
         <f t="shared" si="1"/>
         <v>1978</v>
@@ -5343,11 +4535,11 @@
         <f>IF(D$2="Your Name Here","Enter Name",ROUND(_xlfn.NORM.INV(Random!D35,20,15),1))</f>
         <v>Enter Name</v>
       </c>
-      <c r="D25" s="115"/>
-      <c r="E25" s="113"/>
-      <c r="F25" s="113"/>
-      <c r="G25" s="113"/>
-      <c r="H25" s="114"/>
+      <c r="D25" s="117"/>
+      <c r="E25" s="115"/>
+      <c r="F25" s="115"/>
+      <c r="G25" s="115"/>
+      <c r="H25" s="116"/>
       <c r="AK25" s="4">
         <f t="shared" si="1"/>
         <v>1603</v>
@@ -5362,11 +4554,11 @@
         <f>IF(D$2="Your Name Here","Enter Name",ROUND(_xlfn.NORM.INV(Random!D36,20,15),1))</f>
         <v>Enter Name</v>
       </c>
-      <c r="D26" s="115"/>
-      <c r="E26" s="113"/>
-      <c r="F26" s="113"/>
-      <c r="G26" s="113"/>
-      <c r="H26" s="114"/>
+      <c r="D26" s="117"/>
+      <c r="E26" s="115"/>
+      <c r="F26" s="115"/>
+      <c r="G26" s="115"/>
+      <c r="H26" s="116"/>
       <c r="AK26" s="4">
         <f t="shared" si="1"/>
         <v>8360</v>
@@ -5381,11 +4573,11 @@
         <f>IF(D$2="Your Name Here","Enter Name",ROUND(_xlfn.NORM.INV(Random!D37,20,15),1))</f>
         <v>Enter Name</v>
       </c>
-      <c r="D27" s="116"/>
-      <c r="E27" s="117"/>
-      <c r="F27" s="117"/>
-      <c r="G27" s="117"/>
-      <c r="H27" s="118"/>
+      <c r="D27" s="118"/>
+      <c r="E27" s="119"/>
+      <c r="F27" s="119"/>
+      <c r="G27" s="119"/>
+      <c r="H27" s="120"/>
       <c r="AK27" s="4">
         <f t="shared" si="1"/>
         <v>145</v>
@@ -5400,12 +4592,17 @@
         <f>IF(D$2="Your Name Here","Enter Name",ROUND(_xlfn.NORM.INV(Random!D38,20,15),1))</f>
         <v>Enter Name</v>
       </c>
+      <c r="J28" s="145" t="s">
+        <v>509</v>
+      </c>
+      <c r="K28" s="146"/>
+      <c r="L28" s="147"/>
       <c r="AK28" s="4">
         <f t="shared" si="1"/>
         <v>438</v>
       </c>
     </row>
-    <row r="29" spans="1:37">
+    <row r="29" spans="1:37" ht="19.5" thickBot="1">
       <c r="A29" s="6">
         <f t="shared" si="0"/>
         <v>28</v>
@@ -5414,19 +4611,24 @@
         <f>IF(D$2="Your Name Here","Enter Name",ROUND(_xlfn.NORM.INV(Random!D39,20,15),1))</f>
         <v>Enter Name</v>
       </c>
-      <c r="D29" s="100" t="s">
-        <v>44</v>
-      </c>
-      <c r="E29" s="101"/>
-      <c r="F29" s="101"/>
-      <c r="G29" s="101"/>
-      <c r="H29" s="102"/>
+      <c r="D29" s="102" t="s">
+        <v>508</v>
+      </c>
+      <c r="E29" s="103"/>
+      <c r="F29" s="103"/>
+      <c r="G29" s="103"/>
+      <c r="H29" s="104"/>
+      <c r="J29" s="142" t="s">
+        <v>504</v>
+      </c>
+      <c r="K29" s="143"/>
+      <c r="L29" s="144"/>
       <c r="AK29" s="4">
         <f t="shared" si="1"/>
         <v>8195</v>
       </c>
     </row>
-    <row r="30" spans="1:37">
+    <row r="30" spans="1:37" ht="19.5" thickBot="1">
       <c r="A30" s="6">
         <f t="shared" si="0"/>
         <v>29</v>
@@ -5435,17 +4637,22 @@
         <f>IF(D$2="Your Name Here","Enter Name",ROUND(_xlfn.NORM.INV(Random!D40,20,15),1))</f>
         <v>Enter Name</v>
       </c>
-      <c r="D30" s="103"/>
-      <c r="E30" s="104"/>
-      <c r="F30" s="104"/>
-      <c r="G30" s="104"/>
-      <c r="H30" s="105"/>
+      <c r="D30" s="105"/>
+      <c r="E30" s="106"/>
+      <c r="F30" s="106"/>
+      <c r="G30" s="106"/>
+      <c r="H30" s="107"/>
+      <c r="J30" s="142" t="s">
+        <v>505</v>
+      </c>
+      <c r="K30" s="143"/>
+      <c r="L30" s="144"/>
       <c r="AK30" s="4">
         <f t="shared" si="1"/>
         <v>6420</v>
       </c>
     </row>
-    <row r="31" spans="1:37">
+    <row r="31" spans="1:37" ht="19.5" thickBot="1">
       <c r="A31" s="6">
         <f t="shared" si="0"/>
         <v>30</v>
@@ -5454,11 +4661,16 @@
         <f>IF(D$2="Your Name Here","Enter Name",ROUND(_xlfn.NORM.INV(Random!D41,20,15),1))</f>
         <v>Enter Name</v>
       </c>
-      <c r="D31" s="103"/>
-      <c r="E31" s="104"/>
-      <c r="F31" s="104"/>
-      <c r="G31" s="104"/>
-      <c r="H31" s="105"/>
+      <c r="D31" s="105"/>
+      <c r="E31" s="106"/>
+      <c r="F31" s="106"/>
+      <c r="G31" s="106"/>
+      <c r="H31" s="107"/>
+      <c r="J31" s="142" t="s">
+        <v>506</v>
+      </c>
+      <c r="K31" s="143"/>
+      <c r="L31" s="144"/>
       <c r="AK31" s="4">
         <f t="shared" si="1"/>
         <v>4161</v>
@@ -5473,11 +4685,11 @@
         <f>IF(D$2="Your Name Here","Enter Name",ROUND(_xlfn.NORM.INV(Random!D42,20,15),1))</f>
         <v>Enter Name</v>
       </c>
-      <c r="D32" s="103"/>
-      <c r="E32" s="104"/>
-      <c r="F32" s="104"/>
-      <c r="G32" s="104"/>
-      <c r="H32" s="105"/>
+      <c r="D32" s="105"/>
+      <c r="E32" s="106"/>
+      <c r="F32" s="106"/>
+      <c r="G32" s="106"/>
+      <c r="H32" s="107"/>
       <c r="AK32" s="4">
         <f t="shared" si="1"/>
         <v>5022</v>
@@ -5492,11 +4704,11 @@
         <f>IF(D$2="Your Name Here","Enter Name",ROUND(_xlfn.NORM.INV(Random!D43,20,15),1))</f>
         <v>Enter Name</v>
       </c>
-      <c r="D33" s="103"/>
-      <c r="E33" s="104"/>
-      <c r="F33" s="104"/>
-      <c r="G33" s="104"/>
-      <c r="H33" s="105"/>
+      <c r="D33" s="105"/>
+      <c r="E33" s="106"/>
+      <c r="F33" s="106"/>
+      <c r="G33" s="106"/>
+      <c r="H33" s="107"/>
       <c r="AK33" s="4">
         <f t="shared" si="1"/>
         <v>3963</v>
@@ -5511,11 +4723,11 @@
         <f>IF(D$2="Your Name Here","Enter Name",ROUND(_xlfn.NORM.INV(Random!D44,20,15),1))</f>
         <v>Enter Name</v>
       </c>
-      <c r="D34" s="103"/>
-      <c r="E34" s="104"/>
-      <c r="F34" s="104"/>
-      <c r="G34" s="104"/>
-      <c r="H34" s="105"/>
+      <c r="D34" s="105"/>
+      <c r="E34" s="106"/>
+      <c r="F34" s="106"/>
+      <c r="G34" s="106"/>
+      <c r="H34" s="107"/>
       <c r="AK34" s="4">
         <f t="shared" si="1"/>
         <v>3380</v>
@@ -5530,11 +4742,11 @@
         <f>IF(D$2="Your Name Here","Enter Name",ROUND(_xlfn.NORM.INV(Random!D45,20,15),1))</f>
         <v>Enter Name</v>
       </c>
-      <c r="D35" s="103"/>
-      <c r="E35" s="104"/>
-      <c r="F35" s="104"/>
-      <c r="G35" s="104"/>
-      <c r="H35" s="105"/>
+      <c r="D35" s="105"/>
+      <c r="E35" s="106"/>
+      <c r="F35" s="106"/>
+      <c r="G35" s="106"/>
+      <c r="H35" s="107"/>
       <c r="AK35" s="4">
         <f t="shared" si="1"/>
         <v>1093</v>
@@ -5549,11 +4761,11 @@
         <f>IF(D$2="Your Name Here","Enter Name",ROUND(_xlfn.NORM.INV(Random!D46,20,15),1))</f>
         <v>Enter Name</v>
       </c>
-      <c r="D36" s="103"/>
-      <c r="E36" s="104"/>
-      <c r="F36" s="104"/>
-      <c r="G36" s="104"/>
-      <c r="H36" s="105"/>
+      <c r="D36" s="105"/>
+      <c r="E36" s="106"/>
+      <c r="F36" s="106"/>
+      <c r="G36" s="106"/>
+      <c r="H36" s="107"/>
       <c r="AK36" s="4">
         <f t="shared" si="1"/>
         <v>6910</v>
@@ -5568,11 +4780,11 @@
         <f>IF(D$2="Your Name Here","Enter Name",ROUND(_xlfn.NORM.INV(Random!D47,20,15),1))</f>
         <v>Enter Name</v>
       </c>
-      <c r="D37" s="103"/>
-      <c r="E37" s="104"/>
-      <c r="F37" s="104"/>
-      <c r="G37" s="104"/>
-      <c r="H37" s="105"/>
+      <c r="D37" s="105"/>
+      <c r="E37" s="106"/>
+      <c r="F37" s="106"/>
+      <c r="G37" s="106"/>
+      <c r="H37" s="107"/>
       <c r="AK37" s="4">
         <f t="shared" si="1"/>
         <v>9151</v>
@@ -5587,11 +4799,11 @@
         <f>IF(D$2="Your Name Here","Enter Name",ROUND(_xlfn.NORM.INV(Random!D48,20,15),1))</f>
         <v>Enter Name</v>
       </c>
-      <c r="D38" s="103"/>
-      <c r="E38" s="104"/>
-      <c r="F38" s="104"/>
-      <c r="G38" s="104"/>
-      <c r="H38" s="105"/>
+      <c r="D38" s="105"/>
+      <c r="E38" s="106"/>
+      <c r="F38" s="106"/>
+      <c r="G38" s="106"/>
+      <c r="H38" s="107"/>
       <c r="AK38" s="4">
         <f t="shared" si="1"/>
         <v>2304</v>
@@ -5606,11 +4818,11 @@
         <f>IF(D$2="Your Name Here","Enter Name",ROUND(_xlfn.NORM.INV(Random!D49,20,15),1))</f>
         <v>Enter Name</v>
       </c>
-      <c r="D39" s="103"/>
-      <c r="E39" s="104"/>
-      <c r="F39" s="104"/>
-      <c r="G39" s="104"/>
-      <c r="H39" s="105"/>
+      <c r="D39" s="105"/>
+      <c r="E39" s="106"/>
+      <c r="F39" s="106"/>
+      <c r="G39" s="106"/>
+      <c r="H39" s="107"/>
       <c r="AK39" s="4">
         <f t="shared" si="1"/>
         <v>8105</v>
@@ -5625,11 +4837,11 @@
         <f>IF(D$2="Your Name Here","Enter Name",ROUND(_xlfn.NORM.INV(Random!D50,20,15),1))</f>
         <v>Enter Name</v>
       </c>
-      <c r="D40" s="106"/>
-      <c r="E40" s="107"/>
-      <c r="F40" s="107"/>
-      <c r="G40" s="107"/>
-      <c r="H40" s="108"/>
+      <c r="D40" s="108"/>
+      <c r="E40" s="109"/>
+      <c r="F40" s="109"/>
+      <c r="G40" s="109"/>
+      <c r="H40" s="110"/>
       <c r="AK40" s="4">
         <f t="shared" si="1"/>
         <v>4006</v>
@@ -6518,7 +5730,7 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="KtmsjmAtDQLDyqMZss2JToUwi0WfhTAUOtFvRU4AbgQM8hr0gj0bR7jvKLPHeZrfRCGTm90GzbbxeaBsyO2i2Q==" saltValue="PD74Wt5QUXpE0KrXj4s4Hw==" spinCount="100000" sheet="1" formatCells="0" formatColumns="0" insertColumns="0" insertHyperlinks="0"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="gggHqqpd7p5PNEmWbzUjBg+vdR0u66GfEo/xztKxLYBY+E98qJE8TSpjngra0Q7oh5XpkSVZtrwFlb2riKjktw==" saltValue="CHyH/JXwNeft5xPZnex4XQ==" spinCount="100000" sheet="1" formatCells="0" formatColumns="0" insertColumns="0" insertHyperlinks="0"/>
   <dataConsolidate/>
   <customSheetViews>
     <customSheetView guid="{8A50E3A6-4261-4BD1-A94F-918D0E3EEAC3}" hiddenColumns="1">
@@ -6527,40 +5739,48 @@
       <pageSetup orientation="portrait" r:id="rId1"/>
     </customSheetView>
   </customSheetViews>
-  <mergeCells count="11">
+  <mergeCells count="14">
     <mergeCell ref="D29:H40"/>
     <mergeCell ref="J2:K2"/>
     <mergeCell ref="D24:H27"/>
     <mergeCell ref="D9:H9"/>
     <mergeCell ref="J10:O23"/>
-    <mergeCell ref="F2:H2"/>
-    <mergeCell ref="F3:H3"/>
+    <mergeCell ref="F8:H8"/>
     <mergeCell ref="F4:H4"/>
     <mergeCell ref="N3:S3"/>
     <mergeCell ref="N2:S2"/>
     <mergeCell ref="N5:S5"/>
+    <mergeCell ref="J29:L29"/>
+    <mergeCell ref="J30:L30"/>
+    <mergeCell ref="J31:L31"/>
+    <mergeCell ref="J28:L28"/>
   </mergeCells>
   <conditionalFormatting sqref="E5:E7 D11:F21">
-    <cfRule type="expression" dxfId="5" priority="12">
+    <cfRule type="expression" dxfId="6" priority="13">
       <formula>AND(NOT(ISBLANK(D5)),NOT(_xlfn.ISFORMULA(D5)))</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="G22:H22">
+    <cfRule type="expression" dxfId="2" priority="1">
+      <formula>G22=G23</formula>
+    </cfRule>
+  </conditionalFormatting>
   <hyperlinks>
-    <hyperlink ref="F2:H2" r:id="rId2" display="Video for this" xr:uid="{A260878E-D017-4C87-ABE4-17DB98AF16A4}"/>
-    <hyperlink ref="F4" r:id="rId3" display="Video" xr:uid="{B7B383DF-200C-4381-8B7B-81190D70B7C8}"/>
-    <hyperlink ref="F3:H3" r:id="rId4" display="Video about #SPILL! " xr:uid="{50B49601-0425-4F30-B92C-0A354131C4C2}"/>
-    <hyperlink ref="F4:H4" r:id="rId5" display="Video (for online Excel labeling)" xr:uid="{7505B8F1-41E5-4715-BDF4-A3403EDADFB2}"/>
+    <hyperlink ref="F8:H8" r:id="rId2" display="Video for Frequency Distribution" xr:uid="{A260878E-D017-4C87-ABE4-17DB98AF16A4}"/>
+    <hyperlink ref="F4:H4" r:id="rId3" display="Video about #SPILL! " xr:uid="{50B49601-0425-4F30-B92C-0A354131C4C2}"/>
+    <hyperlink ref="J29:K29" r:id="rId4" display="Video for using the built0in histogram chart" xr:uid="{DBBB20A4-A94D-425B-8908-0B6367E90ABA}"/>
+    <hyperlink ref="J30:L30" r:id="rId5" display="Video for using a bar chart for the histogram" xr:uid="{C0D0B144-1D52-4998-A55C-5D4E96EEB73E}"/>
+    <hyperlink ref="J31:L31" r:id="rId6" display="Video using online Excel - both variants" xr:uid="{A92EF7FE-4B5B-43AB-A572-F559401C0BF2}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId6"/>
-  <drawing r:id="rId7"/>
+  <pageSetup orientation="portrait" r:id="rId7"/>
   <legacyDrawing r:id="rId8"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="expression" priority="11" id="{95EE6F23-0B2C-4FB6-A0DA-4CA5E8A7CDEA}">
-            <xm:f>Solution!$D11</xm:f>
+          <x14:cfRule type="expression" priority="12" id="{95EE6F23-0B2C-4FB6-A0DA-4CA5E8A7CDEA}">
+            <xm:f>D11=Solution!D11</xm:f>
             <x14:dxf>
               <font>
                 <b/>
@@ -6572,7 +5792,7 @@
           <xm:sqref>D11:F21</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="expression" priority="10" id="{DE6384A9-777C-486F-98B0-332395F82AE2}">
+          <x14:cfRule type="expression" priority="11" id="{DE6384A9-777C-486F-98B0-332395F82AE2}">
             <xm:f>ABS(E5-Solution!E5)&lt;=1</xm:f>
             <x14:dxf>
               <font>
@@ -6585,7 +5805,7 @@
           <xm:sqref>E5:E6</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="expression" priority="3" id="{174487E6-EF19-4EDA-A8E0-E0649208B2BD}">
+          <x14:cfRule type="expression" priority="4" id="{174487E6-EF19-4EDA-A8E0-E0649208B2BD}">
             <xm:f>ABS(E7-Solution!E7)&lt;0.001</xm:f>
             <x14:dxf>
               <font>
@@ -6598,7 +5818,7 @@
           <xm:sqref>E7</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="expression" priority="2" id="{246D2ADF-3B33-44BD-B369-436EC59685E8}">
+          <x14:cfRule type="expression" priority="3" id="{246D2ADF-3B33-44BD-B369-436EC59685E8}">
             <xm:f>Solution!$K36</xm:f>
             <x14:dxf>
               <font>
@@ -6608,7 +5828,7 @@
               </font>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="expression" priority="29" id="{03827A15-B0AA-4B09-A0D4-7D276C8E808E}">
+          <x14:cfRule type="expression" priority="30" id="{03827A15-B0AA-4B09-A0D4-7D276C8E808E}">
             <xm:f>AND(NOT(Solution!L$32),NOT(_xlfn.ISFORMULA(G11)),NOT(ISBLANK(G11)))</xm:f>
             <x14:dxf>
               <fill>
@@ -6621,7 +5841,7 @@
           <xm:sqref>G11:G21</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="expression" priority="1" id="{2454C867-EE89-4EA6-B198-26951C41E144}">
+          <x14:cfRule type="expression" priority="2" id="{2454C867-EE89-4EA6-B198-26951C41E144}">
             <xm:f>Solution!$P36</xm:f>
             <x14:dxf>
               <font>
@@ -6631,7 +5851,7 @@
               </font>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="expression" priority="23" id="{4E9ED7D7-7D3C-43AB-856B-D39E9D2A4C8F}">
+          <x14:cfRule type="expression" priority="24" id="{4E9ED7D7-7D3C-43AB-856B-D39E9D2A4C8F}">
             <xm:f>AND(NOT(_xlfn.ISFORMULA(H11)),NOT(Solution!Q$31),NOT(ISBLANK(H11)))</xm:f>
             <x14:dxf>
               <fill>
@@ -6650,2280 +5870,2270 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4A77C245-9072-4501-A0EA-4BD1B1BFE85C}">
+  <dimension ref="A1:M21"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="9.140625" style="80"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13">
+      <c r="A1" s="80" t="s">
+        <v>501</v>
+      </c>
+      <c r="B1" t="s">
+        <v>502</v>
+      </c>
+      <c r="C1" s="81">
+        <v>1</v>
+      </c>
+      <c r="D1" t="str">
+        <f>'Water Quality'!D2</f>
+        <v>Your Name Here</v>
+      </c>
+      <c r="F1" s="148" t="str">
+        <f ca="1">IF(M1="ACTIVE", "✓ Tracking Active", "⚠️ ERROR: Enable Iterative Calculations (File &gt; Options &gt; Formulas)")</f>
+        <v>✓ Tracking Active</v>
+      </c>
+      <c r="G1" s="148"/>
+      <c r="H1" s="148"/>
+      <c r="I1" s="148"/>
+      <c r="J1" s="148"/>
+      <c r="K1" s="148"/>
+      <c r="L1" s="148"/>
+      <c r="M1" s="80" t="str">
+        <f ca="1">IF(M1="ACTIVE", "ACTIVE", "ACTIVE")</f>
+        <v>ACTIVE</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13">
+      <c r="A2" s="80" t="str">
+        <f t="shared" ref="A2:A19" ca="1" si="0">IF(D$1&lt;&gt;A3,A3,A2)</f>
+        <v>Your Name Here</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
+      <c r="A3" s="80" t="str">
+        <f t="shared" ca="1" si="0"/>
+        <v>Your Name Here</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
+      <c r="A4" s="80" t="str">
+        <f t="shared" ca="1" si="0"/>
+        <v>Your Name Here</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
+      <c r="A5" s="80" t="str">
+        <f t="shared" ca="1" si="0"/>
+        <v>Your Name Here</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
+      <c r="A6" s="80" t="str">
+        <f t="shared" ca="1" si="0"/>
+        <v>Your Name Here</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13">
+      <c r="A7" s="80" t="str">
+        <f t="shared" ca="1" si="0"/>
+        <v>Your Name Here</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13">
+      <c r="A8" s="80" t="str">
+        <f t="shared" ca="1" si="0"/>
+        <v>Your Name Here</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13">
+      <c r="A9" s="80" t="str">
+        <f t="shared" ca="1" si="0"/>
+        <v>Your Name Here</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13">
+      <c r="A10" s="80" t="str">
+        <f t="shared" ca="1" si="0"/>
+        <v>Your Name Here</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13">
+      <c r="A11" s="80" t="str">
+        <f t="shared" ca="1" si="0"/>
+        <v>Your Name Here</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13">
+      <c r="A12" s="80" t="str">
+        <f t="shared" ca="1" si="0"/>
+        <v>Your Name Here</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13">
+      <c r="A13" s="80" t="str">
+        <f t="shared" ca="1" si="0"/>
+        <v>Your Name Here</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13">
+      <c r="A14" s="80" t="str">
+        <f t="shared" ca="1" si="0"/>
+        <v>Your Name Here</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13">
+      <c r="A15" s="80" t="str">
+        <f t="shared" ca="1" si="0"/>
+        <v>Your Name Here</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13">
+      <c r="A16" s="80" t="str">
+        <f t="shared" ca="1" si="0"/>
+        <v>Your Name Here</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1">
+      <c r="A17" s="80" t="str">
+        <f t="shared" ca="1" si="0"/>
+        <v>richard</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1">
+      <c r="A18" s="80" t="str">
+        <f t="shared" ca="1" si="0"/>
+        <v>Your Name</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1">
+      <c r="A19" s="80" t="str">
+        <f t="shared" ca="1" si="0"/>
+        <v>Your Name</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1">
+      <c r="A20" s="80" t="str">
+        <f ca="1">IF(D$1&lt;&gt;A21,A21,A20)</f>
+        <v>Your Name</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1">
+      <c r="A21" s="80" t="str">
+        <f ca="1">IF(C1="","",IF(D$1&lt;&gt;A21,D$1,A21))</f>
+        <v>Your Name Here</v>
+      </c>
+    </row>
+  </sheetData>
+  <sheetProtection algorithmName="SHA-512" hashValue="nWPn3QUGnbLdBzuH/hWUqUlTXthV2zQvIQzs2zx+LKbrbjm4KBrjsuKr9pBfs/hPBvFpvkqSgK0qDgj0NPlVxw==" saltValue="4TCMZNRtVgv4y5YbrM0fgA==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
+  <mergeCells count="1">
+    <mergeCell ref="F1:L1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{708DA8AD-4D2F-4B52-9C92-C51D1E89D60F}">
   <dimension ref="A1:AK103"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="9.140625" style="46"/>
-    <col min="2" max="2" width="11.85546875" style="46" customWidth="1"/>
-    <col min="3" max="3" width="9" style="43" customWidth="1"/>
-    <col min="4" max="4" width="20.140625" style="43" customWidth="1"/>
-    <col min="5" max="5" width="19.42578125" style="43" customWidth="1"/>
-    <col min="6" max="6" width="14" style="43" customWidth="1"/>
-    <col min="7" max="7" width="11.42578125" style="43" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="18.85546875" style="43" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="2.28515625" style="43" customWidth="1"/>
-    <col min="10" max="10" width="22.7109375" style="43" customWidth="1"/>
-    <col min="11" max="11" width="22.28515625" style="43" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="23.42578125" style="43" bestFit="1" customWidth="1"/>
-    <col min="13" max="36" width="9.140625" style="43"/>
-    <col min="37" max="37" width="12.85546875" style="43" hidden="1" customWidth="1"/>
-    <col min="38" max="16384" width="9.140625" style="43"/>
+    <col min="1" max="1" width="9.140625" style="42"/>
+    <col min="2" max="2" width="11.85546875" style="42" customWidth="1"/>
+    <col min="3" max="3" width="9" style="39" customWidth="1"/>
+    <col min="4" max="4" width="20.140625" style="39" customWidth="1"/>
+    <col min="5" max="5" width="19.42578125" style="39" customWidth="1"/>
+    <col min="6" max="6" width="14" style="39" customWidth="1"/>
+    <col min="7" max="7" width="11.42578125" style="39" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="18.85546875" style="39" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="2.28515625" style="39" customWidth="1"/>
+    <col min="10" max="10" width="22.7109375" style="39" customWidth="1"/>
+    <col min="11" max="11" width="22.28515625" style="39" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="23.42578125" style="39" bestFit="1" customWidth="1"/>
+    <col min="13" max="36" width="9.140625" style="39"/>
+    <col min="37" max="37" width="12.85546875" style="39" hidden="1" customWidth="1"/>
+    <col min="38" max="16384" width="9.140625" style="39"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:37" ht="43.9" customHeight="1" thickBot="1">
-      <c r="A1" s="41" t="s">
+      <c r="A1" s="37" t="s">
         <v>9</v>
       </c>
-      <c r="B1" s="42" t="s">
+      <c r="B1" s="38" t="s">
         <v>10</v>
       </c>
-      <c r="D1" s="44" t="s">
+      <c r="D1" s="40" t="s">
         <v>11</v>
       </c>
-      <c r="F1" s="45"/>
-      <c r="G1" s="45"/>
-      <c r="H1" s="45"/>
+      <c r="F1" s="41"/>
+      <c r="G1" s="41"/>
+      <c r="H1" s="41"/>
     </row>
     <row r="2" spans="1:37" ht="20.25" thickTop="1" thickBot="1">
-      <c r="A2" s="46">
-        <v>1</v>
-      </c>
-      <c r="B2" s="46" t="str">
+      <c r="A2" s="42">
+        <v>1</v>
+      </c>
+      <c r="B2" s="42" t="str">
         <f>IF(D$2="Your Name Here","Enter Name",ROUND(_xlfn.NORM.INV(Random!D12,20,15),1))</f>
         <v>Enter Name</v>
       </c>
-      <c r="D2" s="47" t="str">
+      <c r="D2" s="43" t="str">
         <f>'Water Quality'!D2</f>
         <v>Your Name Here</v>
       </c>
-      <c r="E2" s="48"/>
-      <c r="F2" s="166" t="s">
+      <c r="E2" s="44"/>
+      <c r="F2" s="175" t="s">
         <v>12</v>
       </c>
-      <c r="G2" s="167"/>
-      <c r="H2" s="168"/>
-      <c r="J2" s="169" t="s">
+      <c r="G2" s="176"/>
+      <c r="H2" s="177"/>
+      <c r="J2" s="178" t="s">
         <v>13</v>
       </c>
-      <c r="K2" s="170"/>
-      <c r="AK2" s="43">
+      <c r="K2" s="179"/>
+      <c r="AK2" s="39">
         <f>MOD(CODE(MID(D2,1,1))*CODE(MID(D2,2,1))*CODE(MID(D2,3,1))*1103515245 + 12345,9172)</f>
         <v>5008</v>
       </c>
     </row>
     <row r="3" spans="1:37" ht="19.5" thickBot="1">
-      <c r="A3" s="46">
+      <c r="A3" s="42">
         <f>A2+1</f>
         <v>2</v>
       </c>
-      <c r="B3" s="46" t="str">
+      <c r="B3" s="42" t="str">
         <f>IF(D$2="Your Name Here","Enter Name",ROUND(_xlfn.NORM.INV(Random!D13,20,15),1))</f>
         <v>Enter Name</v>
       </c>
-      <c r="E3" s="48"/>
-      <c r="F3" s="166" t="s">
+      <c r="E3" s="44"/>
+      <c r="F3" s="175" t="s">
         <v>15</v>
       </c>
-      <c r="G3" s="167"/>
-      <c r="H3" s="168"/>
-      <c r="J3" s="49" t="s">
+      <c r="G3" s="176"/>
+      <c r="H3" s="177"/>
+      <c r="J3" s="45" t="s">
         <v>16</v>
       </c>
-      <c r="K3" s="50" t="s">
+      <c r="K3" s="46" t="s">
         <v>17</v>
       </c>
-      <c r="AK3" s="43">
+      <c r="AK3" s="39">
         <f>MOD(AK2*1103515245 + 12345,9172)</f>
         <v>6441</v>
       </c>
     </row>
     <row r="4" spans="1:37" ht="19.5" customHeight="1" thickBot="1">
-      <c r="A4" s="46">
+      <c r="A4" s="42">
         <f t="shared" ref="A4:A67" si="0">A3+1</f>
         <v>3</v>
       </c>
-      <c r="B4" s="46" t="str">
+      <c r="B4" s="42" t="str">
         <f>IF(D$2="Your Name Here","Enter Name",ROUND(_xlfn.NORM.INV(Random!D14,20,15),1))</f>
         <v>Enter Name</v>
       </c>
-      <c r="D4" s="51" t="s">
+      <c r="D4" s="47" t="s">
         <v>19</v>
       </c>
-      <c r="E4" s="52"/>
-      <c r="F4" s="166" t="s">
+      <c r="E4" s="48"/>
+      <c r="F4" s="175" t="s">
         <v>20</v>
       </c>
-      <c r="G4" s="167"/>
-      <c r="H4" s="168"/>
-      <c r="J4" s="49" t="s">
+      <c r="G4" s="176"/>
+      <c r="H4" s="177"/>
+      <c r="J4" s="45" t="s">
         <v>21</v>
       </c>
-      <c r="K4" s="50" t="s">
+      <c r="K4" s="46" t="s">
         <v>22</v>
       </c>
-      <c r="AK4" s="43">
+      <c r="AK4" s="39">
         <f t="shared" ref="AK4:AK67" si="1">MOD(AK3*1103515245 + 12345,9172)</f>
         <v>5030</v>
       </c>
     </row>
     <row r="5" spans="1:37" ht="16.5" customHeight="1" thickBot="1">
-      <c r="A5" s="46">
+      <c r="A5" s="42">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="B5" s="46" t="str">
+      <c r="B5" s="42" t="str">
         <f>IF(D$2="Your Name Here","Enter Name",ROUND(_xlfn.NORM.INV(Random!D15,20,15),1))</f>
         <v>Enter Name</v>
       </c>
       <c r="D5" s="26" t="s">
         <v>24</v>
       </c>
-      <c r="E5" s="53">
+      <c r="E5" s="49">
         <f>MIN(B:B)</f>
         <v>0</v>
       </c>
-      <c r="G5" s="54"/>
-      <c r="H5" s="55"/>
-      <c r="J5" s="49" t="s">
+      <c r="G5" s="50"/>
+      <c r="H5" s="51"/>
+      <c r="J5" s="45" t="s">
         <v>25</v>
       </c>
-      <c r="K5" s="50" t="s">
+      <c r="K5" s="46" t="s">
         <v>26</v>
       </c>
-      <c r="AK5" s="43">
+      <c r="AK5" s="39">
         <f t="shared" si="1"/>
         <v>2547</v>
       </c>
     </row>
     <row r="6" spans="1:37" ht="15.75">
-      <c r="A6" s="46">
+      <c r="A6" s="42">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="B6" s="46" t="str">
+      <c r="B6" s="42" t="str">
         <f>IF(D$2="Your Name Here","Enter Name",ROUND(_xlfn.NORM.INV(Random!D16,20,15),1))</f>
         <v>Enter Name</v>
       </c>
       <c r="D6" s="29" t="s">
         <v>28</v>
       </c>
-      <c r="E6" s="56">
+      <c r="E6" s="52">
         <f>MAX(B:B)</f>
         <v>0</v>
       </c>
-      <c r="G6" s="171" t="s">
+      <c r="G6" s="180" t="s">
         <v>45</v>
       </c>
-      <c r="H6" s="172"/>
-      <c r="J6" s="49" t="s">
+      <c r="H6" s="181"/>
+      <c r="J6" s="45" t="s">
         <v>29</v>
       </c>
-      <c r="K6" s="50" t="s">
+      <c r="K6" s="46" t="s">
         <v>30</v>
       </c>
-      <c r="AK6" s="43">
+      <c r="AK6" s="39">
         <f t="shared" si="1"/>
         <v>6368</v>
       </c>
     </row>
     <row r="7" spans="1:37" ht="16.5" thickBot="1">
-      <c r="A7" s="46">
+      <c r="A7" s="42">
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
-      <c r="B7" s="46" t="str">
+      <c r="B7" s="42" t="str">
         <f>IF(D$2="Your Name Here","Enter Name",ROUND(_xlfn.NORM.INV(Random!D17,20,15),1))</f>
         <v>Enter Name</v>
       </c>
       <c r="D7" s="30" t="s">
         <v>31</v>
       </c>
-      <c r="E7" s="57">
+      <c r="E7" s="53">
         <f>('Water Quality'!E6-'Water Quality'!E5)/11</f>
         <v>0</v>
       </c>
-      <c r="G7" s="173"/>
-      <c r="H7" s="174"/>
-      <c r="J7" s="58" t="s">
+      <c r="G7" s="182"/>
+      <c r="H7" s="183"/>
+      <c r="J7" s="54" t="s">
         <v>32</v>
       </c>
-      <c r="K7" s="59" t="s">
+      <c r="K7" s="55" t="s">
         <v>33</v>
       </c>
-      <c r="AK7" s="43">
+      <c r="AK7" s="39">
         <f t="shared" si="1"/>
         <v>4193</v>
       </c>
     </row>
     <row r="8" spans="1:37" ht="15.75" thickBot="1">
-      <c r="A8" s="46">
+      <c r="A8" s="42">
         <f t="shared" si="0"/>
         <v>7</v>
       </c>
-      <c r="B8" s="46" t="str">
+      <c r="B8" s="42" t="str">
         <f>IF(D$2="Your Name Here","Enter Name",ROUND(_xlfn.NORM.INV(Random!D18,20,15),1))</f>
         <v>Enter Name</v>
       </c>
-      <c r="AK8" s="43">
+      <c r="AK8" s="39">
         <f>MOD(AK7*1103515245 + 12345,9172)</f>
         <v>8530</v>
       </c>
     </row>
     <row r="9" spans="1:37" ht="15.75" thickBot="1">
-      <c r="A9" s="46">
+      <c r="A9" s="42">
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
-      <c r="B9" s="46" t="str">
+      <c r="B9" s="42" t="str">
         <f>IF(D$2="Your Name Here","Enter Name",ROUND(_xlfn.NORM.INV(Random!D19,20,15),1))</f>
         <v>Enter Name</v>
       </c>
-      <c r="D9" s="175" t="s">
+      <c r="D9" s="184" t="s">
         <v>34</v>
       </c>
-      <c r="E9" s="176"/>
-      <c r="F9" s="176"/>
-      <c r="G9" s="176"/>
-      <c r="H9" s="177"/>
-      <c r="AK9" s="43">
+      <c r="E9" s="185"/>
+      <c r="F9" s="185"/>
+      <c r="G9" s="185"/>
+      <c r="H9" s="186"/>
+      <c r="AK9" s="39">
         <f t="shared" si="1"/>
         <v>6743</v>
       </c>
     </row>
     <row r="10" spans="1:37" ht="15" customHeight="1" thickBot="1">
-      <c r="A10" s="46">
+      <c r="A10" s="42">
         <f t="shared" si="0"/>
         <v>9</v>
       </c>
-      <c r="B10" s="46" t="str">
+      <c r="B10" s="42" t="str">
         <f>IF(D$2="Your Name Here","Enter Name",ROUND(_xlfn.NORM.INV(Random!D20,20,15),1))</f>
         <v>Enter Name</v>
       </c>
-      <c r="D10" s="60" t="s">
+      <c r="D10" s="56" t="s">
         <v>35</v>
       </c>
-      <c r="E10" s="61" t="s">
+      <c r="E10" s="57" t="s">
         <v>36</v>
       </c>
-      <c r="F10" s="61" t="s">
+      <c r="F10" s="57" t="s">
         <v>46</v>
       </c>
-      <c r="G10" s="61" t="s">
+      <c r="G10" s="57" t="s">
         <v>38</v>
       </c>
-      <c r="H10" s="62" t="s">
+      <c r="H10" s="58" t="s">
         <v>39</v>
       </c>
-      <c r="J10" s="140" t="s">
+      <c r="J10" s="149" t="s">
         <v>47</v>
       </c>
-      <c r="K10" s="141"/>
-      <c r="L10" s="141"/>
-      <c r="M10" s="141"/>
-      <c r="N10" s="141"/>
-      <c r="O10" s="142"/>
-      <c r="AK10" s="43">
+      <c r="K10" s="150"/>
+      <c r="L10" s="150"/>
+      <c r="M10" s="150"/>
+      <c r="N10" s="150"/>
+      <c r="O10" s="151"/>
+      <c r="AK10" s="39">
         <f t="shared" si="1"/>
         <v>6608</v>
       </c>
     </row>
     <row r="11" spans="1:37" ht="15.75">
-      <c r="A11" s="46">
+      <c r="A11" s="42">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="B11" s="46" t="str">
+      <c r="B11" s="42" t="str">
         <f>IF(D$2="Your Name Here","Enter Name",ROUND(_xlfn.NORM.INV(Random!D21,20,15),1))</f>
         <v>Enter Name</v>
       </c>
-      <c r="D11" s="63">
+      <c r="D11" s="59">
         <f>'Water Quality'!E5</f>
         <v>0</v>
       </c>
-      <c r="E11" s="64">
+      <c r="E11" s="60">
         <f>D11+'Water Quality'!E$7</f>
         <v>0</v>
       </c>
-      <c r="F11" s="64">
+      <c r="F11" s="60">
         <f>(D11+E11)/2</f>
         <v>0</v>
       </c>
-      <c r="G11" s="65" cm="1">
+      <c r="G11" s="61" cm="1">
         <f t="array" ref="G11:G21">FREQUENCY(B:B,E11:E20)</f>
         <v>0</v>
       </c>
-      <c r="H11" s="66" t="e" cm="1">
+      <c r="H11" s="62" t="e" cm="1">
         <f t="array" ref="H11:H21">_xlfn.ANCHORARRAY(G11)/SUM(_xlfn.ANCHORARRAY(G11))</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="J11" s="143"/>
-      <c r="K11" s="144"/>
-      <c r="L11" s="144"/>
-      <c r="M11" s="144"/>
-      <c r="N11" s="144"/>
-      <c r="O11" s="145"/>
-      <c r="AK11" s="43">
+      <c r="J11" s="152"/>
+      <c r="K11" s="153"/>
+      <c r="L11" s="153"/>
+      <c r="M11" s="153"/>
+      <c r="N11" s="153"/>
+      <c r="O11" s="154"/>
+      <c r="AK11" s="39">
         <f t="shared" si="1"/>
         <v>7573</v>
       </c>
     </row>
     <row r="12" spans="1:37" ht="15.75">
-      <c r="A12" s="46">
+      <c r="A12" s="42">
         <f t="shared" si="0"/>
         <v>11</v>
       </c>
-      <c r="B12" s="46" t="str">
+      <c r="B12" s="42" t="str">
         <f>IF(D$2="Your Name Here","Enter Name",ROUND(_xlfn.NORM.INV(Random!D22,20,15),1))</f>
         <v>Enter Name</v>
       </c>
-      <c r="D12" s="67">
+      <c r="D12" s="63">
         <f>E11</f>
         <v>0</v>
       </c>
-      <c r="E12" s="64">
+      <c r="E12" s="60">
         <f>D12+'Water Quality'!E$7</f>
         <v>0</v>
       </c>
-      <c r="F12" s="64">
+      <c r="F12" s="60">
         <f t="shared" ref="F12:F21" si="2">(D12+E12)/2</f>
         <v>0</v>
       </c>
-      <c r="G12" s="65">
-        <v>0</v>
-      </c>
-      <c r="H12" s="66" t="e">
+      <c r="G12" s="61">
+        <v>0</v>
+      </c>
+      <c r="H12" s="62" t="e">
         <v>#DIV/0!</v>
       </c>
-      <c r="J12" s="143"/>
-      <c r="K12" s="144"/>
-      <c r="L12" s="144"/>
-      <c r="M12" s="144"/>
-      <c r="N12" s="144"/>
-      <c r="O12" s="145"/>
-      <c r="AK12" s="43">
+      <c r="J12" s="152"/>
+      <c r="K12" s="153"/>
+      <c r="L12" s="153"/>
+      <c r="M12" s="153"/>
+      <c r="N12" s="153"/>
+      <c r="O12" s="154"/>
+      <c r="AK12" s="39">
         <f t="shared" si="1"/>
         <v>6450</v>
       </c>
     </row>
     <row r="13" spans="1:37" ht="15.75">
-      <c r="A13" s="46">
+      <c r="A13" s="42">
         <f t="shared" si="0"/>
         <v>12</v>
       </c>
-      <c r="B13" s="46" t="str">
+      <c r="B13" s="42" t="str">
         <f>IF(D$2="Your Name Here","Enter Name",ROUND(_xlfn.NORM.INV(Random!D23,20,15),1))</f>
         <v>Enter Name</v>
       </c>
-      <c r="D13" s="67">
+      <c r="D13" s="63">
         <f t="shared" ref="D13:D21" si="3">E12</f>
         <v>0</v>
       </c>
-      <c r="E13" s="64">
+      <c r="E13" s="60">
         <f>D13+'Water Quality'!E$7</f>
         <v>0</v>
       </c>
-      <c r="F13" s="64">
+      <c r="F13" s="60">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="G13" s="65">
-        <v>0</v>
-      </c>
-      <c r="H13" s="66" t="e">
+      <c r="G13" s="61">
+        <v>0</v>
+      </c>
+      <c r="H13" s="62" t="e">
         <v>#DIV/0!</v>
       </c>
-      <c r="J13" s="143"/>
-      <c r="K13" s="144"/>
-      <c r="L13" s="144"/>
-      <c r="M13" s="144"/>
-      <c r="N13" s="144"/>
-      <c r="O13" s="145"/>
-      <c r="AK13" s="43">
+      <c r="J13" s="152"/>
+      <c r="K13" s="153"/>
+      <c r="L13" s="153"/>
+      <c r="M13" s="153"/>
+      <c r="N13" s="153"/>
+      <c r="O13" s="154"/>
+      <c r="AK13" s="39">
         <f t="shared" si="1"/>
         <v>8023</v>
       </c>
     </row>
     <row r="14" spans="1:37" ht="15.75">
-      <c r="A14" s="46">
+      <c r="A14" s="42">
         <f t="shared" si="0"/>
         <v>13</v>
       </c>
-      <c r="B14" s="46" t="str">
+      <c r="B14" s="42" t="str">
         <f>IF(D$2="Your Name Here","Enter Name",ROUND(_xlfn.NORM.INV(Random!D24,20,15),1))</f>
         <v>Enter Name</v>
       </c>
-      <c r="D14" s="67">
+      <c r="D14" s="63">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="E14" s="64">
+      <c r="E14" s="60">
         <f>D14+'Water Quality'!E$7</f>
         <v>0</v>
       </c>
-      <c r="F14" s="64">
+      <c r="F14" s="60">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="G14" s="65">
-        <v>0</v>
-      </c>
-      <c r="H14" s="66" t="e">
+      <c r="G14" s="61">
+        <v>0</v>
+      </c>
+      <c r="H14" s="62" t="e">
         <v>#DIV/0!</v>
       </c>
-      <c r="J14" s="143"/>
-      <c r="K14" s="144"/>
-      <c r="L14" s="144"/>
-      <c r="M14" s="144"/>
-      <c r="N14" s="144"/>
-      <c r="O14" s="145"/>
-      <c r="AK14" s="43">
+      <c r="J14" s="152"/>
+      <c r="K14" s="153"/>
+      <c r="L14" s="153"/>
+      <c r="M14" s="153"/>
+      <c r="N14" s="153"/>
+      <c r="O14" s="154"/>
+      <c r="AK14" s="39">
         <f>MOD(AK13*1103515245 + 12345,9172)</f>
         <v>176</v>
       </c>
     </row>
     <row r="15" spans="1:37" ht="15.75">
-      <c r="A15" s="46">
+      <c r="A15" s="42">
         <f t="shared" si="0"/>
         <v>14</v>
       </c>
-      <c r="B15" s="46" t="str">
+      <c r="B15" s="42" t="str">
         <f>IF(D$2="Your Name Here","Enter Name",ROUND(_xlfn.NORM.INV(Random!D25,20,15),1))</f>
         <v>Enter Name</v>
       </c>
-      <c r="D15" s="67">
+      <c r="D15" s="63">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="E15" s="64">
+      <c r="E15" s="60">
         <f>D15+'Water Quality'!E$7</f>
         <v>0</v>
       </c>
-      <c r="F15" s="64">
+      <c r="F15" s="60">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="G15" s="65">
-        <v>0</v>
-      </c>
-      <c r="H15" s="66" t="e">
+      <c r="G15" s="61">
+        <v>0</v>
+      </c>
+      <c r="H15" s="62" t="e">
         <v>#DIV/0!</v>
       </c>
-      <c r="J15" s="143"/>
-      <c r="K15" s="144"/>
-      <c r="L15" s="144"/>
-      <c r="M15" s="144"/>
-      <c r="N15" s="144"/>
-      <c r="O15" s="145"/>
-      <c r="AK15" s="43">
+      <c r="J15" s="152"/>
+      <c r="K15" s="153"/>
+      <c r="L15" s="153"/>
+      <c r="M15" s="153"/>
+      <c r="N15" s="153"/>
+      <c r="O15" s="154"/>
+      <c r="AK15" s="39">
         <f t="shared" si="1"/>
         <v>8709</v>
       </c>
     </row>
     <row r="16" spans="1:37" ht="15.75" customHeight="1">
-      <c r="A16" s="46">
+      <c r="A16" s="42">
         <f t="shared" si="0"/>
         <v>15</v>
       </c>
-      <c r="B16" s="46" t="str">
+      <c r="B16" s="42" t="str">
         <f>IF(D$2="Your Name Here","Enter Name",ROUND(_xlfn.NORM.INV(Random!D26,20,15),1))</f>
         <v>Enter Name</v>
       </c>
-      <c r="D16" s="67">
+      <c r="D16" s="63">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="E16" s="64">
+      <c r="E16" s="60">
         <f>D16+'Water Quality'!E$7</f>
         <v>0</v>
       </c>
-      <c r="F16" s="64">
+      <c r="F16" s="60">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="G16" s="65">
-        <v>0</v>
-      </c>
-      <c r="H16" s="66" t="e">
+      <c r="G16" s="61">
+        <v>0</v>
+      </c>
+      <c r="H16" s="62" t="e">
         <v>#DIV/0!</v>
       </c>
-      <c r="J16" s="143"/>
-      <c r="K16" s="144"/>
-      <c r="L16" s="144"/>
-      <c r="M16" s="144"/>
-      <c r="N16" s="144"/>
-      <c r="O16" s="145"/>
-      <c r="AK16" s="43">
+      <c r="J16" s="152"/>
+      <c r="K16" s="153"/>
+      <c r="L16" s="153"/>
+      <c r="M16" s="153"/>
+      <c r="N16" s="153"/>
+      <c r="O16" s="154"/>
+      <c r="AK16" s="39">
         <f t="shared" si="1"/>
         <v>7162</v>
       </c>
     </row>
     <row r="17" spans="1:37" ht="15.75">
-      <c r="A17" s="46">
+      <c r="A17" s="42">
         <f t="shared" si="0"/>
         <v>16</v>
       </c>
-      <c r="B17" s="46" t="str">
+      <c r="B17" s="42" t="str">
         <f>IF(D$2="Your Name Here","Enter Name",ROUND(_xlfn.NORM.INV(Random!D27,20,15),1))</f>
         <v>Enter Name</v>
       </c>
-      <c r="D17" s="67">
+      <c r="D17" s="63">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="E17" s="64">
+      <c r="E17" s="60">
         <f>D17+'Water Quality'!E$7</f>
         <v>0</v>
       </c>
-      <c r="F17" s="64">
+      <c r="F17" s="60">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="G17" s="65">
-        <v>0</v>
-      </c>
-      <c r="H17" s="66" t="e">
+      <c r="G17" s="61">
+        <v>0</v>
+      </c>
+      <c r="H17" s="62" t="e">
         <v>#DIV/0!</v>
       </c>
-      <c r="J17" s="143"/>
-      <c r="K17" s="144"/>
-      <c r="L17" s="144"/>
-      <c r="M17" s="144"/>
-      <c r="N17" s="144"/>
-      <c r="O17" s="145"/>
-      <c r="AK17" s="43">
+      <c r="J17" s="152"/>
+      <c r="K17" s="153"/>
+      <c r="L17" s="153"/>
+      <c r="M17" s="153"/>
+      <c r="N17" s="153"/>
+      <c r="O17" s="154"/>
+      <c r="AK17" s="39">
         <f t="shared" si="1"/>
         <v>1235</v>
       </c>
     </row>
     <row r="18" spans="1:37" ht="15.75">
-      <c r="A18" s="46">
+      <c r="A18" s="42">
         <f t="shared" si="0"/>
         <v>17</v>
       </c>
-      <c r="B18" s="46" t="str">
+      <c r="B18" s="42" t="str">
         <f>IF(D$2="Your Name Here","Enter Name",ROUND(_xlfn.NORM.INV(Random!D28,20,15),1))</f>
         <v>Enter Name</v>
       </c>
-      <c r="D18" s="67">
+      <c r="D18" s="63">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="E18" s="64">
+      <c r="E18" s="60">
         <f>D18+'Water Quality'!E$7</f>
         <v>0</v>
       </c>
-      <c r="F18" s="64">
+      <c r="F18" s="60">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="G18" s="65">
-        <v>0</v>
-      </c>
-      <c r="H18" s="66" t="e">
+      <c r="G18" s="61">
+        <v>0</v>
+      </c>
+      <c r="H18" s="62" t="e">
         <v>#DIV/0!</v>
       </c>
-      <c r="J18" s="143"/>
-      <c r="K18" s="144"/>
-      <c r="L18" s="144"/>
-      <c r="M18" s="144"/>
-      <c r="N18" s="144"/>
-      <c r="O18" s="145"/>
-      <c r="AK18" s="43">
+      <c r="J18" s="152"/>
+      <c r="K18" s="153"/>
+      <c r="L18" s="153"/>
+      <c r="M18" s="153"/>
+      <c r="N18" s="153"/>
+      <c r="O18" s="154"/>
+      <c r="AK18" s="39">
         <f t="shared" si="1"/>
         <v>120</v>
       </c>
     </row>
     <row r="19" spans="1:37" ht="15" customHeight="1">
-      <c r="A19" s="46">
+      <c r="A19" s="42">
         <f t="shared" si="0"/>
         <v>18</v>
       </c>
-      <c r="B19" s="46" t="str">
+      <c r="B19" s="42" t="str">
         <f>IF(D$2="Your Name Here","Enter Name",ROUND(_xlfn.NORM.INV(Random!D29,20,15),1))</f>
         <v>Enter Name</v>
       </c>
-      <c r="D19" s="67">
+      <c r="D19" s="63">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="E19" s="64">
+      <c r="E19" s="60">
         <f>D19+'Water Quality'!E$7</f>
         <v>0</v>
       </c>
-      <c r="F19" s="64">
+      <c r="F19" s="60">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="G19" s="65">
-        <v>0</v>
-      </c>
-      <c r="H19" s="66" t="e">
+      <c r="G19" s="61">
+        <v>0</v>
+      </c>
+      <c r="H19" s="62" t="e">
         <v>#DIV/0!</v>
       </c>
-      <c r="J19" s="143"/>
-      <c r="K19" s="144"/>
-      <c r="L19" s="144"/>
-      <c r="M19" s="144"/>
-      <c r="N19" s="144"/>
-      <c r="O19" s="145"/>
-      <c r="Q19" s="68"/>
-      <c r="AK19" s="43">
+      <c r="J19" s="152"/>
+      <c r="K19" s="153"/>
+      <c r="L19" s="153"/>
+      <c r="M19" s="153"/>
+      <c r="N19" s="153"/>
+      <c r="O19" s="154"/>
+      <c r="Q19" s="64"/>
+      <c r="AK19" s="39">
         <f t="shared" si="1"/>
         <v>277</v>
       </c>
     </row>
     <row r="20" spans="1:37" ht="15.75">
-      <c r="A20" s="46">
+      <c r="A20" s="42">
         <f t="shared" si="0"/>
         <v>19</v>
       </c>
-      <c r="B20" s="46" t="str">
+      <c r="B20" s="42" t="str">
         <f>IF(D$2="Your Name Here","Enter Name",ROUND(_xlfn.NORM.INV(Random!D30,20,15),1))</f>
         <v>Enter Name</v>
       </c>
-      <c r="D20" s="67">
+      <c r="D20" s="63">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="E20" s="64">
+      <c r="E20" s="60">
         <f>D20+'Water Quality'!E$7</f>
         <v>0</v>
       </c>
-      <c r="F20" s="64">
+      <c r="F20" s="60">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="G20" s="65">
-        <v>0</v>
-      </c>
-      <c r="H20" s="66" t="e">
+      <c r="G20" s="61">
+        <v>0</v>
+      </c>
+      <c r="H20" s="62" t="e">
         <v>#DIV/0!</v>
       </c>
-      <c r="J20" s="143"/>
-      <c r="K20" s="144"/>
-      <c r="L20" s="144"/>
-      <c r="M20" s="144"/>
-      <c r="N20" s="144"/>
-      <c r="O20" s="145"/>
-      <c r="Q20" s="68"/>
-      <c r="AK20" s="43">
+      <c r="J20" s="152"/>
+      <c r="K20" s="153"/>
+      <c r="L20" s="153"/>
+      <c r="M20" s="153"/>
+      <c r="N20" s="153"/>
+      <c r="O20" s="154"/>
+      <c r="Q20" s="64"/>
+      <c r="AK20" s="39">
         <f t="shared" si="1"/>
         <v>4590</v>
       </c>
     </row>
     <row r="21" spans="1:37" ht="16.5" thickBot="1">
-      <c r="A21" s="46">
+      <c r="A21" s="42">
         <f t="shared" si="0"/>
         <v>20</v>
       </c>
-      <c r="B21" s="46" t="str">
+      <c r="B21" s="42" t="str">
         <f>IF(D$2="Your Name Here","Enter Name",ROUND(_xlfn.NORM.INV(Random!D31,20,15),1))</f>
         <v>Enter Name</v>
       </c>
-      <c r="D21" s="67">
+      <c r="D21" s="63">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="E21" s="64">
+      <c r="E21" s="60">
         <f>D21+'Water Quality'!E$7</f>
         <v>0</v>
       </c>
-      <c r="F21" s="64">
+      <c r="F21" s="60">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="G21" s="69">
-        <v>0</v>
-      </c>
-      <c r="H21" s="70" t="e">
+      <c r="G21" s="65">
+        <v>0</v>
+      </c>
+      <c r="H21" s="66" t="e">
         <v>#DIV/0!</v>
       </c>
-      <c r="J21" s="143"/>
-      <c r="K21" s="144"/>
-      <c r="L21" s="144"/>
-      <c r="M21" s="144"/>
-      <c r="N21" s="144"/>
-      <c r="O21" s="145"/>
-      <c r="AK21" s="43">
+      <c r="J21" s="152"/>
+      <c r="K21" s="153"/>
+      <c r="L21" s="153"/>
+      <c r="M21" s="153"/>
+      <c r="N21" s="153"/>
+      <c r="O21" s="154"/>
+      <c r="AK21" s="39">
         <f t="shared" si="1"/>
         <v>7051</v>
       </c>
     </row>
     <row r="22" spans="1:37" ht="15.75" thickBot="1">
-      <c r="A22" s="46">
+      <c r="A22" s="42">
         <f t="shared" si="0"/>
         <v>21</v>
       </c>
-      <c r="B22" s="46" t="str">
+      <c r="B22" s="42" t="str">
         <f>IF(D$2="Your Name Here","Enter Name",ROUND(_xlfn.NORM.INV(Random!D32,20,15),1))</f>
         <v>Enter Name</v>
       </c>
-      <c r="F22" s="71" t="s">
+      <c r="F22" s="67" t="s">
         <v>41</v>
       </c>
-      <c r="G22" s="72">
+      <c r="G22" s="68">
         <f>SUM(G11:G21)</f>
         <v>0</v>
       </c>
-      <c r="H22" s="73" t="e">
+      <c r="H22" s="69" t="e">
         <f>SUM(H11:H21)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="J22" s="143"/>
-      <c r="K22" s="144"/>
-      <c r="L22" s="144"/>
-      <c r="M22" s="144"/>
-      <c r="N22" s="144"/>
-      <c r="O22" s="145"/>
-      <c r="AK22" s="43">
+      <c r="J22" s="152"/>
+      <c r="K22" s="153"/>
+      <c r="L22" s="153"/>
+      <c r="M22" s="153"/>
+      <c r="N22" s="153"/>
+      <c r="O22" s="154"/>
+      <c r="AK22" s="39">
         <f t="shared" si="1"/>
         <v>7124</v>
       </c>
     </row>
     <row r="23" spans="1:37" ht="14.45" customHeight="1" thickBot="1">
-      <c r="A23" s="46">
+      <c r="A23" s="42">
         <f t="shared" si="0"/>
         <v>22</v>
       </c>
-      <c r="B23" s="46" t="str">
+      <c r="B23" s="42" t="str">
         <f>IF(D$2="Your Name Here","Enter Name",ROUND(_xlfn.NORM.INV(Random!D33,20,15),1))</f>
         <v>Enter Name</v>
       </c>
-      <c r="F23" s="74" t="s">
+      <c r="F23" s="70" t="s">
         <v>42</v>
       </c>
-      <c r="G23" s="75">
+      <c r="G23" s="71">
         <v>102</v>
       </c>
-      <c r="H23" s="76">
-        <v>1</v>
-      </c>
-      <c r="J23" s="146"/>
-      <c r="K23" s="147"/>
-      <c r="L23" s="147"/>
-      <c r="M23" s="147"/>
-      <c r="N23" s="147"/>
-      <c r="O23" s="148"/>
-      <c r="AK23" s="43">
+      <c r="H23" s="72">
+        <v>1</v>
+      </c>
+      <c r="J23" s="155"/>
+      <c r="K23" s="156"/>
+      <c r="L23" s="156"/>
+      <c r="M23" s="156"/>
+      <c r="N23" s="156"/>
+      <c r="O23" s="157"/>
+      <c r="AK23" s="39">
         <f t="shared" si="1"/>
         <v>7961</v>
       </c>
     </row>
     <row r="24" spans="1:37">
-      <c r="A24" s="46">
+      <c r="A24" s="42">
         <f t="shared" si="0"/>
         <v>23</v>
       </c>
-      <c r="B24" s="46" t="str">
+      <c r="B24" s="42" t="str">
         <f>IF(D$2="Your Name Here","Enter Name",ROUND(_xlfn.NORM.INV(Random!D34,20,15),1))</f>
         <v>Enter Name</v>
       </c>
-      <c r="D24" s="149" t="s">
+      <c r="D24" s="158" t="s">
         <v>43</v>
       </c>
-      <c r="E24" s="150"/>
-      <c r="F24" s="151"/>
-      <c r="G24" s="151"/>
-      <c r="H24" s="152"/>
-      <c r="AK24" s="43">
+      <c r="E24" s="159"/>
+      <c r="F24" s="160"/>
+      <c r="G24" s="160"/>
+      <c r="H24" s="161"/>
+      <c r="AK24" s="39">
         <f t="shared" si="1"/>
         <v>1978</v>
       </c>
     </row>
     <row r="25" spans="1:37">
-      <c r="A25" s="46">
+      <c r="A25" s="42">
         <f t="shared" si="0"/>
         <v>24</v>
       </c>
-      <c r="B25" s="46" t="str">
+      <c r="B25" s="42" t="str">
         <f>IF(D$2="Your Name Here","Enter Name",ROUND(_xlfn.NORM.INV(Random!D35,20,15),1))</f>
         <v>Enter Name</v>
       </c>
-      <c r="D25" s="153"/>
-      <c r="E25" s="151"/>
-      <c r="F25" s="151"/>
-      <c r="G25" s="151"/>
-      <c r="H25" s="152"/>
-      <c r="AK25" s="43">
+      <c r="D25" s="162"/>
+      <c r="E25" s="160"/>
+      <c r="F25" s="160"/>
+      <c r="G25" s="160"/>
+      <c r="H25" s="161"/>
+      <c r="AK25" s="39">
         <f t="shared" si="1"/>
         <v>1603</v>
       </c>
     </row>
     <row r="26" spans="1:37">
-      <c r="A26" s="46">
+      <c r="A26" s="42">
         <f t="shared" si="0"/>
         <v>25</v>
       </c>
-      <c r="B26" s="46" t="str">
+      <c r="B26" s="42" t="str">
         <f>IF(D$2="Your Name Here","Enter Name",ROUND(_xlfn.NORM.INV(Random!D36,20,15),1))</f>
         <v>Enter Name</v>
       </c>
-      <c r="D26" s="153"/>
-      <c r="E26" s="151"/>
-      <c r="F26" s="151"/>
-      <c r="G26" s="151"/>
-      <c r="H26" s="152"/>
-      <c r="AK26" s="43">
+      <c r="D26" s="162"/>
+      <c r="E26" s="160"/>
+      <c r="F26" s="160"/>
+      <c r="G26" s="160"/>
+      <c r="H26" s="161"/>
+      <c r="AK26" s="39">
         <f t="shared" si="1"/>
         <v>8360</v>
       </c>
     </row>
     <row r="27" spans="1:37" ht="15.75" thickBot="1">
-      <c r="A27" s="46">
+      <c r="A27" s="42">
         <f t="shared" si="0"/>
         <v>26</v>
       </c>
-      <c r="B27" s="46" t="str">
+      <c r="B27" s="42" t="str">
         <f>IF(D$2="Your Name Here","Enter Name",ROUND(_xlfn.NORM.INV(Random!D37,20,15),1))</f>
         <v>Enter Name</v>
       </c>
-      <c r="D27" s="154"/>
-      <c r="E27" s="155"/>
-      <c r="F27" s="155"/>
-      <c r="G27" s="155"/>
-      <c r="H27" s="156"/>
-      <c r="AK27" s="43">
+      <c r="D27" s="163"/>
+      <c r="E27" s="164"/>
+      <c r="F27" s="164"/>
+      <c r="G27" s="164"/>
+      <c r="H27" s="165"/>
+      <c r="AK27" s="39">
         <f t="shared" si="1"/>
         <v>145</v>
       </c>
     </row>
     <row r="28" spans="1:37" ht="15.75" thickBot="1">
-      <c r="A28" s="46">
+      <c r="A28" s="42">
         <f t="shared" si="0"/>
         <v>27</v>
       </c>
-      <c r="B28" s="46" t="str">
+      <c r="B28" s="42" t="str">
         <f>IF(D$2="Your Name Here","Enter Name",ROUND(_xlfn.NORM.INV(Random!D38,20,15),1))</f>
         <v>Enter Name</v>
       </c>
-      <c r="AK28" s="43">
+      <c r="AK28" s="39">
         <f t="shared" si="1"/>
         <v>438</v>
       </c>
     </row>
     <row r="29" spans="1:37">
-      <c r="A29" s="46">
+      <c r="A29" s="42">
         <f t="shared" si="0"/>
         <v>28</v>
       </c>
-      <c r="B29" s="46" t="str">
+      <c r="B29" s="42" t="str">
         <f>IF(D$2="Your Name Here","Enter Name",ROUND(_xlfn.NORM.INV(Random!D39,20,15),1))</f>
         <v>Enter Name</v>
       </c>
-      <c r="D29" s="157" t="s">
+      <c r="D29" s="166" t="s">
         <v>44</v>
       </c>
-      <c r="E29" s="158"/>
-      <c r="F29" s="158"/>
-      <c r="G29" s="158"/>
-      <c r="H29" s="159"/>
-      <c r="AK29" s="43">
+      <c r="E29" s="167"/>
+      <c r="F29" s="167"/>
+      <c r="G29" s="167"/>
+      <c r="H29" s="168"/>
+      <c r="AK29" s="39">
         <f t="shared" si="1"/>
         <v>8195</v>
       </c>
     </row>
     <row r="30" spans="1:37">
-      <c r="A30" s="46">
+      <c r="A30" s="42">
         <f t="shared" si="0"/>
         <v>29</v>
       </c>
-      <c r="B30" s="46" t="str">
+      <c r="B30" s="42" t="str">
         <f>IF(D$2="Your Name Here","Enter Name",ROUND(_xlfn.NORM.INV(Random!D40,20,15),1))</f>
         <v>Enter Name</v>
       </c>
-      <c r="D30" s="160"/>
-      <c r="E30" s="161"/>
-      <c r="F30" s="161"/>
-      <c r="G30" s="161"/>
-      <c r="H30" s="162"/>
-      <c r="AK30" s="43">
+      <c r="D30" s="169"/>
+      <c r="E30" s="170"/>
+      <c r="F30" s="170"/>
+      <c r="G30" s="170"/>
+      <c r="H30" s="171"/>
+      <c r="P30" s="39" t="e">
+        <f ca="1">SUBSTITUTE(SUBSTITUTE(_xlfn.FORMULATEXT('Water Quality'!H11), " ",""),"$","") = "=G11#/count(B:B)"</f>
+        <v>#N/A</v>
+      </c>
+      <c r="AK30" s="39">
         <f t="shared" si="1"/>
         <v>6420</v>
       </c>
     </row>
     <row r="31" spans="1:37">
-      <c r="A31" s="46">
+      <c r="A31" s="42">
         <f t="shared" si="0"/>
         <v>30</v>
       </c>
-      <c r="B31" s="46" t="str">
+      <c r="B31" s="42" t="str">
         <f>IF(D$2="Your Name Here","Enter Name",ROUND(_xlfn.NORM.INV(Random!D41,20,15),1))</f>
         <v>Enter Name</v>
       </c>
-      <c r="D31" s="160"/>
-      <c r="E31" s="161"/>
-      <c r="F31" s="161"/>
-      <c r="G31" s="161"/>
-      <c r="H31" s="162"/>
-      <c r="Q31" s="43" t="b">
-        <f ca="1">IFERROR(OR(P32:P35),FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="AK31" s="43">
+      <c r="D31" s="169"/>
+      <c r="E31" s="170"/>
+      <c r="F31" s="170"/>
+      <c r="G31" s="170"/>
+      <c r="H31" s="171"/>
+      <c r="P31" s="39" t="e">
+        <f ca="1">SUBSTITUTE(SUBSTITUTE(_xlfn.FORMULATEXT('Water Quality'!H11), " ",""),"$","") = "=G11#/count(B2:B103)"</f>
+        <v>#N/A</v>
+      </c>
+      <c r="Q31" s="39" t="b">
+        <f ca="1">IFERROR(OR(P30:P35),FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="AK31" s="39">
         <f t="shared" si="1"/>
         <v>4161</v>
       </c>
     </row>
     <row r="32" spans="1:37">
-      <c r="A32" s="46">
+      <c r="A32" s="42">
         <f t="shared" si="0"/>
         <v>31</v>
       </c>
-      <c r="B32" s="46" t="str">
+      <c r="B32" s="42" t="str">
         <f>IF(D$2="Your Name Here","Enter Name",ROUND(_xlfn.NORM.INV(Random!D42,20,15),1))</f>
         <v>Enter Name</v>
       </c>
-      <c r="D32" s="160"/>
-      <c r="E32" s="161"/>
-      <c r="F32" s="161"/>
-      <c r="G32" s="161"/>
-      <c r="H32" s="162"/>
-      <c r="L32" s="43" t="b">
+      <c r="D32" s="169"/>
+      <c r="E32" s="170"/>
+      <c r="F32" s="170"/>
+      <c r="G32" s="170"/>
+      <c r="H32" s="171"/>
+      <c r="L32" s="39" t="b">
         <f ca="1">IFERROR(OR(K33:K35),FALSE)</f>
         <v>0</v>
       </c>
-      <c r="P32" s="43" t="e">
+      <c r="P32" s="39" t="e">
         <f ca="1">SUBSTITUTE(SUBSTITUTE(_xlfn.FORMULATEXT('Water Quality'!H11), " ",""),"$","") = "=G11#/SUM(G11#)"</f>
         <v>#N/A</v>
       </c>
-      <c r="Q32" s="43" t="b">
-        <f ca="1">IFERROR(OR(P32:P46),FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="AK32" s="43">
+      <c r="AK32" s="39">
         <f t="shared" si="1"/>
         <v>5022</v>
       </c>
     </row>
     <row r="33" spans="1:37">
-      <c r="A33" s="46">
+      <c r="A33" s="42">
         <f t="shared" si="0"/>
         <v>32</v>
       </c>
-      <c r="B33" s="46" t="str">
+      <c r="B33" s="42" t="str">
         <f>IF(D$2="Your Name Here","Enter Name",ROUND(_xlfn.NORM.INV(Random!D43,20,15),1))</f>
         <v>Enter Name</v>
       </c>
-      <c r="D33" s="160"/>
-      <c r="E33" s="161"/>
-      <c r="F33" s="161"/>
-      <c r="G33" s="161"/>
-      <c r="H33" s="162"/>
-      <c r="K33" s="43" t="e">
+      <c r="D33" s="169"/>
+      <c r="E33" s="170"/>
+      <c r="F33" s="170"/>
+      <c r="G33" s="170"/>
+      <c r="H33" s="171"/>
+      <c r="K33" s="39" t="e">
         <f ca="1">SUBSTITUTE(SUBSTITUTE(_xlfn.FORMULATEXT('Water Quality'!G11), " ",""),"$","") = "=FREQUENCY(B:B,E11:E20)"</f>
         <v>#N/A</v>
       </c>
-      <c r="L33" s="43" t="b">
-        <f ca="1">IFERROR(OR(K33:K35),FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="P33" s="43" t="e">
+      <c r="P33" s="39" t="e">
         <f ca="1">SUBSTITUTE(SUBSTITUTE(_xlfn.FORMULATEXT('Water Quality'!H11), " ",""),"$","") = "=G11:G28/SUM(G11:G28)"</f>
         <v>#N/A</v>
       </c>
-      <c r="AK33" s="43">
+      <c r="AK33" s="39">
         <f t="shared" si="1"/>
         <v>3963</v>
       </c>
     </row>
     <row r="34" spans="1:37">
-      <c r="A34" s="46">
+      <c r="A34" s="42">
         <f t="shared" si="0"/>
         <v>33</v>
       </c>
-      <c r="B34" s="46" t="str">
+      <c r="B34" s="42" t="str">
         <f>IF(D$2="Your Name Here","Enter Name",ROUND(_xlfn.NORM.INV(Random!D44,20,15),1))</f>
         <v>Enter Name</v>
       </c>
-      <c r="D34" s="160"/>
-      <c r="E34" s="161"/>
-      <c r="F34" s="161"/>
-      <c r="G34" s="161"/>
-      <c r="H34" s="162"/>
-      <c r="K34" s="43" t="e">
+      <c r="D34" s="169"/>
+      <c r="E34" s="170"/>
+      <c r="F34" s="170"/>
+      <c r="G34" s="170"/>
+      <c r="H34" s="171"/>
+      <c r="K34" s="39" t="e">
         <f ca="1">SUBSTITUTE(SUBSTITUTE(_xlfn.FORMULATEXT('Water Quality'!G11), " ",""),"$","") = "=FREQUENCY(B2:B103,E11:E20)"</f>
         <v>#N/A</v>
       </c>
-      <c r="P34" s="43" t="e">
+      <c r="P34" s="39" t="e">
         <f ca="1">SUBSTITUTE(SUBSTITUTE(_xlfn.FORMULATEXT('Water Quality'!H11), " ",""),"$","") = "=G11#/102"</f>
         <v>#N/A</v>
       </c>
-      <c r="AK34" s="43">
+      <c r="AK34" s="39">
         <f t="shared" si="1"/>
         <v>3380</v>
       </c>
     </row>
     <row r="35" spans="1:37">
-      <c r="A35" s="46">
+      <c r="A35" s="42">
         <f t="shared" si="0"/>
         <v>34</v>
       </c>
-      <c r="B35" s="46" t="str">
+      <c r="B35" s="42" t="str">
         <f>IF(D$2="Your Name Here","Enter Name",ROUND(_xlfn.NORM.INV(Random!D45,20,15),1))</f>
         <v>Enter Name</v>
       </c>
-      <c r="D35" s="160"/>
-      <c r="E35" s="161"/>
-      <c r="F35" s="161"/>
-      <c r="G35" s="161"/>
-      <c r="H35" s="162"/>
-      <c r="K35" s="43" t="e">
+      <c r="D35" s="169"/>
+      <c r="E35" s="170"/>
+      <c r="F35" s="170"/>
+      <c r="G35" s="170"/>
+      <c r="H35" s="171"/>
+      <c r="K35" s="39" t="e">
         <f ca="1">SUBSTITUTE(SUBSTITUTE(_xlfn.FORMULATEXT('Water Quality'!G11), " ",""),"$","") = "=FREQUENCY(Difference_in_water_quality,E11:E20)"</f>
         <v>#N/A</v>
       </c>
-      <c r="P35" s="43" t="e">
+      <c r="P35" s="39" t="e">
         <f ca="1">SUBSTITUTE(SUBSTITUTE(_xlfn.FORMULATEXT('Water Quality'!H11), " ",""),"$","") = "=G11:G21/102"</f>
         <v>#N/A</v>
       </c>
-      <c r="AK35" s="43">
+      <c r="AK35" s="39">
         <f t="shared" si="1"/>
         <v>1093</v>
       </c>
     </row>
     <row r="36" spans="1:37">
-      <c r="A36" s="46">
+      <c r="A36" s="42">
         <f t="shared" si="0"/>
         <v>35</v>
       </c>
-      <c r="B36" s="46" t="str">
+      <c r="B36" s="42" t="str">
         <f>IF(D$2="Your Name Here","Enter Name",ROUND(_xlfn.NORM.INV(Random!D46,20,15),1))</f>
         <v>Enter Name</v>
       </c>
-      <c r="D36" s="160"/>
-      <c r="E36" s="161"/>
-      <c r="F36" s="161"/>
-      <c r="G36" s="161"/>
-      <c r="H36" s="162"/>
-      <c r="K36" s="43" t="b">
+      <c r="D36" s="169"/>
+      <c r="E36" s="170"/>
+      <c r="F36" s="170"/>
+      <c r="G36" s="170"/>
+      <c r="H36" s="171"/>
+      <c r="K36" s="39" t="b">
         <f>'Water Quality'!G11=Solution!G11</f>
         <v>1</v>
       </c>
-      <c r="L36" s="43" t="b">
-        <f t="shared" ref="L36:L46" ca="1" si="4">OR(L$33,K36)</f>
-        <v>1</v>
-      </c>
-      <c r="M36" s="43" t="b">
-        <f ca="1">AND(L$32,K36)</f>
-        <v>0</v>
-      </c>
-      <c r="P36" s="43" t="e">
+      <c r="P36" s="39" t="e">
         <f>'Water Quality'!H11=Solution!H11</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="Q36" s="43" t="e">
-        <f t="shared" ref="Q36:Q46" si="5">OR(P36,Q$32)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="R36" s="43" t="e">
-        <f ca="1">AND(Q$31,P36)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AK36" s="43">
+      <c r="AK36" s="39">
         <f t="shared" si="1"/>
         <v>6910</v>
       </c>
     </row>
     <row r="37" spans="1:37">
-      <c r="A37" s="46">
+      <c r="A37" s="42">
         <f t="shared" si="0"/>
         <v>36</v>
       </c>
-      <c r="B37" s="46" t="str">
+      <c r="B37" s="42" t="str">
         <f>IF(D$2="Your Name Here","Enter Name",ROUND(_xlfn.NORM.INV(Random!D47,20,15),1))</f>
         <v>Enter Name</v>
       </c>
-      <c r="D37" s="160"/>
-      <c r="E37" s="161"/>
-      <c r="F37" s="161"/>
-      <c r="G37" s="161"/>
-      <c r="H37" s="162"/>
-      <c r="K37" s="43" t="b">
+      <c r="D37" s="169"/>
+      <c r="E37" s="170"/>
+      <c r="F37" s="170"/>
+      <c r="G37" s="170"/>
+      <c r="H37" s="171"/>
+      <c r="K37" s="39" t="b">
         <f>'Water Quality'!G12=Solution!G12</f>
         <v>1</v>
       </c>
-      <c r="L37" s="43" t="b">
-        <f t="shared" ca="1" si="4"/>
-        <v>1</v>
-      </c>
-      <c r="M37" s="43" t="b">
-        <f t="shared" ref="M37:M46" ca="1" si="6">AND(L$32,K37)</f>
-        <v>0</v>
-      </c>
-      <c r="P37" s="43" t="e">
+      <c r="P37" s="39" t="e">
         <f>'Water Quality'!H12=Solution!H12</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="Q37" s="43" t="e">
-        <f t="shared" si="5"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="R37" s="43" t="e">
-        <f t="shared" ref="R37:R46" ca="1" si="7">AND(Q$31,P37)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AK37" s="43">
+      <c r="AK37" s="39">
         <f t="shared" si="1"/>
         <v>9151</v>
       </c>
     </row>
     <row r="38" spans="1:37">
-      <c r="A38" s="46">
+      <c r="A38" s="42">
         <f t="shared" si="0"/>
         <v>37</v>
       </c>
-      <c r="B38" s="46" t="str">
+      <c r="B38" s="42" t="str">
         <f>IF(D$2="Your Name Here","Enter Name",ROUND(_xlfn.NORM.INV(Random!D48,20,15),1))</f>
         <v>Enter Name</v>
       </c>
-      <c r="D38" s="160"/>
-      <c r="E38" s="161"/>
-      <c r="F38" s="161"/>
-      <c r="G38" s="161"/>
-      <c r="H38" s="162"/>
-      <c r="K38" s="43" t="b">
+      <c r="D38" s="169"/>
+      <c r="E38" s="170"/>
+      <c r="F38" s="170"/>
+      <c r="G38" s="170"/>
+      <c r="H38" s="171"/>
+      <c r="K38" s="39" t="b">
         <f>'Water Quality'!G13=Solution!G13</f>
         <v>1</v>
       </c>
-      <c r="L38" s="43" t="b">
-        <f t="shared" ca="1" si="4"/>
-        <v>1</v>
-      </c>
-      <c r="M38" s="43" t="b">
-        <f t="shared" ca="1" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="P38" s="43" t="e">
+      <c r="P38" s="39" t="e">
         <f>'Water Quality'!H13=Solution!H13</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="Q38" s="43" t="e">
-        <f t="shared" si="5"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="R38" s="43" t="e">
-        <f t="shared" ca="1" si="7"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AK38" s="43">
+      <c r="AK38" s="39">
         <f t="shared" si="1"/>
         <v>2304</v>
       </c>
     </row>
     <row r="39" spans="1:37">
-      <c r="A39" s="46">
+      <c r="A39" s="42">
         <f t="shared" si="0"/>
         <v>38</v>
       </c>
-      <c r="B39" s="46" t="str">
+      <c r="B39" s="42" t="str">
         <f>IF(D$2="Your Name Here","Enter Name",ROUND(_xlfn.NORM.INV(Random!D49,20,15),1))</f>
         <v>Enter Name</v>
       </c>
-      <c r="D39" s="160"/>
-      <c r="E39" s="161"/>
-      <c r="F39" s="161"/>
-      <c r="G39" s="161"/>
-      <c r="H39" s="162"/>
-      <c r="K39" s="43" t="b">
+      <c r="D39" s="169"/>
+      <c r="E39" s="170"/>
+      <c r="F39" s="170"/>
+      <c r="G39" s="170"/>
+      <c r="H39" s="171"/>
+      <c r="K39" s="39" t="b">
         <f>'Water Quality'!G14=Solution!G14</f>
         <v>1</v>
       </c>
-      <c r="L39" s="43" t="b">
-        <f t="shared" ca="1" si="4"/>
-        <v>1</v>
-      </c>
-      <c r="M39" s="43" t="b">
-        <f t="shared" ca="1" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="P39" s="43" t="e">
+      <c r="P39" s="39" t="e">
         <f>'Water Quality'!H14=Solution!H14</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="Q39" s="43" t="e">
-        <f t="shared" si="5"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="R39" s="43" t="e">
-        <f t="shared" ca="1" si="7"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AK39" s="43">
+      <c r="AK39" s="39">
         <f t="shared" si="1"/>
         <v>8105</v>
       </c>
     </row>
     <row r="40" spans="1:37" ht="15.75" thickBot="1">
-      <c r="A40" s="46">
+      <c r="A40" s="42">
         <f t="shared" si="0"/>
         <v>39</v>
       </c>
-      <c r="B40" s="46" t="str">
+      <c r="B40" s="42" t="str">
         <f>IF(D$2="Your Name Here","Enter Name",ROUND(_xlfn.NORM.INV(Random!D50,20,15),1))</f>
         <v>Enter Name</v>
       </c>
-      <c r="D40" s="163"/>
-      <c r="E40" s="164"/>
-      <c r="F40" s="164"/>
-      <c r="G40" s="164"/>
-      <c r="H40" s="165"/>
-      <c r="K40" s="43" t="b">
+      <c r="D40" s="172"/>
+      <c r="E40" s="173"/>
+      <c r="F40" s="173"/>
+      <c r="G40" s="173"/>
+      <c r="H40" s="174"/>
+      <c r="K40" s="39" t="b">
         <f>'Water Quality'!G15=Solution!G15</f>
         <v>1</v>
       </c>
-      <c r="L40" s="43" t="b">
-        <f t="shared" ca="1" si="4"/>
-        <v>1</v>
-      </c>
-      <c r="M40" s="43" t="b">
-        <f t="shared" ca="1" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="P40" s="43" t="e">
+      <c r="P40" s="39" t="e">
         <f>'Water Quality'!H15=Solution!H15</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="Q40" s="43" t="e">
-        <f t="shared" si="5"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="R40" s="43" t="e">
-        <f t="shared" ca="1" si="7"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AK40" s="43">
+      <c r="AK40" s="39">
         <f t="shared" si="1"/>
         <v>4006</v>
       </c>
     </row>
     <row r="41" spans="1:37">
-      <c r="A41" s="46">
+      <c r="A41" s="42">
         <f t="shared" si="0"/>
         <v>40</v>
       </c>
-      <c r="B41" s="46" t="str">
+      <c r="B41" s="42" t="str">
         <f>IF(D$2="Your Name Here","Enter Name",ROUND(_xlfn.NORM.INV(Random!D51,20,15),1))</f>
         <v>Enter Name</v>
       </c>
-      <c r="K41" s="43" t="b">
+      <c r="K41" s="39" t="b">
         <f>'Water Quality'!G16=Solution!G16</f>
         <v>1</v>
       </c>
-      <c r="L41" s="43" t="b">
-        <f t="shared" ca="1" si="4"/>
-        <v>1</v>
-      </c>
-      <c r="M41" s="43" t="b">
-        <f t="shared" ca="1" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="P41" s="43" t="e">
+      <c r="P41" s="39" t="e">
         <f>'Water Quality'!H16=Solution!H16</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="Q41" s="43" t="e">
-        <f t="shared" si="5"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="R41" s="43" t="e">
-        <f t="shared" ca="1" si="7"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AK41" s="43">
+      <c r="AK41" s="39">
         <f t="shared" si="1"/>
         <v>355</v>
       </c>
     </row>
     <row r="42" spans="1:37">
-      <c r="A42" s="46">
+      <c r="A42" s="42">
         <f t="shared" si="0"/>
         <v>41</v>
       </c>
-      <c r="B42" s="46" t="str">
+      <c r="B42" s="42" t="str">
         <f>IF(D$2="Your Name Here","Enter Name",ROUND(_xlfn.NORM.INV(Random!D52,20,15),1))</f>
         <v>Enter Name</v>
       </c>
-      <c r="K42" s="43" t="b">
+      <c r="K42" s="39" t="b">
         <f>'Water Quality'!G17=Solution!G17</f>
         <v>1</v>
       </c>
-      <c r="L42" s="43" t="b">
-        <f t="shared" ca="1" si="4"/>
-        <v>1</v>
-      </c>
-      <c r="M42" s="43" t="b">
-        <f t="shared" ca="1" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="P42" s="43" t="e">
+      <c r="P42" s="39" t="e">
         <f>'Water Quality'!H17=Solution!H17</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="Q42" s="43" t="e">
-        <f t="shared" si="5"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="R42" s="43" t="e">
-        <f t="shared" ca="1" si="7"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AK42" s="43">
+      <c r="AK42" s="39">
         <f t="shared" si="1"/>
         <v>9128</v>
       </c>
     </row>
     <row r="43" spans="1:37">
-      <c r="A43" s="46">
+      <c r="A43" s="42">
         <f t="shared" si="0"/>
         <v>42</v>
       </c>
-      <c r="B43" s="46" t="str">
+      <c r="B43" s="42" t="str">
         <f>IF(D$2="Your Name Here","Enter Name",ROUND(_xlfn.NORM.INV(Random!D53,20,15),1))</f>
         <v>Enter Name</v>
       </c>
-      <c r="K43" s="43" t="b">
+      <c r="K43" s="39" t="b">
         <f>'Water Quality'!G18=Solution!G18</f>
         <v>1</v>
       </c>
-      <c r="L43" s="43" t="b">
-        <f t="shared" ca="1" si="4"/>
-        <v>1</v>
-      </c>
-      <c r="M43" s="43" t="b">
-        <f t="shared" ca="1" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="P43" s="43" t="e">
+      <c r="P43" s="39" t="e">
         <f>'Water Quality'!H18=Solution!H18</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="Q43" s="43" t="e">
-        <f t="shared" si="5"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="R43" s="43" t="e">
-        <f t="shared" ca="1" si="7"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AK43" s="43">
+      <c r="AK43" s="39">
         <f t="shared" si="1"/>
         <v>1789</v>
       </c>
     </row>
     <row r="44" spans="1:37">
-      <c r="A44" s="46">
+      <c r="A44" s="42">
         <f t="shared" si="0"/>
         <v>43</v>
       </c>
-      <c r="B44" s="46" t="str">
+      <c r="B44" s="42" t="str">
         <f>IF(D$2="Your Name Here","Enter Name",ROUND(_xlfn.NORM.INV(Random!D54,20,15),1))</f>
         <v>Enter Name</v>
       </c>
-      <c r="K44" s="43" t="b">
+      <c r="K44" s="39" t="b">
         <f>'Water Quality'!G19=Solution!G19</f>
         <v>1</v>
       </c>
-      <c r="L44" s="43" t="b">
-        <f t="shared" ca="1" si="4"/>
-        <v>1</v>
-      </c>
-      <c r="M44" s="43" t="b">
-        <f t="shared" ca="1" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="P44" s="43" t="e">
+      <c r="P44" s="39" t="e">
         <f>'Water Quality'!H19=Solution!H19</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="Q44" s="43" t="e">
-        <f t="shared" si="5"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="R44" s="43" t="e">
-        <f t="shared" ca="1" si="7"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AK44" s="43">
+      <c r="AK44" s="39">
         <f t="shared" si="1"/>
         <v>2954</v>
       </c>
     </row>
     <row r="45" spans="1:37">
-      <c r="A45" s="46">
+      <c r="A45" s="42">
         <f t="shared" si="0"/>
         <v>44</v>
       </c>
-      <c r="B45" s="46" t="str">
+      <c r="B45" s="42" t="str">
         <f>IF(D$2="Your Name Here","Enter Name",ROUND(_xlfn.NORM.INV(Random!D55,20,15),1))</f>
         <v>Enter Name</v>
       </c>
-      <c r="K45" s="43" t="b">
+      <c r="K45" s="39" t="b">
         <f>'Water Quality'!G20=Solution!G20</f>
         <v>1</v>
       </c>
-      <c r="L45" s="43" t="b">
-        <f t="shared" ca="1" si="4"/>
-        <v>1</v>
-      </c>
-      <c r="M45" s="43" t="b">
-        <f t="shared" ca="1" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="P45" s="43" t="e">
+      <c r="P45" s="39" t="e">
         <f>'Water Quality'!H20=Solution!H20</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="Q45" s="43" t="e">
-        <f t="shared" si="5"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="R45" s="43" t="e">
-        <f t="shared" ca="1" si="7"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AK45" s="43">
+      <c r="AK45" s="39">
         <f t="shared" si="1"/>
         <v>3119</v>
       </c>
     </row>
     <row r="46" spans="1:37">
-      <c r="A46" s="46">
+      <c r="A46" s="42">
         <f t="shared" si="0"/>
         <v>45</v>
       </c>
-      <c r="B46" s="46" t="str">
+      <c r="B46" s="42" t="str">
         <f>IF(D$2="Your Name Here","Enter Name",ROUND(_xlfn.NORM.INV(Random!D56,20,15),1))</f>
         <v>Enter Name</v>
       </c>
-      <c r="K46" s="43" t="b">
+      <c r="K46" s="39" t="b">
         <f>'Water Quality'!G21=Solution!G21</f>
         <v>1</v>
       </c>
-      <c r="L46" s="43" t="b">
-        <f t="shared" ca="1" si="4"/>
-        <v>1</v>
-      </c>
-      <c r="M46" s="43" t="b">
-        <f t="shared" ca="1" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="P46" s="43" t="e">
+      <c r="P46" s="39" t="e">
         <f>'Water Quality'!H21=Solution!H21</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="Q46" s="43" t="e">
-        <f t="shared" si="5"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="R46" s="43" t="e">
-        <f t="shared" ca="1" si="7"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AK46" s="43">
+      <c r="AK46" s="39">
         <f t="shared" si="1"/>
         <v>6016</v>
       </c>
     </row>
     <row r="47" spans="1:37">
-      <c r="A47" s="46">
+      <c r="A47" s="42">
         <f t="shared" si="0"/>
         <v>46</v>
       </c>
-      <c r="B47" s="46" t="str">
+      <c r="B47" s="42" t="str">
         <f>IF(D$2="Your Name Here","Enter Name",ROUND(_xlfn.NORM.INV(Random!D57,20,15),1))</f>
         <v>Enter Name</v>
       </c>
-      <c r="AK47" s="43">
+      <c r="AK47" s="39">
         <f t="shared" si="1"/>
         <v>2293</v>
       </c>
     </row>
     <row r="48" spans="1:37">
-      <c r="A48" s="46">
+      <c r="A48" s="42">
         <f t="shared" si="0"/>
         <v>47</v>
       </c>
-      <c r="B48" s="46" t="str">
+      <c r="B48" s="42" t="str">
         <f>IF(D$2="Your Name Here","Enter Name",ROUND(_xlfn.NORM.INV(Random!D58,20,15),1))</f>
         <v>Enter Name</v>
       </c>
-      <c r="AK48" s="43">
+      <c r="AK48" s="39">
         <f t="shared" si="1"/>
         <v>5466</v>
       </c>
     </row>
     <row r="49" spans="1:37">
-      <c r="A49" s="46">
+      <c r="A49" s="42">
         <f t="shared" si="0"/>
         <v>48</v>
       </c>
-      <c r="B49" s="46" t="str">
+      <c r="B49" s="42" t="str">
         <f>IF(D$2="Your Name Here","Enter Name",ROUND(_xlfn.NORM.INV(Random!D59,20,15),1))</f>
         <v>Enter Name</v>
       </c>
-      <c r="AK49" s="43">
+      <c r="AK49" s="39">
         <f t="shared" si="1"/>
         <v>7923</v>
       </c>
     </row>
     <row r="50" spans="1:37">
-      <c r="A50" s="46">
+      <c r="A50" s="42">
         <f t="shared" si="0"/>
         <v>49</v>
       </c>
-      <c r="B50" s="46" t="str">
+      <c r="B50" s="42" t="str">
         <f>IF(D$2="Your Name Here","Enter Name",ROUND(_xlfn.NORM.INV(Random!D60,20,15),1))</f>
         <v>Enter Name</v>
       </c>
-      <c r="AK50" s="43">
+      <c r="AK50" s="39">
         <f t="shared" si="1"/>
         <v>8704</v>
       </c>
     </row>
     <row r="51" spans="1:37">
-      <c r="A51" s="46">
+      <c r="A51" s="42">
         <f t="shared" si="0"/>
         <v>50</v>
       </c>
-      <c r="B51" s="46" t="str">
+      <c r="B51" s="42" t="str">
         <f>IF(D$2="Your Name Here","Enter Name",ROUND(_xlfn.NORM.INV(Random!D61,20,15),1))</f>
         <v>Enter Name</v>
       </c>
-      <c r="AK51" s="43">
+      <c r="AK51" s="39">
         <f t="shared" si="1"/>
         <v>3461</v>
       </c>
     </row>
     <row r="52" spans="1:37">
-      <c r="A52" s="46">
+      <c r="A52" s="42">
         <f t="shared" si="0"/>
         <v>51</v>
       </c>
-      <c r="B52" s="46" t="str">
+      <c r="B52" s="42" t="str">
         <f>IF(D$2="Your Name Here","Enter Name",ROUND(_xlfn.NORM.INV(Random!D62,20,15),1))</f>
         <v>Enter Name</v>
       </c>
-      <c r="AK52" s="43">
+      <c r="AK52" s="39">
         <f t="shared" si="1"/>
         <v>514</v>
       </c>
     </row>
     <row r="53" spans="1:37">
-      <c r="A53" s="46">
+      <c r="A53" s="42">
         <f t="shared" si="0"/>
         <v>52</v>
       </c>
-      <c r="B53" s="46" t="str">
+      <c r="B53" s="42" t="str">
         <f>IF(D$2="Your Name Here","Enter Name",ROUND(_xlfn.NORM.INV(Random!D63,20,15),1))</f>
         <v>Enter Name</v>
       </c>
-      <c r="AK53" s="43">
+      <c r="AK53" s="39">
         <f t="shared" si="1"/>
         <v>3915</v>
       </c>
     </row>
     <row r="54" spans="1:37">
-      <c r="A54" s="46">
+      <c r="A54" s="42">
         <f t="shared" si="0"/>
         <v>53</v>
       </c>
-      <c r="B54" s="46" t="str">
+      <c r="B54" s="42" t="str">
         <f>IF(D$2="Your Name Here","Enter Name",ROUND(_xlfn.NORM.INV(Random!D64,20,15),1))</f>
         <v>Enter Name</v>
       </c>
-      <c r="AK54" s="43">
+      <c r="AK54" s="39">
         <f t="shared" si="1"/>
         <v>2704</v>
       </c>
     </row>
     <row r="55" spans="1:37">
-      <c r="A55" s="46">
+      <c r="A55" s="42">
         <f t="shared" si="0"/>
         <v>54</v>
       </c>
-      <c r="B55" s="46" t="str">
+      <c r="B55" s="42" t="str">
         <f>IF(D$2="Your Name Here","Enter Name",ROUND(_xlfn.NORM.INV(Random!D65,20,15),1))</f>
         <v>Enter Name</v>
       </c>
-      <c r="AK55" s="43">
+      <c r="AK55" s="39">
         <f t="shared" si="1"/>
         <v>1509</v>
       </c>
     </row>
     <row r="56" spans="1:37">
-      <c r="A56" s="46">
+      <c r="A56" s="42">
         <f t="shared" si="0"/>
         <v>55</v>
       </c>
-      <c r="B56" s="46" t="str">
+      <c r="B56" s="42" t="str">
         <f>IF(D$2="Your Name Here","Enter Name",ROUND(_xlfn.NORM.INV(Random!D66,20,15),1))</f>
         <v>Enter Name</v>
       </c>
-      <c r="AK56" s="43">
+      <c r="AK56" s="39">
         <f t="shared" si="1"/>
         <v>6654</v>
       </c>
     </row>
     <row r="57" spans="1:37">
-      <c r="A57" s="46">
+      <c r="A57" s="42">
         <f t="shared" si="0"/>
         <v>56</v>
       </c>
-      <c r="B57" s="46" t="str">
+      <c r="B57" s="42" t="str">
         <f>IF(D$2="Your Name Here","Enter Name",ROUND(_xlfn.NORM.INV(Random!D67,20,15),1))</f>
         <v>Enter Name</v>
       </c>
-      <c r="AK57" s="43">
+      <c r="AK57" s="39">
         <f t="shared" si="1"/>
         <v>8603</v>
       </c>
     </row>
     <row r="58" spans="1:37">
-      <c r="A58" s="46">
+      <c r="A58" s="42">
         <f t="shared" si="0"/>
         <v>57</v>
       </c>
-      <c r="B58" s="46" t="str">
+      <c r="B58" s="42" t="str">
         <f>IF(D$2="Your Name Here","Enter Name",ROUND(_xlfn.NORM.INV(Random!D68,20,15),1))</f>
         <v>Enter Name</v>
       </c>
-      <c r="AK58" s="43">
+      <c r="AK58" s="39">
         <f t="shared" si="1"/>
         <v>7580</v>
       </c>
     </row>
     <row r="59" spans="1:37">
-      <c r="A59" s="46">
+      <c r="A59" s="42">
         <f t="shared" si="0"/>
         <v>58</v>
       </c>
-      <c r="B59" s="46" t="str">
+      <c r="B59" s="42" t="str">
         <f>IF(D$2="Your Name Here","Enter Name",ROUND(_xlfn.NORM.INV(Random!D69,20,15),1))</f>
         <v>Enter Name</v>
       </c>
-      <c r="AK59" s="43">
+      <c r="AK59" s="39">
         <f t="shared" si="1"/>
         <v>625</v>
       </c>
     </row>
     <row r="60" spans="1:37">
-      <c r="A60" s="46">
+      <c r="A60" s="42">
         <f t="shared" si="0"/>
         <v>59</v>
       </c>
-      <c r="B60" s="46" t="str">
+      <c r="B60" s="42" t="str">
         <f>IF(D$2="Your Name Here","Enter Name",ROUND(_xlfn.NORM.INV(Random!D70,20,15),1))</f>
         <v>Enter Name</v>
       </c>
-      <c r="AK60" s="43">
+      <c r="AK60" s="39">
         <f t="shared" si="1"/>
         <v>7198</v>
       </c>
     </row>
     <row r="61" spans="1:37">
-      <c r="A61" s="46">
+      <c r="A61" s="42">
         <f t="shared" si="0"/>
         <v>60</v>
       </c>
-      <c r="B61" s="46" t="str">
+      <c r="B61" s="42" t="str">
         <f>IF(D$2="Your Name Here","Enter Name",ROUND(_xlfn.NORM.INV(Random!D71,20,15),1))</f>
         <v>Enter Name</v>
       </c>
-      <c r="AK61" s="43">
+      <c r="AK61" s="39">
         <f t="shared" si="1"/>
         <v>4035</v>
       </c>
     </row>
     <row r="62" spans="1:37">
-      <c r="A62" s="46">
+      <c r="A62" s="42">
         <f t="shared" si="0"/>
         <v>61</v>
       </c>
-      <c r="B62" s="46" t="str">
+      <c r="B62" s="42" t="str">
         <f>IF(D$2="Your Name Here","Enter Name",ROUND(_xlfn.NORM.INV(Random!D72,20,15),1))</f>
         <v>Enter Name</v>
       </c>
-      <c r="AK62" s="43">
+      <c r="AK62" s="39">
         <f t="shared" si="1"/>
         <v>8980</v>
       </c>
     </row>
     <row r="63" spans="1:37">
-      <c r="A63" s="46">
+      <c r="A63" s="42">
         <f t="shared" si="0"/>
         <v>62</v>
       </c>
-      <c r="B63" s="46" t="str">
+      <c r="B63" s="42" t="str">
         <f>IF(D$2="Your Name Here","Enter Name",ROUND(_xlfn.NORM.INV(Random!D73,20,15),1))</f>
         <v>Enter Name</v>
       </c>
-      <c r="AK63" s="43">
+      <c r="AK63" s="39">
         <f t="shared" si="1"/>
         <v>469</v>
       </c>
     </row>
     <row r="64" spans="1:37">
-      <c r="A64" s="46">
+      <c r="A64" s="42">
         <f t="shared" si="0"/>
         <v>63</v>
       </c>
-      <c r="B64" s="46" t="str">
+      <c r="B64" s="42" t="str">
         <f>IF(D$2="Your Name Here","Enter Name",ROUND(_xlfn.NORM.INV(Random!D74,20,15),1))</f>
         <v>Enter Name</v>
       </c>
-      <c r="AK64" s="43">
+      <c r="AK64" s="39">
         <f t="shared" si="1"/>
         <v>7294</v>
       </c>
     </row>
     <row r="65" spans="1:37">
-      <c r="A65" s="46">
+      <c r="A65" s="42">
         <f t="shared" si="0"/>
         <v>64</v>
       </c>
-      <c r="B65" s="46" t="str">
+      <c r="B65" s="42" t="str">
         <f>IF(D$2="Your Name Here","Enter Name",ROUND(_xlfn.NORM.INV(Random!D75,20,15),1))</f>
         <v>Enter Name</v>
       </c>
-      <c r="AK65" s="43">
+      <c r="AK65" s="39">
         <f t="shared" si="1"/>
         <v>5387</v>
       </c>
     </row>
     <row r="66" spans="1:37">
-      <c r="A66" s="46">
+      <c r="A66" s="42">
         <f t="shared" si="0"/>
         <v>65</v>
       </c>
-      <c r="B66" s="46" t="str">
+      <c r="B66" s="42" t="str">
         <f>IF(D$2="Your Name Here","Enter Name",ROUND(_xlfn.NORM.INV(Random!D76,20,15),1))</f>
         <v>Enter Name</v>
       </c>
-      <c r="AK66" s="43">
+      <c r="AK66" s="39">
         <f t="shared" si="1"/>
         <v>8148</v>
       </c>
     </row>
     <row r="67" spans="1:37">
-      <c r="A67" s="46">
+      <c r="A67" s="42">
         <f t="shared" si="0"/>
         <v>66</v>
       </c>
-      <c r="B67" s="46" t="str">
+      <c r="B67" s="42" t="str">
         <f>IF(D$2="Your Name Here","Enter Name",ROUND(_xlfn.NORM.INV(Random!D77,20,15),1))</f>
         <v>Enter Name</v>
       </c>
-      <c r="AK67" s="43">
+      <c r="AK67" s="39">
         <f t="shared" si="1"/>
         <v>981</v>
       </c>
     </row>
     <row r="68" spans="1:37">
-      <c r="A68" s="46">
-        <f t="shared" ref="A68:A103" si="8">A67+1</f>
+      <c r="A68" s="42">
+        <f t="shared" ref="A68:A103" si="4">A67+1</f>
         <v>67</v>
       </c>
-      <c r="B68" s="46" t="str">
+      <c r="B68" s="42" t="str">
         <f>IF(D$2="Your Name Here","Enter Name",ROUND(_xlfn.NORM.INV(Random!D78,20,15),1))</f>
         <v>Enter Name</v>
       </c>
-      <c r="AK68" s="43">
-        <f t="shared" ref="AK68:AK103" si="9">MOD(AK67*1103515245 + 12345,9172)</f>
+      <c r="AK68" s="39">
+        <f t="shared" ref="AK68:AK103" si="5">MOD(AK67*1103515245 + 12345,9172)</f>
         <v>8390</v>
       </c>
     </row>
     <row r="69" spans="1:37">
-      <c r="A69" s="46">
-        <f t="shared" si="8"/>
+      <c r="A69" s="42">
+        <f t="shared" si="4"/>
         <v>68</v>
       </c>
-      <c r="B69" s="46" t="str">
+      <c r="B69" s="42" t="str">
         <f>IF(D$2="Your Name Here","Enter Name",ROUND(_xlfn.NORM.INV(Random!D79,20,15),1))</f>
         <v>Enter Name</v>
       </c>
-      <c r="AK69" s="43">
-        <f t="shared" si="9"/>
+      <c r="AK69" s="39">
+        <f t="shared" si="5"/>
         <v>4007</v>
       </c>
     </row>
     <row r="70" spans="1:37">
-      <c r="A70" s="46">
-        <f t="shared" si="8"/>
+      <c r="A70" s="42">
+        <f t="shared" si="4"/>
         <v>69</v>
       </c>
-      <c r="B70" s="46" t="str">
+      <c r="B70" s="42" t="str">
         <f>IF(D$2="Your Name Here","Enter Name",ROUND(_xlfn.NORM.INV(Random!D80,20,15),1))</f>
         <v>Enter Name</v>
       </c>
-      <c r="AK70" s="43">
-        <f t="shared" si="9"/>
+      <c r="AK70" s="39">
+        <f t="shared" si="5"/>
         <v>4764</v>
       </c>
     </row>
     <row r="71" spans="1:37">
-      <c r="A71" s="46">
-        <f t="shared" si="8"/>
+      <c r="A71" s="42">
+        <f t="shared" si="4"/>
         <v>70</v>
       </c>
-      <c r="B71" s="46" t="str">
+      <c r="B71" s="42" t="str">
         <f>IF(D$2="Your Name Here","Enter Name",ROUND(_xlfn.NORM.INV(Random!D81,20,15),1))</f>
         <v>Enter Name</v>
       </c>
-      <c r="AK71" s="43">
-        <f t="shared" si="9"/>
+      <c r="AK71" s="39">
+        <f t="shared" si="5"/>
         <v>3769</v>
       </c>
     </row>
     <row r="72" spans="1:37">
-      <c r="A72" s="46">
-        <f t="shared" si="8"/>
+      <c r="A72" s="42">
+        <f t="shared" si="4"/>
         <v>71</v>
       </c>
-      <c r="B72" s="46" t="str">
+      <c r="B72" s="42" t="str">
         <f>IF(D$2="Your Name Here","Enter Name",ROUND(_xlfn.NORM.INV(Random!D82,20,15),1))</f>
         <v>Enter Name</v>
       </c>
-      <c r="AK72" s="43">
-        <f t="shared" si="9"/>
+      <c r="AK72" s="39">
+        <f t="shared" si="5"/>
         <v>1030</v>
       </c>
     </row>
     <row r="73" spans="1:37">
-      <c r="A73" s="46">
-        <f t="shared" si="8"/>
+      <c r="A73" s="42">
+        <f t="shared" si="4"/>
         <v>72</v>
       </c>
-      <c r="B73" s="46" t="str">
+      <c r="B73" s="42" t="str">
         <f>IF(D$2="Your Name Here","Enter Name",ROUND(_xlfn.NORM.INV(Random!D83,20,15),1))</f>
         <v>Enter Name</v>
       </c>
-      <c r="AK73" s="43">
-        <f t="shared" si="9"/>
+      <c r="AK73" s="39">
+        <f t="shared" si="5"/>
         <v>4303</v>
       </c>
     </row>
     <row r="74" spans="1:37">
-      <c r="A74" s="46">
-        <f t="shared" si="8"/>
+      <c r="A74" s="42">
+        <f t="shared" si="4"/>
         <v>73</v>
       </c>
-      <c r="B74" s="46" t="str">
+      <c r="B74" s="42" t="str">
         <f>IF(D$2="Your Name Here","Enter Name",ROUND(_xlfn.NORM.INV(Random!D84,20,15),1))</f>
         <v>Enter Name</v>
       </c>
-      <c r="AK74" s="43">
-        <f t="shared" si="9"/>
+      <c r="AK74" s="39">
+        <f t="shared" si="5"/>
         <v>7404</v>
       </c>
     </row>
     <row r="75" spans="1:37">
-      <c r="A75" s="46">
-        <f t="shared" si="8"/>
+      <c r="A75" s="42">
+        <f t="shared" si="4"/>
         <v>74</v>
       </c>
-      <c r="B75" s="46" t="str">
+      <c r="B75" s="42" t="str">
         <f>IF(D$2="Your Name Here","Enter Name",ROUND(_xlfn.NORM.INV(Random!D85,20,15),1))</f>
         <v>Enter Name</v>
       </c>
-      <c r="AK75" s="43">
-        <f t="shared" si="9"/>
+      <c r="AK75" s="39">
+        <f t="shared" si="5"/>
         <v>4261</v>
       </c>
     </row>
     <row r="76" spans="1:37">
-      <c r="A76" s="46">
-        <f t="shared" si="8"/>
+      <c r="A76" s="42">
+        <f t="shared" si="4"/>
         <v>75</v>
       </c>
-      <c r="B76" s="46" t="str">
+      <c r="B76" s="42" t="str">
         <f>IF(D$2="Your Name Here","Enter Name",ROUND(_xlfn.NORM.INV(Random!D86,20,15),1))</f>
         <v>Enter Name</v>
       </c>
-      <c r="AK76" s="43">
-        <f t="shared" si="9"/>
+      <c r="AK76" s="39">
+        <f t="shared" si="5"/>
         <v>5666</v>
       </c>
     </row>
     <row r="77" spans="1:37">
-      <c r="A77" s="46">
-        <f t="shared" si="8"/>
+      <c r="A77" s="42">
+        <f t="shared" si="4"/>
         <v>76</v>
       </c>
-      <c r="B77" s="46" t="str">
+      <c r="B77" s="42" t="str">
         <f>IF(D$2="Your Name Here","Enter Name",ROUND(_xlfn.NORM.INV(Random!D87,20,15),1))</f>
         <v>Enter Name</v>
       </c>
-      <c r="AK77" s="43">
-        <f t="shared" si="9"/>
+      <c r="AK77" s="39">
+        <f t="shared" si="5"/>
         <v>39</v>
       </c>
     </row>
     <row r="78" spans="1:37">
-      <c r="A78" s="46">
-        <f t="shared" si="8"/>
+      <c r="A78" s="42">
+        <f t="shared" si="4"/>
         <v>77</v>
       </c>
-      <c r="B78" s="46" t="str">
+      <c r="B78" s="42" t="str">
         <f>IF(D$2="Your Name Here","Enter Name",ROUND(_xlfn.NORM.INV(Random!D88,20,15),1))</f>
         <v>Enter Name</v>
       </c>
-      <c r="AK78" s="43">
-        <f t="shared" si="9"/>
+      <c r="AK78" s="39">
+        <f t="shared" si="5"/>
         <v>856</v>
       </c>
     </row>
     <row r="79" spans="1:37">
-      <c r="A79" s="46">
-        <f t="shared" si="8"/>
+      <c r="A79" s="42">
+        <f t="shared" si="4"/>
         <v>78</v>
       </c>
-      <c r="B79" s="46" t="str">
+      <c r="B79" s="42" t="str">
         <f>IF(D$2="Your Name Here","Enter Name",ROUND(_xlfn.NORM.INV(Random!D89,20,15),1))</f>
         <v>Enter Name</v>
       </c>
-      <c r="AK79" s="43">
-        <f t="shared" si="9"/>
+      <c r="AK79" s="39">
+        <f t="shared" si="5"/>
         <v>7585</v>
       </c>
     </row>
     <row r="80" spans="1:37">
-      <c r="A80" s="46">
-        <f t="shared" si="8"/>
+      <c r="A80" s="42">
+        <f t="shared" si="4"/>
         <v>79</v>
       </c>
-      <c r="B80" s="46" t="str">
+      <c r="B80" s="42" t="str">
         <f>IF(D$2="Your Name Here","Enter Name",ROUND(_xlfn.NORM.INV(Random!D90,20,15),1))</f>
         <v>Enter Name</v>
       </c>
-      <c r="AK80" s="43">
-        <f t="shared" si="9"/>
+      <c r="AK80" s="39">
+        <f t="shared" si="5"/>
         <v>4326</v>
       </c>
     </row>
     <row r="81" spans="1:37">
-      <c r="A81" s="46">
-        <f t="shared" si="8"/>
+      <c r="A81" s="42">
+        <f t="shared" si="4"/>
         <v>80</v>
       </c>
-      <c r="B81" s="46" t="str">
+      <c r="B81" s="42" t="str">
         <f>IF(D$2="Your Name Here","Enter Name",ROUND(_xlfn.NORM.INV(Random!D91,20,15),1))</f>
         <v>Enter Name</v>
       </c>
-      <c r="AK81" s="43">
-        <f t="shared" si="9"/>
+      <c r="AK81" s="39">
+        <f t="shared" si="5"/>
         <v>7919</v>
       </c>
     </row>
     <row r="82" spans="1:37">
-      <c r="A82" s="46">
-        <f t="shared" si="8"/>
+      <c r="A82" s="42">
+        <f t="shared" si="4"/>
         <v>81</v>
       </c>
-      <c r="B82" s="46" t="str">
+      <c r="B82" s="42" t="str">
         <f>IF(D$2="Your Name Here","Enter Name",ROUND(_xlfn.NORM.INV(Random!D92,20,15),1))</f>
         <v>Enter Name</v>
       </c>
-      <c r="AK82" s="43">
-        <f t="shared" si="9"/>
+      <c r="AK82" s="39">
+        <f t="shared" si="5"/>
         <v>240</v>
       </c>
     </row>
     <row r="83" spans="1:37">
-      <c r="A83" s="46">
-        <f t="shared" si="8"/>
+      <c r="A83" s="42">
+        <f t="shared" si="4"/>
         <v>82</v>
       </c>
-      <c r="B83" s="46" t="str">
+      <c r="B83" s="42" t="str">
         <f>IF(D$2="Your Name Here","Enter Name",ROUND(_xlfn.NORM.INV(Random!D93,20,15),1))</f>
         <v>Enter Name</v>
       </c>
-      <c r="AK83" s="43">
-        <f t="shared" si="9"/>
+      <c r="AK83" s="39">
+        <f t="shared" si="5"/>
         <v>6553</v>
       </c>
     </row>
     <row r="84" spans="1:37">
-      <c r="A84" s="46">
-        <f t="shared" si="8"/>
+      <c r="A84" s="42">
+        <f t="shared" si="4"/>
         <v>83</v>
       </c>
-      <c r="B84" s="46" t="str">
+      <c r="B84" s="42" t="str">
         <f>IF(D$2="Your Name Here","Enter Name",ROUND(_xlfn.NORM.INV(Random!D94,20,15),1))</f>
         <v>Enter Name</v>
       </c>
-      <c r="AK84" s="43">
-        <f t="shared" si="9"/>
+      <c r="AK84" s="39">
+        <f t="shared" si="5"/>
         <v>3550</v>
       </c>
     </row>
     <row r="85" spans="1:37">
-      <c r="A85" s="46">
-        <f t="shared" si="8"/>
+      <c r="A85" s="42">
+        <f t="shared" si="4"/>
         <v>84</v>
       </c>
-      <c r="B85" s="46" t="str">
+      <c r="B85" s="42" t="str">
         <f>IF(D$2="Your Name Here","Enter Name",ROUND(_xlfn.NORM.INV(Random!D95,20,15),1))</f>
         <v>Enter Name</v>
       </c>
-      <c r="AK85" s="43">
-        <f t="shared" si="9"/>
+      <c r="AK85" s="39">
+        <f t="shared" si="5"/>
         <v>7691</v>
       </c>
     </row>
     <row r="86" spans="1:37">
-      <c r="A86" s="46">
-        <f t="shared" si="8"/>
+      <c r="A86" s="42">
+        <f t="shared" si="4"/>
         <v>85</v>
       </c>
-      <c r="B86" s="46" t="str">
+      <c r="B86" s="42" t="str">
         <f>IF(D$2="Your Name Here","Enter Name",ROUND(_xlfn.NORM.INV(Random!D96,20,15),1))</f>
         <v>Enter Name</v>
       </c>
-      <c r="AK86" s="43">
-        <f t="shared" si="9"/>
+      <c r="AK86" s="39">
+        <f t="shared" si="5"/>
         <v>3908</v>
       </c>
     </row>
     <row r="87" spans="1:37">
-      <c r="A87" s="46">
-        <f t="shared" si="8"/>
+      <c r="A87" s="42">
+        <f t="shared" si="4"/>
         <v>86</v>
       </c>
-      <c r="B87" s="46" t="str">
+      <c r="B87" s="42" t="str">
         <f>IF(D$2="Your Name Here","Enter Name",ROUND(_xlfn.NORM.INV(Random!D97,20,15),1))</f>
         <v>Enter Name</v>
       </c>
-      <c r="AK87" s="43">
-        <f t="shared" si="9"/>
+      <c r="AK87" s="39">
+        <f t="shared" si="5"/>
         <v>8529</v>
       </c>
     </row>
     <row r="88" spans="1:37">
-      <c r="A88" s="46">
-        <f t="shared" si="8"/>
+      <c r="A88" s="42">
+        <f t="shared" si="4"/>
         <v>87</v>
       </c>
-      <c r="B88" s="46" t="str">
+      <c r="B88" s="42" t="str">
         <f>IF(D$2="Your Name Here","Enter Name",ROUND(_xlfn.NORM.INV(Random!D98,20,15),1))</f>
         <v>Enter Name</v>
       </c>
-      <c r="AK88" s="43">
-        <f t="shared" si="9"/>
+      <c r="AK88" s="39">
+        <f t="shared" si="5"/>
         <v>2334</v>
       </c>
     </row>
     <row r="89" spans="1:37">
-      <c r="A89" s="46">
-        <f t="shared" si="8"/>
+      <c r="A89" s="42">
+        <f t="shared" si="4"/>
         <v>88</v>
       </c>
-      <c r="B89" s="46" t="str">
+      <c r="B89" s="42" t="str">
         <f>IF(D$2="Your Name Here","Enter Name",ROUND(_xlfn.NORM.INV(Random!D99,20,15),1))</f>
         <v>Enter Name</v>
       </c>
-      <c r="AK89" s="43">
-        <f t="shared" si="9"/>
+      <c r="AK89" s="39">
+        <f t="shared" si="5"/>
         <v>2795</v>
       </c>
     </row>
     <row r="90" spans="1:37">
-      <c r="A90" s="46">
-        <f t="shared" si="8"/>
+      <c r="A90" s="42">
+        <f t="shared" si="4"/>
         <v>89</v>
       </c>
-      <c r="B90" s="46" t="str">
+      <c r="B90" s="42" t="str">
         <f>IF(D$2="Your Name Here","Enter Name",ROUND(_xlfn.NORM.INV(Random!D100,20,15),1))</f>
         <v>Enter Name</v>
       </c>
-      <c r="AK90" s="43">
-        <f t="shared" si="9"/>
+      <c r="AK90" s="39">
+        <f t="shared" si="5"/>
         <v>8332</v>
       </c>
     </row>
     <row r="91" spans="1:37">
-      <c r="A91" s="46">
-        <f t="shared" si="8"/>
+      <c r="A91" s="42">
+        <f t="shared" si="4"/>
         <v>90</v>
       </c>
-      <c r="B91" s="46" t="str">
+      <c r="B91" s="42" t="str">
         <f>IF(D$2="Your Name Here","Enter Name",ROUND(_xlfn.NORM.INV(Random!D101,20,15),1))</f>
         <v>Enter Name</v>
       </c>
-      <c r="AK91" s="43">
-        <f t="shared" si="9"/>
+      <c r="AK91" s="39">
+        <f t="shared" si="5"/>
         <v>5101</v>
       </c>
     </row>
     <row r="92" spans="1:37">
-      <c r="A92" s="46">
-        <f t="shared" si="8"/>
+      <c r="A92" s="42">
+        <f t="shared" si="4"/>
         <v>91</v>
       </c>
-      <c r="B92" s="46" t="str">
+      <c r="B92" s="42" t="str">
         <f>IF(D$2="Your Name Here","Enter Name",ROUND(_xlfn.NORM.INV(Random!D102,20,15),1))</f>
         <v>Enter Name</v>
       </c>
-      <c r="AK92" s="43">
-        <f t="shared" si="9"/>
+      <c r="AK92" s="39">
+        <f t="shared" si="5"/>
         <v>3738</v>
       </c>
     </row>
     <row r="93" spans="1:37">
-      <c r="A93" s="46">
-        <f t="shared" si="8"/>
+      <c r="A93" s="42">
+        <f t="shared" si="4"/>
         <v>92</v>
       </c>
-      <c r="B93" s="46" t="str">
+      <c r="B93" s="42" t="str">
         <f>IF(D$2="Your Name Here","Enter Name",ROUND(_xlfn.NORM.INV(Random!D103,20,15),1))</f>
         <v>Enter Name</v>
       </c>
-      <c r="AK93" s="43">
-        <f t="shared" si="9"/>
+      <c r="AK93" s="39">
+        <f t="shared" si="5"/>
         <v>1931</v>
       </c>
     </row>
     <row r="94" spans="1:37">
-      <c r="A94" s="46">
-        <f t="shared" si="8"/>
+      <c r="A94" s="42">
+        <f t="shared" si="4"/>
         <v>93</v>
       </c>
-      <c r="B94" s="46" t="str">
+      <c r="B94" s="42" t="str">
         <f>IF(D$2="Your Name Here","Enter Name",ROUND(_xlfn.NORM.INV(Random!D104,20,15),1))</f>
         <v>Enter Name</v>
       </c>
-      <c r="AK94" s="43">
-        <f t="shared" si="9"/>
+      <c r="AK94" s="39">
+        <f t="shared" si="5"/>
         <v>5336</v>
       </c>
     </row>
     <row r="95" spans="1:37">
-      <c r="A95" s="46">
-        <f t="shared" si="8"/>
+      <c r="A95" s="42">
+        <f t="shared" si="4"/>
         <v>94</v>
       </c>
-      <c r="B95" s="46" t="str">
+      <c r="B95" s="42" t="str">
         <f>IF(D$2="Your Name Here","Enter Name",ROUND(_xlfn.NORM.INV(Random!D105,20,15),1))</f>
         <v>Enter Name</v>
       </c>
-      <c r="AK95" s="43">
-        <f t="shared" si="9"/>
+      <c r="AK95" s="39">
+        <f t="shared" si="5"/>
         <v>3417</v>
       </c>
     </row>
     <row r="96" spans="1:37">
-      <c r="A96" s="46">
-        <f t="shared" si="8"/>
+      <c r="A96" s="42">
+        <f t="shared" si="4"/>
         <v>95</v>
       </c>
-      <c r="B96" s="46" t="str">
+      <c r="B96" s="42" t="str">
         <f>IF(D$2="Your Name Here","Enter Name",ROUND(_xlfn.NORM.INV(Random!D106,20,15),1))</f>
         <v>Enter Name</v>
       </c>
-      <c r="AK96" s="43">
-        <f t="shared" si="9"/>
+      <c r="AK96" s="39">
+        <f t="shared" si="5"/>
         <v>8302</v>
       </c>
     </row>
     <row r="97" spans="1:37">
-      <c r="A97" s="46">
-        <f t="shared" si="8"/>
+      <c r="A97" s="42">
+        <f t="shared" si="4"/>
         <v>96</v>
       </c>
-      <c r="B97" s="46" t="str">
+      <c r="B97" s="42" t="str">
         <f>IF(D$2="Your Name Here","Enter Name",ROUND(_xlfn.NORM.INV(Random!D107,20,15),1))</f>
         <v>Enter Name</v>
       </c>
-      <c r="AK97" s="43">
-        <f t="shared" si="9"/>
+      <c r="AK97" s="39">
+        <f t="shared" si="5"/>
         <v>1239</v>
       </c>
     </row>
     <row r="98" spans="1:37">
-      <c r="A98" s="46">
-        <f t="shared" si="8"/>
+      <c r="A98" s="42">
+        <f t="shared" si="4"/>
         <v>97</v>
       </c>
-      <c r="B98" s="46" t="str">
+      <c r="B98" s="42" t="str">
         <f>IF(D$2="Your Name Here","Enter Name",ROUND(_xlfn.NORM.INV(Random!D108,20,15),1))</f>
         <v>Enter Name</v>
       </c>
-      <c r="AK98" s="43">
-        <f t="shared" si="9"/>
+      <c r="AK98" s="39">
+        <f t="shared" si="5"/>
         <v>8584</v>
       </c>
     </row>
     <row r="99" spans="1:37">
-      <c r="A99" s="46">
-        <f t="shared" si="8"/>
+      <c r="A99" s="42">
+        <f t="shared" si="4"/>
         <v>98</v>
       </c>
-      <c r="B99" s="46" t="str">
+      <c r="B99" s="42" t="str">
         <f>IF(D$2="Your Name Here","Enter Name",ROUND(_xlfn.NORM.INV(Random!D109,20,15),1))</f>
         <v>Enter Name</v>
       </c>
-      <c r="AK99" s="43">
-        <f t="shared" si="9"/>
+      <c r="AK99" s="39">
+        <f t="shared" si="5"/>
         <v>6357</v>
       </c>
     </row>
     <row r="100" spans="1:37">
-      <c r="A100" s="46">
-        <f t="shared" si="8"/>
+      <c r="A100" s="42">
+        <f t="shared" si="4"/>
         <v>99</v>
       </c>
-      <c r="B100" s="46" t="str">
+      <c r="B100" s="42" t="str">
         <f>IF(D$2="Your Name Here","Enter Name",ROUND(_xlfn.NORM.INV(Random!D110,20,15),1))</f>
         <v>Enter Name</v>
       </c>
-      <c r="AK100" s="43">
-        <f t="shared" si="9"/>
+      <c r="AK100" s="39">
+        <f t="shared" si="5"/>
         <v>1554</v>
       </c>
     </row>
     <row r="101" spans="1:37">
-      <c r="A101" s="46">
-        <f t="shared" si="8"/>
+      <c r="A101" s="42">
+        <f t="shared" si="4"/>
         <v>100</v>
       </c>
-      <c r="B101" s="46" t="str">
+      <c r="B101" s="42" t="str">
         <f>IF(D$2="Your Name Here","Enter Name",ROUND(_xlfn.NORM.INV(Random!D111,20,15),1))</f>
         <v>Enter Name</v>
       </c>
-      <c r="AK101" s="43">
-        <f t="shared" si="9"/>
+      <c r="AK101" s="39">
+        <f t="shared" si="5"/>
         <v>3275</v>
       </c>
     </row>
     <row r="102" spans="1:37">
-      <c r="A102" s="46">
-        <f t="shared" si="8"/>
+      <c r="A102" s="42">
+        <f t="shared" si="4"/>
         <v>101</v>
       </c>
-      <c r="B102" s="46" t="str">
+      <c r="B102" s="42" t="str">
         <f>IF(D$2="Your Name Here","Enter Name",ROUND(_xlfn.NORM.INV(Random!D112,20,15),1))</f>
         <v>Enter Name</v>
       </c>
-      <c r="AK102" s="43">
-        <f t="shared" si="9"/>
+      <c r="AK102" s="39">
+        <f t="shared" si="5"/>
         <v>5920</v>
       </c>
     </row>
     <row r="103" spans="1:37">
-      <c r="A103" s="46">
-        <f t="shared" si="8"/>
+      <c r="A103" s="42">
+        <f t="shared" si="4"/>
         <v>102</v>
       </c>
-      <c r="B103" s="46" t="str">
+      <c r="B103" s="42" t="str">
         <f>IF(D$2="Your Name Here","Enter Name",ROUND(_xlfn.NORM.INV(Random!D113,20,15),1))</f>
         <v>Enter Name</v>
       </c>
-      <c r="AK103" s="43">
-        <f t="shared" si="9"/>
+      <c r="AK103" s="39">
+        <f t="shared" si="5"/>
         <v>941</v>
       </c>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="dDUi1CJseNMyE8aGANYgAz66Evc8HOEXri92JnAymyteplit9tNtJI27MSfmOFS6Bg5n3iXWmq0g81nO1Dqsvg==" saltValue="E23xxHiqqRs5AcThDrYNVw==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="nKVifps17/ZBu6dF25M2+vF8la0+P6VKtLPw5cGTnsfXR7hJyuKULjOHDc4e39PDbMEAw+j/Z225Q88MgtHXow==" saltValue="/RKR6ffGVD1Z5ds8daF0Ug==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
   <mergeCells count="9">
     <mergeCell ref="J10:O23"/>
     <mergeCell ref="D24:H27"/>
@@ -8947,7 +8157,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1A0C24EC-2702-4508-A145-C8DDC53D6026}">
   <dimension ref="A1:W461"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -19416,7 +18626,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <sheetPr codeName="Sheet5"/>
   <dimension ref="A1:A103"/>
@@ -19433,613 +18643,613 @@
     <row r="2" spans="1:1">
       <c r="A2" s="3">
         <f ca="1">ROUND(NORMINV(RAND(),68,3.75),1)</f>
-        <v>67</v>
+        <v>71.5</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="3">
         <f t="shared" ref="A3:A66" ca="1" si="0">ROUND(NORMINV(RAND(),68,3.75),1)</f>
-        <v>62.4</v>
+        <v>71.8</v>
       </c>
     </row>
     <row r="4" spans="1:1">
       <c r="A4" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>69.400000000000006</v>
+        <v>65.8</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>65.599999999999994</v>
+        <v>71.7</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>73.099999999999994</v>
+        <v>70.8</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>64.400000000000006</v>
+        <v>70.400000000000006</v>
       </c>
     </row>
     <row r="8" spans="1:1">
       <c r="A8" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>71.400000000000006</v>
+        <v>69.900000000000006</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>71.7</v>
+        <v>74.599999999999994</v>
       </c>
     </row>
     <row r="10" spans="1:1">
       <c r="A10" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>67.7</v>
+        <v>65.8</v>
       </c>
     </row>
     <row r="11" spans="1:1">
       <c r="A11" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>72</v>
+        <v>70.599999999999994</v>
       </c>
     </row>
     <row r="12" spans="1:1">
       <c r="A12" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>68.3</v>
+        <v>69.2</v>
       </c>
     </row>
     <row r="13" spans="1:1">
       <c r="A13" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>64.400000000000006</v>
+        <v>65.099999999999994</v>
       </c>
     </row>
     <row r="14" spans="1:1">
       <c r="A14" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>68.3</v>
+        <v>72.400000000000006</v>
       </c>
     </row>
     <row r="15" spans="1:1">
       <c r="A15" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>66.400000000000006</v>
+        <v>70.2</v>
       </c>
     </row>
     <row r="16" spans="1:1">
       <c r="A16" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>75.2</v>
+        <v>63.8</v>
       </c>
     </row>
     <row r="17" spans="1:1">
       <c r="A17" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>54.9</v>
+        <v>66.2</v>
       </c>
     </row>
     <row r="18" spans="1:1">
       <c r="A18" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>63.8</v>
+        <v>67</v>
       </c>
     </row>
     <row r="19" spans="1:1">
       <c r="A19" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>65</v>
+        <v>68.5</v>
       </c>
     </row>
     <row r="20" spans="1:1">
       <c r="A20" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>68.2</v>
+        <v>68.599999999999994</v>
       </c>
     </row>
     <row r="21" spans="1:1">
       <c r="A21" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>61.3</v>
+        <v>64.3</v>
       </c>
     </row>
     <row r="22" spans="1:1">
       <c r="A22" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>71.099999999999994</v>
+        <v>65.900000000000006</v>
       </c>
     </row>
     <row r="23" spans="1:1">
       <c r="A23" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>69.599999999999994</v>
+        <v>65.2</v>
       </c>
     </row>
     <row r="24" spans="1:1">
       <c r="A24" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>65.400000000000006</v>
+        <v>69.599999999999994</v>
       </c>
     </row>
     <row r="25" spans="1:1">
       <c r="A25" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>68</v>
+        <v>64.7</v>
       </c>
     </row>
     <row r="26" spans="1:1">
       <c r="A26" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>67.099999999999994</v>
+        <v>73.400000000000006</v>
       </c>
     </row>
     <row r="27" spans="1:1">
       <c r="A27" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>71.400000000000006</v>
+        <v>68.900000000000006</v>
       </c>
     </row>
     <row r="28" spans="1:1">
       <c r="A28" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>69.400000000000006</v>
+        <v>65.8</v>
       </c>
     </row>
     <row r="29" spans="1:1">
       <c r="A29" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>65.7</v>
+        <v>67</v>
       </c>
     </row>
     <row r="30" spans="1:1">
       <c r="A30" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>69.7</v>
+        <v>69.599999999999994</v>
       </c>
     </row>
     <row r="31" spans="1:1">
       <c r="A31" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>66</v>
+        <v>67.2</v>
       </c>
     </row>
     <row r="32" spans="1:1">
       <c r="A32" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>69.5</v>
+        <v>72.2</v>
       </c>
     </row>
     <row r="33" spans="1:1">
       <c r="A33" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>73.3</v>
+        <v>63.5</v>
       </c>
     </row>
     <row r="34" spans="1:1">
       <c r="A34" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>69.599999999999994</v>
+        <v>74.599999999999994</v>
       </c>
     </row>
     <row r="35" spans="1:1">
       <c r="A35" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>68.099999999999994</v>
+        <v>63.8</v>
       </c>
     </row>
     <row r="36" spans="1:1">
       <c r="A36" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>73</v>
+        <v>70</v>
       </c>
     </row>
     <row r="37" spans="1:1">
       <c r="A37" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>70.900000000000006</v>
+        <v>60.8</v>
       </c>
     </row>
     <row r="38" spans="1:1">
       <c r="A38" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>66.5</v>
+        <v>67.2</v>
       </c>
     </row>
     <row r="39" spans="1:1">
       <c r="A39" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>74.900000000000006</v>
+        <v>70.8</v>
       </c>
     </row>
     <row r="40" spans="1:1">
       <c r="A40" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>72</v>
+        <v>62.2</v>
       </c>
     </row>
     <row r="41" spans="1:1">
       <c r="A41" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>62.4</v>
+        <v>66.3</v>
       </c>
     </row>
     <row r="42" spans="1:1">
       <c r="A42" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>68.400000000000006</v>
+        <v>70.2</v>
       </c>
     </row>
     <row r="43" spans="1:1">
       <c r="A43" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>69.599999999999994</v>
+        <v>67.400000000000006</v>
       </c>
     </row>
     <row r="44" spans="1:1">
       <c r="A44" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>77.2</v>
+        <v>64.5</v>
       </c>
     </row>
     <row r="45" spans="1:1">
       <c r="A45" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>69</v>
+        <v>69.5</v>
       </c>
     </row>
     <row r="46" spans="1:1">
       <c r="A46" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>67.8</v>
+        <v>63.8</v>
       </c>
     </row>
     <row r="47" spans="1:1">
       <c r="A47" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>75.900000000000006</v>
+        <v>73.099999999999994</v>
       </c>
     </row>
     <row r="48" spans="1:1">
       <c r="A48" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>67.900000000000006</v>
+        <v>69.900000000000006</v>
       </c>
     </row>
     <row r="49" spans="1:1">
       <c r="A49" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>66.3</v>
+        <v>63.9</v>
       </c>
     </row>
     <row r="50" spans="1:1">
       <c r="A50" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>71.900000000000006</v>
+        <v>66.8</v>
       </c>
     </row>
     <row r="51" spans="1:1">
       <c r="A51" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>64.2</v>
+        <v>63.9</v>
       </c>
     </row>
     <row r="52" spans="1:1">
       <c r="A52" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>67.099999999999994</v>
+        <v>63.7</v>
       </c>
     </row>
     <row r="53" spans="1:1">
       <c r="A53" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>73.3</v>
+        <v>65.3</v>
       </c>
     </row>
     <row r="54" spans="1:1">
       <c r="A54" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>69.3</v>
+        <v>64.900000000000006</v>
       </c>
     </row>
     <row r="55" spans="1:1">
       <c r="A55" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>61.6</v>
+        <v>66</v>
       </c>
     </row>
     <row r="56" spans="1:1">
       <c r="A56" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>67.8</v>
+        <v>67.900000000000006</v>
       </c>
     </row>
     <row r="57" spans="1:1">
       <c r="A57" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>73.099999999999994</v>
+        <v>61.9</v>
       </c>
     </row>
     <row r="58" spans="1:1">
       <c r="A58" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>66.2</v>
+        <v>70.3</v>
       </c>
     </row>
     <row r="59" spans="1:1">
       <c r="A59" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>71.599999999999994</v>
+        <v>71.3</v>
       </c>
     </row>
     <row r="60" spans="1:1">
       <c r="A60" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>62.1</v>
+        <v>71.3</v>
       </c>
     </row>
     <row r="61" spans="1:1">
       <c r="A61" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>79.8</v>
+        <v>69.3</v>
       </c>
     </row>
     <row r="62" spans="1:1">
       <c r="A62" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>67.099999999999994</v>
+        <v>68.7</v>
       </c>
     </row>
     <row r="63" spans="1:1">
       <c r="A63" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>67.7</v>
+        <v>71.7</v>
       </c>
     </row>
     <row r="64" spans="1:1">
       <c r="A64" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>67.3</v>
+        <v>70.3</v>
       </c>
     </row>
     <row r="65" spans="1:1">
       <c r="A65" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>72</v>
+        <v>67.7</v>
       </c>
     </row>
     <row r="66" spans="1:1">
       <c r="A66" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>70.3</v>
+        <v>66.8</v>
       </c>
     </row>
     <row r="67" spans="1:1">
       <c r="A67" s="3">
         <f t="shared" ref="A67:A103" ca="1" si="1">ROUND(NORMINV(RAND(),68,3.75),1)</f>
-        <v>67.5</v>
+        <v>66.400000000000006</v>
       </c>
     </row>
     <row r="68" spans="1:1">
       <c r="A68" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>72.3</v>
+        <v>68.599999999999994</v>
       </c>
     </row>
     <row r="69" spans="1:1">
       <c r="A69" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>67.099999999999994</v>
+        <v>67</v>
       </c>
     </row>
     <row r="70" spans="1:1">
       <c r="A70" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>75.5</v>
+        <v>71.7</v>
       </c>
     </row>
     <row r="71" spans="1:1">
       <c r="A71" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>62.8</v>
+        <v>65.2</v>
       </c>
     </row>
     <row r="72" spans="1:1">
       <c r="A72" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>69.2</v>
+        <v>66.599999999999994</v>
       </c>
     </row>
     <row r="73" spans="1:1">
       <c r="A73" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>70.900000000000006</v>
+        <v>68.400000000000006</v>
       </c>
     </row>
     <row r="74" spans="1:1">
       <c r="A74" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>73.3</v>
+        <v>65.5</v>
       </c>
     </row>
     <row r="75" spans="1:1">
       <c r="A75" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>68.3</v>
+        <v>67.2</v>
       </c>
     </row>
     <row r="76" spans="1:1">
       <c r="A76" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>65.2</v>
+        <v>64.900000000000006</v>
       </c>
     </row>
     <row r="77" spans="1:1">
       <c r="A77" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>66.900000000000006</v>
+        <v>59.5</v>
       </c>
     </row>
     <row r="78" spans="1:1">
       <c r="A78" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>69.5</v>
+        <v>57.1</v>
       </c>
     </row>
     <row r="79" spans="1:1">
       <c r="A79" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>72.8</v>
+        <v>61.6</v>
       </c>
     </row>
     <row r="80" spans="1:1">
       <c r="A80" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>73.900000000000006</v>
+        <v>68.099999999999994</v>
       </c>
     </row>
     <row r="81" spans="1:1">
       <c r="A81" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>72.2</v>
+        <v>63.4</v>
       </c>
     </row>
     <row r="82" spans="1:1">
       <c r="A82" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>65.2</v>
+        <v>69.900000000000006</v>
       </c>
     </row>
     <row r="83" spans="1:1">
       <c r="A83" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>69.900000000000006</v>
+        <v>75.400000000000006</v>
       </c>
     </row>
     <row r="84" spans="1:1">
       <c r="A84" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>72.2</v>
+        <v>66.400000000000006</v>
       </c>
     </row>
     <row r="85" spans="1:1">
       <c r="A85" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>63.2</v>
+        <v>70.7</v>
       </c>
     </row>
     <row r="86" spans="1:1">
       <c r="A86" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>63.1</v>
+        <v>69.2</v>
       </c>
     </row>
     <row r="87" spans="1:1">
       <c r="A87" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>69.2</v>
+        <v>79</v>
       </c>
     </row>
     <row r="88" spans="1:1">
       <c r="A88" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>62.1</v>
+        <v>68</v>
       </c>
     </row>
     <row r="89" spans="1:1">
       <c r="A89" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>71.400000000000006</v>
+        <v>72.099999999999994</v>
       </c>
     </row>
     <row r="90" spans="1:1">
       <c r="A90" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>66.8</v>
+        <v>70.8</v>
       </c>
     </row>
     <row r="91" spans="1:1">
       <c r="A91" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>70.900000000000006</v>
+        <v>68.7</v>
       </c>
     </row>
     <row r="92" spans="1:1">
       <c r="A92" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>74.3</v>
+        <v>61.9</v>
       </c>
     </row>
     <row r="93" spans="1:1">
       <c r="A93" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>63.9</v>
+        <v>70.599999999999994</v>
       </c>
     </row>
     <row r="94" spans="1:1">
       <c r="A94" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>67.3</v>
+        <v>79.2</v>
       </c>
     </row>
     <row r="95" spans="1:1">
       <c r="A95" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>64.099999999999994</v>
+        <v>68.2</v>
       </c>
     </row>
     <row r="96" spans="1:1">
       <c r="A96" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>63.7</v>
+        <v>61.1</v>
       </c>
     </row>
     <row r="97" spans="1:1">
       <c r="A97" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>63.8</v>
+        <v>69.900000000000006</v>
       </c>
     </row>
     <row r="98" spans="1:1">
       <c r="A98" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>69</v>
+        <v>59.5</v>
       </c>
     </row>
     <row r="99" spans="1:1">
       <c r="A99" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>68.099999999999994</v>
+        <v>65.400000000000006</v>
       </c>
     </row>
     <row r="100" spans="1:1">
       <c r="A100" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>67.099999999999994</v>
+        <v>70</v>
       </c>
     </row>
     <row r="101" spans="1:1">
       <c r="A101" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>68</v>
+        <v>69.599999999999994</v>
       </c>
     </row>
     <row r="102" spans="1:1">
       <c r="A102" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>68.900000000000006</v>
+        <v>75</v>
       </c>
     </row>
     <row r="103" spans="1:1">
       <c r="A103" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>72.5</v>
+        <v>65.3</v>
       </c>
     </row>
   </sheetData>
@@ -20053,84 +19263,84 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B21D072D-12F0-444E-8D9A-9CC18311A26B}">
   <dimension ref="B2:H9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="2" spans="2:8">
-      <c r="B2" s="178" t="s">
+      <c r="B2" s="187" t="s">
         <v>500</v>
       </c>
-      <c r="C2" s="178"/>
-      <c r="D2" s="178"/>
-      <c r="E2" s="178"/>
-      <c r="F2" s="178"/>
-      <c r="G2" s="178"/>
-      <c r="H2" s="178"/>
+      <c r="C2" s="187"/>
+      <c r="D2" s="187"/>
+      <c r="E2" s="187"/>
+      <c r="F2" s="187"/>
+      <c r="G2" s="187"/>
+      <c r="H2" s="187"/>
     </row>
     <row r="3" spans="2:8">
-      <c r="B3" s="178"/>
-      <c r="C3" s="178"/>
-      <c r="D3" s="178"/>
-      <c r="E3" s="178"/>
-      <c r="F3" s="178"/>
-      <c r="G3" s="178"/>
-      <c r="H3" s="178"/>
+      <c r="B3" s="187"/>
+      <c r="C3" s="187"/>
+      <c r="D3" s="187"/>
+      <c r="E3" s="187"/>
+      <c r="F3" s="187"/>
+      <c r="G3" s="187"/>
+      <c r="H3" s="187"/>
     </row>
     <row r="4" spans="2:8">
-      <c r="B4" s="178"/>
-      <c r="C4" s="178"/>
-      <c r="D4" s="178"/>
-      <c r="E4" s="178"/>
-      <c r="F4" s="178"/>
-      <c r="G4" s="178"/>
-      <c r="H4" s="178"/>
+      <c r="B4" s="187"/>
+      <c r="C4" s="187"/>
+      <c r="D4" s="187"/>
+      <c r="E4" s="187"/>
+      <c r="F4" s="187"/>
+      <c r="G4" s="187"/>
+      <c r="H4" s="187"/>
     </row>
     <row r="5" spans="2:8">
-      <c r="B5" s="178"/>
-      <c r="C5" s="178"/>
-      <c r="D5" s="178"/>
-      <c r="E5" s="178"/>
-      <c r="F5" s="178"/>
-      <c r="G5" s="178"/>
-      <c r="H5" s="178"/>
+      <c r="B5" s="187"/>
+      <c r="C5" s="187"/>
+      <c r="D5" s="187"/>
+      <c r="E5" s="187"/>
+      <c r="F5" s="187"/>
+      <c r="G5" s="187"/>
+      <c r="H5" s="187"/>
     </row>
     <row r="6" spans="2:8">
-      <c r="B6" s="178"/>
-      <c r="C6" s="178"/>
-      <c r="D6" s="178"/>
-      <c r="E6" s="178"/>
-      <c r="F6" s="178"/>
-      <c r="G6" s="178"/>
-      <c r="H6" s="178"/>
+      <c r="B6" s="187"/>
+      <c r="C6" s="187"/>
+      <c r="D6" s="187"/>
+      <c r="E6" s="187"/>
+      <c r="F6" s="187"/>
+      <c r="G6" s="187"/>
+      <c r="H6" s="187"/>
     </row>
     <row r="7" spans="2:8">
-      <c r="B7" s="178"/>
-      <c r="C7" s="178"/>
-      <c r="D7" s="178"/>
-      <c r="E7" s="178"/>
-      <c r="F7" s="178"/>
-      <c r="G7" s="178"/>
-      <c r="H7" s="178"/>
+      <c r="B7" s="187"/>
+      <c r="C7" s="187"/>
+      <c r="D7" s="187"/>
+      <c r="E7" s="187"/>
+      <c r="F7" s="187"/>
+      <c r="G7" s="187"/>
+      <c r="H7" s="187"/>
     </row>
     <row r="8" spans="2:8">
-      <c r="B8" s="178"/>
-      <c r="C8" s="178"/>
-      <c r="D8" s="178"/>
-      <c r="E8" s="178"/>
-      <c r="F8" s="178"/>
-      <c r="G8" s="178"/>
-      <c r="H8" s="178"/>
+      <c r="B8" s="187"/>
+      <c r="C8" s="187"/>
+      <c r="D8" s="187"/>
+      <c r="E8" s="187"/>
+      <c r="F8" s="187"/>
+      <c r="G8" s="187"/>
+      <c r="H8" s="187"/>
     </row>
     <row r="9" spans="2:8">
-      <c r="B9" s="178"/>
-      <c r="C9" s="178"/>
-      <c r="D9" s="178"/>
-      <c r="E9" s="178"/>
-      <c r="F9" s="178"/>
-      <c r="G9" s="178"/>
-      <c r="H9" s="178"/>
+      <c r="B9" s="187"/>
+      <c r="C9" s="187"/>
+      <c r="D9" s="187"/>
+      <c r="E9" s="187"/>
+      <c r="F9" s="187"/>
+      <c r="G9" s="187"/>
+      <c r="H9" s="187"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -20359,6 +19569,15 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <lcf76f155ced4ddcb4097134ff3c332f xmlns="cca9fd2d-ef84-45c9-8063-8f4bd4c29606">
@@ -20366,15 +19585,6 @@
     </lcf76f155ced4ddcb4097134ff3c332f>
   </documentManagement>
 </p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -20397,6 +19607,14 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{17F1EF20-95AB-4016-A693-6625F3A67214}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{924A8F3D-57F5-4941-A32A-55B7F7F7AF07}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
@@ -20404,12 +19622,4 @@
     <ds:schemaRef ds:uri="cca9fd2d-ef84-45c9-8063-8f4bd4c29606"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{17F1EF20-95AB-4016-A693-6625F3A67214}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>